--- a/output/BhavikBhagat_A00494758_WorkLogs.xlsx
+++ b/output/BhavikBhagat_A00494758_WorkLogs.xlsx
@@ -116,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -166,25 +166,11 @@
         <color rgb="008A0027"/>
       </bottom>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="008A0027"/>
-      </left>
-      <right style="medium">
-        <color rgb="008A0027"/>
-      </right>
-      <top style="medium">
-        <color rgb="008A0027"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="008A0027"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -259,26 +245,20 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -651,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:F294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -739,10 +719,10 @@
         </is>
       </c>
       <c r="E4" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="4">
-        <f>SUM(E4:E6)</f>
+        <f>SUM(E4:E8)</f>
         <v/>
       </c>
     </row>
@@ -751,10 +731,24 @@
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="9" t="inlineStr">
         <is>
+          <t>Onboarding &amp; Environment Setup</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr"/>
+      <c r="E5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="143" customHeight="1">
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
           <t>Environment Configuration &amp; Architecture Study</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>- Configured AWS CLI with Citco's local machine connection guide for SSO-based authentication.
 - Tested AWS SSO login flow and verified access to citcoshareddev01 account via console.
@@ -768,20 +762,34 @@
 - Explored CloudWatch console to understand existing log groups and metric namespaces.</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="8" t="n"/>
-    </row>
-    <row r="6" ht="143" customHeight="1">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="E6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="143" customHeight="1">
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Environment Configuration &amp; Architecture Study</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="143" customHeight="1">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>KT session with Horace for RPA Support Queue</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>- Attended BPM Control Questionnaire security review meeting.
 - Learned about Citco's Line of Business (LoB) role structure and Active Directory integration.
@@ -791,28 +799,28 @@
 - Understood UAT vs Production environment data handling policies.</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E8" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="11" t="n"/>
-    </row>
-    <row r="7" ht="143" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="F8" s="11" t="n"/>
+    </row>
+    <row r="9" ht="143" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Week 2</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Mar 23 – Mar 27, 2026</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>AWS Database Services Deep Dive</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>- Studied AWS relational databases: RDS architecture with Single-AZ and Multi-AZ deployment options.
 - Learned Aurora auto-scaling capabilities and cost advantages over standard RDS.
@@ -826,23 +834,37 @@
 - Reviewed Amazon TimeStream for IoT time-series data with automatic data lifecycle management.</t>
         </is>
       </c>
-      <c r="E7" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="14">
-        <f>SUM(E7:E9)</f>
+      <c r="E9" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="14">
+        <f>SUM(E9:E14)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="143" customHeight="1">
-      <c r="A8" s="18" t="n"/>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="19" t="inlineStr">
+    <row r="10" ht="143" customHeight="1">
+      <c r="A10" s="18" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>AWS Database Services Deep Dive</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr"/>
+      <c r="E10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="18" t="n"/>
+    </row>
+    <row r="11" ht="143" customHeight="1">
+      <c r="A11" s="18" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>CloudWatch &amp; CloudFormation Study</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>- Studied CloudWatch CMAA cycle: Collect, Monitor, Act, Analyze.
 - Learned CloudWatch metrics: EC2 (1min detailed vs 5min free), custom metrics, 15-month retention.
@@ -856,20 +878,34 @@
 - Explored CloudFormation change sets to understand how to preview infrastructure changes before applying.</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="18" t="n"/>
-    </row>
-    <row r="9" ht="143" customHeight="1">
-      <c r="A9" s="21" t="n"/>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="E11" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="143" customHeight="1">
+      <c r="A12" s="18" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>CloudWatch &amp; CloudFormation Study</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr"/>
+      <c r="E12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="143" customHeight="1">
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>AWS Lambda &amp; Serverless Architecture</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>- Deep dive into AWS Lambda execution environment: runtime lifecycle, handler function structure.
 - Studied Lambda memory configuration (128MB–10GB) and CPU allocation proportional to memory.
@@ -883,28 +919,42 @@
 - Practiced creating a simple Lambda function with Python runtime via AWS Console.</t>
         </is>
       </c>
-      <c r="E9" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" s="21" t="n"/>
-    </row>
-    <row r="10" ht="143" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="E13" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="143" customHeight="1">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>AWS Lambda &amp; Serverless Architecture</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr"/>
+      <c r="E14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="143" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Week 3</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Mar 30 – Apr 03, 2026</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>CTI CloudWatch Metrics &amp; Dashboard</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>- Added CloudWatch metrics instrumentation to track CTI submission activities within the pipeline.
 - Created CloudWatch Pipeline Health Dashboard for operational visibility into system performance.
@@ -918,23 +968,37 @@
 - Added CloudWatch dashboard screenshots to support the PR review process.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F10" s="4">
-        <f>SUM(E10:E12)</f>
+      <c r="E15" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="4">
+        <f>SUM(E15:E19)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="143" customHeight="1">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="9" t="inlineStr">
+    <row r="16" ht="143" customHeight="1">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>CTI CloudWatch Metrics &amp; Dashboard</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="143" customHeight="1">
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>CTI CloudWatch Dashboard Log Insights</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>- Added technical dashboard with CloudWatch Log Insights widget for deeper system analysis.
 - Created CloudWatch Logs Insights queries to extract error patterns from Lambda execution logs.
@@ -948,20 +1012,34 @@
 - Documented Log Insights query syntax and widget configuration for team knowledge sharing.</t>
         </is>
       </c>
-      <c r="E11" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F11" s="8" t="n"/>
-    </row>
-    <row r="12" ht="143" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="E17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="143" customHeight="1">
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>CTI CloudWatch Dashboard Log Insights</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="143" customHeight="1">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>CTI Dashboard Testing &amp; Code Quality</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>- Added comprehensive unit tests for CloudWatch Logs Insights query functionality.
 - Created unit tests for dashboard CloudFormation templates to validate deployment reliability.
@@ -975,28 +1053,28 @@
 - Prepared PR description with detailed summary of changes and testing performed.</t>
         </is>
       </c>
-      <c r="E12" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="11" t="n"/>
-    </row>
-    <row r="13" ht="143" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="E19" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="143" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Week 4</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Apr 06 – Apr 10, 2026</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>CTI Technical Dashboard &amp; Branch Merge</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D20" s="16" t="inlineStr">
         <is>
           <t>- Added technical dashboard with CloudWatch Log Insights widget for deeper system analysis.
 - Created comprehensive unit tests for CloudWatch Logs Insights query functionality.
@@ -1010,23 +1088,37 @@
 - Added CloudWatch dashboard screenshots to support the PR review process.</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="14">
-        <f>SUM(E13:E15)</f>
+      <c r="E20" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="14">
+        <f>SUM(E20:E24)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="143" customHeight="1">
-      <c r="A14" s="18" t="n"/>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="19" t="inlineStr">
+    <row r="21" ht="143" customHeight="1">
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>CTI Technical Dashboard &amp; Branch Merge</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr"/>
+      <c r="E21" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="143" customHeight="1">
+      <c r="A22" s="18" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>IA Lambda Monitoring Dashboard</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>- Created static CloudWatch dashboard IA-Lambda-Monitoring-Dashboard.
 - Added filter info widget at the top with usage instructions for team members.
@@ -1040,20 +1132,34 @@
 - Fixed dashboard builder to validate text widgets with markdown property correctly.</t>
         </is>
       </c>
-      <c r="E14" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="18" t="n"/>
-    </row>
-    <row r="15" ht="143" customHeight="1">
-      <c r="A15" s="21" t="n"/>
-      <c r="B15" s="21" t="n"/>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="E22" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="143" customHeight="1">
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>IA Lambda Monitoring Dashboard</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr"/>
+      <c r="E23" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="18" t="n"/>
+    </row>
+    <row r="24" ht="143" customHeight="1">
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>Lambda Dashboard PR Review &amp; Refinement</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>- Addressed PR review feedback on Lambda Monitoring Dashboard from senior team members.
 - Refined dashboard widget layout based on usability suggestions from code review.
@@ -1067,28 +1173,28 @@
 - Updated team runbook with links to the new Lambda monitoring dashboard and inventory page.</t>
         </is>
       </c>
-      <c r="E15" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="F15" s="21" t="n"/>
-    </row>
-    <row r="16" ht="143" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="E24" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="21" t="n"/>
+    </row>
+    <row r="25" ht="143" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Week 5</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Apr 13 – Apr 17, 2026</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Multi-Dashboard Architecture Refactor</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>- Refactored the monitoring solution to a multi-dashboard architecture for better organization and maintainability.
 - Implemented explicit Lambda list filtering to ensure dashboards display only relevant functions.
@@ -1098,23 +1204,37 @@
 - Separated dashboard concerns into distinct views for better user experience and focused monitoring.</t>
         </is>
       </c>
-      <c r="E16" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="4">
-        <f>SUM(E16:E21)</f>
+      <c r="E25" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="4">
+        <f>SUM(E25:E35)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="143" customHeight="1">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9" t="inlineStr">
+    <row r="26" ht="143" customHeight="1">
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Multi-Dashboard Architecture Refactor</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr"/>
+      <c r="E26" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="8" t="n"/>
+    </row>
+    <row r="27" ht="143" customHeight="1">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Training Week Day 2</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>- Attended Citco corporate onboarding and compliance training sessions.
 - Completed mandatory security awareness training modules.
@@ -1122,20 +1242,34 @@
 - Met with team members for introductions and role overview.</t>
         </is>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F17" s="8" t="n"/>
-    </row>
-    <row r="18" ht="143" customHeight="1">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="E27" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="8" t="n"/>
+    </row>
+    <row r="28" ht="143" customHeight="1">
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Training Week Day 2</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr"/>
+      <c r="E28" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="8" t="n"/>
+    </row>
+    <row r="29" ht="143" customHeight="1">
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Training Week Day 3</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>- Continued Citco corporate training modules.
 - AWS environment walkthrough with Horace (Ho Hoi Leung).
@@ -1143,20 +1277,34 @@
 - Reviewed existing CloudWatch dashboards and monitoring approach.</t>
         </is>
       </c>
-      <c r="E18" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="143" customHeight="1">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="E29" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="143" customHeight="1">
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Training Week Day 3</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="8" t="n"/>
+    </row>
+    <row r="31" ht="143" customHeight="1">
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Training Week Day 4</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>- RPA platform overview: Blue Prism / UiPath architecture KT.
 - Event Store API and logging standards training — patterns will be used in dashboard work.
@@ -1164,38 +1312,66 @@
 - Reviewed RPA support responsibilities for future rotations.</t>
         </is>
       </c>
-      <c r="E19" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="143" customHeight="1">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="E31" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="8" t="n"/>
+    </row>
+    <row r="32" ht="143" customHeight="1">
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Training Week Day 4</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33" ht="143" customHeight="1">
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Development &amp; Implementation</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>- Continued development work and implementation tasks.</t>
         </is>
       </c>
-      <c r="E20" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="143" customHeight="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="E33" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="143" customHeight="1">
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Development &amp; Implementation</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr"/>
+      <c r="E34" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="143" customHeight="1">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D35" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (4 meetings, 2.5h):
 - SRE Team Standup (30 min)
@@ -1204,28 +1380,28 @@
 - Knowledge Transfer (30 min)</t>
         </is>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E35" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="143" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="F35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="143" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Week 6</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>Apr 20 – Apr 24, 2026</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>Centralized CloudWatch Dashboard Improvements</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D36" s="16" t="inlineStr">
         <is>
           <t>- Added a monitoring export Lambda function with daily cron scheduling and automatic S3 upload capability.
 - Implemented S3 upload functionality for monitoring reports and resource lists.
@@ -1237,23 +1413,37 @@
 - Updated the dashboard to pull Lambda data from the API instead of static files.</t>
         </is>
       </c>
-      <c r="E22" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F22" s="14">
-        <f>SUM(E22:E32)</f>
+      <c r="E36" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="14">
+        <f>SUM(E36:E48)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="143" customHeight="1">
-      <c r="A23" s="18" t="n"/>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="19" t="inlineStr">
+    <row r="37" ht="143" customHeight="1">
+      <c r="A37" s="18" t="n"/>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>Centralized CloudWatch Dashboard Improvements</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr"/>
+      <c r="E37" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" s="18" t="n"/>
+    </row>
+    <row r="38" ht="143" customHeight="1">
+      <c r="A38" s="18" t="n"/>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>Lambda Trigger Detection, API Refactor &amp; Test Overhaul</t>
         </is>
       </c>
-      <c r="D23" s="19" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>- Added Lambda trigger source detection to identify whether functions are triggered by SQS, API Gateway, or EventBridge/Scheduled events.
 - Implemented detection logic using list_event_source_mappings, get_policy, and describe_rule APIs.
@@ -1265,58 +1455,72 @@
 - Updated the resources_monitoring_api README with production server commands and refactored structure documentation.</t>
         </is>
       </c>
-      <c r="E23" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="18" t="n"/>
-    </row>
-    <row r="24" ht="143" customHeight="1">
-      <c r="A24" s="18" t="n"/>
-      <c r="B24" s="18" t="n"/>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="E38" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="18" t="n"/>
+    </row>
+    <row r="39" ht="143" customHeight="1">
+      <c r="A39" s="18" t="n"/>
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>Lambda Trigger Detection, API Refactor &amp; Test Overhaul</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr"/>
+      <c r="E39" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="18" t="n"/>
+    </row>
+    <row r="40" ht="143" customHeight="1">
+      <c r="A40" s="18" t="n"/>
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>EC2/ECS/EKS Resource Discovery &amp; API Consolidation</t>
         </is>
       </c>
-      <c r="D24" s="19" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>- Added EC2, ECS, and EKS resource discovery endpoints to resources_monitoring_api for broader infrastructure visibility.
 - Refactored the API by consolidating all resource endpoints under the /api/v1/resources/ path for consistent routing.</t>
         </is>
       </c>
-      <c r="E24" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F24" s="18" t="n"/>
-    </row>
-    <row r="25" ht="143" customHeight="1">
-      <c r="A25" s="18" t="n"/>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="E40" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="18" t="n"/>
+    </row>
+    <row r="41" ht="143" customHeight="1">
+      <c r="A41" s="18" t="n"/>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>Versioned S3 Export &amp; DEV Bucket Fix</t>
         </is>
       </c>
-      <c r="D25" s="19" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>- Implemented versioned Lambda list saving to S3 alongside the latest version for historical tracking.
 - Changed the DEV S3 bucket to dev-citco-ia-checklist-service-documents for proper environment alignment.</t>
         </is>
       </c>
-      <c r="E25" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F25" s="18" t="n"/>
-    </row>
-    <row r="26" ht="143" customHeight="1">
-      <c r="A26" s="18" t="n"/>
-      <c r="B26" s="18" t="n"/>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="E41" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="18" t="n"/>
+    </row>
+    <row r="42" ht="143" customHeight="1">
+      <c r="A42" s="18" t="n"/>
+      <c r="B42" s="18" t="n"/>
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>API Swagger Redirect, Registry Refactor &amp; Package Structure</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D42" s="19" t="inlineStr">
         <is>
           <t>- Updated the monitoring export Lambda to use the new DEV S3 bucket for proper environment configuration.
 - Added redirect from root URL to Swagger UI at /docs for better API discoverability.
@@ -1328,39 +1532,39 @@
 - Removed redundant region/account_id fields from resource item models to simplify the data structure.</t>
         </is>
       </c>
-      <c r="E26" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F26" s="18" t="n"/>
-    </row>
-    <row r="27" ht="143" customHeight="1">
-      <c r="A27" s="18" t="n"/>
-      <c r="B27" s="18" t="n"/>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="E42" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="18" t="n"/>
+    </row>
+    <row r="43" ht="143" customHeight="1">
+      <c r="A43" s="18" t="n"/>
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>EC2 Registry Module</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D43" s="19" t="inlineStr">
         <is>
           <t>- Added availability_zone and tags fields to EC2 instance response for richer resource metadata.
 - Created a standalone ec2_registry.py module with session-based API for EC2 resource discovery.</t>
         </is>
       </c>
-      <c r="E27" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F27" s="18" t="n"/>
-    </row>
-    <row r="28" ht="143" customHeight="1">
-      <c r="A28" s="18" t="n"/>
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="E43" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" s="18" t="n"/>
+    </row>
+    <row r="44" ht="143" customHeight="1">
+      <c r="A44" s="18" t="n"/>
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>ia-resources-monitoring Repo Setup, Code Quality &amp; CLI Entry Point</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D44" s="19" t="inlineStr">
         <is>
           <t>- Set up new ia-resources-monitoring repository with initial docs, requirements, pyproject.toml, and pre-commit configuration.
 - Added limitations documentation and dashboard screenshots.
@@ -1372,56 +1576,56 @@
 - Created ia_paths.py module and refactored all sys.path.insert calls to use package imports.</t>
         </is>
       </c>
-      <c r="E28" s="20" t="n">
+      <c r="E44" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="18" t="n"/>
-    </row>
-    <row r="29" ht="143" customHeight="1">
-      <c r="A29" s="18" t="n"/>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="F44" s="18" t="n"/>
+    </row>
+    <row r="45" ht="143" customHeight="1">
+      <c r="A45" s="18" t="n"/>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>resources_monitoring_api Migration</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>- Migrated resources_monitoring_api package to the new ia-resources-monitoring repository.</t>
         </is>
       </c>
-      <c r="E29" s="20" t="n">
+      <c r="E45" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="18" t="n"/>
-    </row>
-    <row r="30" ht="143" customHeight="1">
-      <c r="A30" s="18" t="n"/>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="F45" s="18" t="n"/>
+    </row>
+    <row r="46" ht="143" customHeight="1">
+      <c r="A46" s="18" t="n"/>
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>ia_lambda_monitoring_dashboard Migration</t>
         </is>
       </c>
-      <c r="D30" s="19" t="inlineStr">
+      <c r="D46" s="19" t="inlineStr">
         <is>
           <t>- Migrated ia_lambda_monitoring_dashboard package to the centralized ia-resources-monitoring repository.</t>
         </is>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E46" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="18" t="n"/>
-    </row>
-    <row r="31" ht="143" customHeight="1">
-      <c r="A31" s="18" t="n"/>
-      <c r="B31" s="18" t="n"/>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="F46" s="18" t="n"/>
+    </row>
+    <row r="47" ht="143" customHeight="1">
+      <c r="A47" s="18" t="n"/>
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>EC2 Dashboard Migration &amp; rpacfs1 EC2 Work</t>
         </is>
       </c>
-      <c r="D31" s="19" t="inlineStr">
+      <c r="D47" s="19" t="inlineStr">
         <is>
           <t>- Migrated ia_ec2_monitoring_dashboard package to the centralized ia-resources-monitoring repository.
 - Added ia_ec2_monitoring_dashboard package with navigation bar in rpacfs1 repo.
@@ -1431,20 +1635,20 @@
 - Moved cais-pe-dashboard CloudFormation templates to project root for easier access.</t>
         </is>
       </c>
-      <c r="E31" s="20" t="n">
+      <c r="E47" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F31" s="18" t="n"/>
-    </row>
-    <row r="32" ht="143" customHeight="1">
-      <c r="A32" s="21" t="n"/>
-      <c r="B32" s="21" t="n"/>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="F47" s="18" t="n"/>
+    </row>
+    <row r="48" ht="143" customHeight="1">
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="21" t="n"/>
+      <c r="C48" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D48" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (4 meetings, 2.5h):
 - SRE Team Standup (30 min)
@@ -1453,28 +1657,28 @@
 - Sprint Planning (60 min)</t>
         </is>
       </c>
-      <c r="E32" s="26" t="n">
+      <c r="E48" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F32" s="21" t="n"/>
-    </row>
-    <row r="33" ht="143" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="F48" s="21" t="n"/>
+    </row>
+    <row r="49" ht="143" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Week 7</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Apr 27 – May 01, 2026</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>ECS Monitoring Dashboard</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>- Added the ia_ecs_monitoring_dashboard package with complete dashboards, widgets, tests, CloudFormation templates, export functionality, and deploy support.
 - Fixed the preview functionality to use resolved output showing text widget titles and replacing placeholders correctly.
@@ -1483,42 +1687,56 @@
 - Updated to use native PendingTaskCount metric instead of calculated values.</t>
         </is>
       </c>
-      <c r="E33" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F33" s="4">
-        <f>SUM(E33:E47)</f>
+      <c r="E49" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="4">
+        <f>SUM(E49:E65)</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="143" customHeight="1">
-      <c r="A34" s="8" t="n"/>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="9" t="inlineStr">
+    <row r="50" ht="143" customHeight="1">
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>ECS Monitoring Dashboard</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr"/>
+      <c r="E50" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="8" t="n"/>
+    </row>
+    <row r="51" ht="143" customHeight="1">
+      <c r="A51" s="8" t="n"/>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>src/api Package Restructure &amp; Save-Queries CLI</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>- Added --delete flag to save-queries CLI for CloudWatch Logs Insights query management.
 - Restructured the ia-resources-monitoring project into src/ and api/ packages for better organization.</t>
         </is>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E51" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="F34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="143" customHeight="1">
-      <c r="A35" s="8" t="n"/>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="F51" s="8" t="n"/>
+    </row>
+    <row r="52" ht="143" customHeight="1">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>EKS Monitoring Dashboard</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>- Completed the EKS monitoring dashboard with full functionality.
 - Fixed S3 export bucket configuration and added EKS paths to shared config.
@@ -1529,38 +1747,38 @@
 - Moved error investigation from health dashboard to overview and added EKS saved query.</t>
         </is>
       </c>
-      <c r="E35" s="10" t="n">
+      <c r="E52" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="143" customHeight="1">
-      <c r="A36" s="8" t="n"/>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="F52" s="8" t="n"/>
+    </row>
+    <row r="53" ht="143" customHeight="1">
+      <c r="A53" s="8" t="n"/>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>ECS Widget YAML Split</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>- Split ECS widget YAMLs into 1 file per row following the src/ structure pattern.</t>
         </is>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E53" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="F36" s="8" t="n"/>
-    </row>
-    <row r="37" ht="143" customHeight="1">
-      <c r="A37" s="8" t="n"/>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="F53" s="8" t="n"/>
+    </row>
+    <row r="54" ht="143" customHeight="1">
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>Output Structure, S3 Prefixes &amp; Dashboard Builder Updates</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>- Added navigation and header widgets to all ECS and EKS dashboards for consistent UX.
 - Consolidated output folders to use _lists suffix for consistent naming.
@@ -1571,20 +1789,20 @@
 - Updated dashboard builders to use {ENV}/resources/ paths.</t>
         </is>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E54" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="F37" s="8" t="n"/>
-    </row>
-    <row r="38" ht="143" customHeight="1">
-      <c r="A38" s="8" t="n"/>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="F54" s="8" t="n"/>
+    </row>
+    <row r="55" ht="143" customHeight="1">
+      <c r="A55" s="8" t="n"/>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>cais-pe Dashboard Pipeline &amp; rpacfs1 Cleanup</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>- Removed monitoring packages from rpacfs1 repo — fully migrated to ia-resources-monitoring.
 - Removed docs/screenshots from rpacfs1 — migrated to centralized repo.
@@ -1596,20 +1814,20 @@
 - Added @log field to error investigation query in technical dashboard for better log filtering.</t>
         </is>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E55" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="F38" s="8" t="n"/>
-    </row>
-    <row r="39" ht="143" customHeight="1">
-      <c r="A39" s="8" t="n"/>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="F55" s="8" t="n"/>
+    </row>
+    <row r="56" ht="143" customHeight="1">
+      <c r="A56" s="8" t="n"/>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Logs Insights Optimisation, Saved Queries &amp; Code Quality</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>- Removed old output folder creation from lambda exporter and associated tests.
 - Updated all markdown files to reflect current state: 4 resources, 12 dashboards, EKS support, correct paths.
@@ -1621,20 +1839,34 @@
 - Fixed delete functionality to handle both folder-prefixed and legacy query names.</t>
         </is>
       </c>
-      <c r="E39" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F39" s="8" t="n"/>
-    </row>
-    <row r="40" ht="143" customHeight="1">
-      <c r="A40" s="8" t="n"/>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="E56" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" s="8" t="n"/>
+    </row>
+    <row r="57" ht="143" customHeight="1">
+      <c r="A57" s="8" t="n"/>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>Logs Insights Optimisation, Saved Queries &amp; Code Quality</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr"/>
+      <c r="E57" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F57" s="8" t="n"/>
+    </row>
+    <row r="58" ht="143" customHeight="1">
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>EC2 Dashboard Polish</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>- Fixed EC2 dashboard discovery to use AppName fallback for instances without standard naming.
 - Fixed EC2 dashboard layout and added missing performance widgets.
@@ -1645,74 +1877,74 @@
 - Fixed header height to 4, added Credit Balance widget to health dashboard, and added annotations and AVG line to performance dashboard.</t>
         </is>
       </c>
-      <c r="E40" s="10" t="n">
+      <c r="E58" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F40" s="8" t="n"/>
-    </row>
-    <row r="41" ht="143" customHeight="1">
-      <c r="A41" s="8" t="n"/>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="F58" s="8" t="n"/>
+    </row>
+    <row r="59" ht="143" customHeight="1">
+      <c r="A59" s="8" t="n"/>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>Dashboard Header Standardisation</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
         <is>
           <t>- Standardized dashboard headers across all resources and excluded them from the trailing-whitespace pre-commit hook.</t>
         </is>
       </c>
-      <c r="E41" s="10" t="n">
+      <c r="E59" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F41" s="8" t="n"/>
-    </row>
-    <row r="42" ht="143" customHeight="1">
-      <c r="A42" s="8" t="n"/>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="F59" s="8" t="n"/>
+    </row>
+    <row r="60" ht="143" customHeight="1">
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>ECS Reservation Widgets Restore</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>- Restored CPU/Memory reservation widgets that were previously removed.</t>
         </is>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E60" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F42" s="8" t="n"/>
-    </row>
-    <row r="43" ht="143" customHeight="1">
-      <c r="A43" s="8" t="n"/>
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="F60" s="8" t="n"/>
+    </row>
+    <row r="61" ht="143" customHeight="1">
+      <c r="A61" s="8" t="n"/>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>ECS Service Inventory Table</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>- Replaced ECS reservation widgets with a service inventory table for better visibility.</t>
         </is>
       </c>
-      <c r="E43" s="10" t="n">
+      <c r="E61" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="8" t="n"/>
-    </row>
-    <row r="44" ht="143" customHeight="1">
-      <c r="A44" s="8" t="n"/>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="F61" s="8" t="n"/>
+    </row>
+    <row r="62" ht="143" customHeight="1">
+      <c r="A62" s="8" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>EKS Dashboard Finalisation &amp; Merge</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>- Switched EKS dashboard to use AWS/EKS control plane metrics for accurate monitoring.
 - Fixed EKS Overview layout for proper widget alignment.
@@ -1724,20 +1956,20 @@
 - Increased EKS test coverage to 81% for better code reliability.</t>
         </is>
       </c>
-      <c r="E44" s="10" t="n">
+      <c r="E62" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F44" s="8" t="n"/>
-    </row>
-    <row r="45" ht="143" customHeight="1">
-      <c r="A45" s="8" t="n"/>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="F62" s="8" t="n"/>
+    </row>
+    <row r="63" ht="143" customHeight="1">
+      <c r="A63" s="8" t="n"/>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>Structured Logging &amp; Test Coverage</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>- Added .gitattributes for line ending normalization across different platforms.
 - Replaced print statements and disable_warnings with structured logging in the API package.
@@ -1747,38 +1979,38 @@
 - Merged test coverage improvements into release/SRE.</t>
         </is>
       </c>
-      <c r="E45" s="10" t="n">
+      <c r="E63" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F45" s="8" t="n"/>
-    </row>
-    <row r="46" ht="143" customHeight="1">
-      <c r="A46" s="8" t="n"/>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="F63" s="8" t="n"/>
+    </row>
+    <row r="64" ht="143" customHeight="1">
+      <c r="A64" s="8" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>EC2 Dashboard Improvements</t>
         </is>
       </c>
-      <c r="D46" s="9" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>- Improved EC2 dashboard with Fleet Status, EBS metrics, and removed Fleet Avg widget.</t>
         </is>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E64" s="10" t="n">
         <v>2.25</v>
       </c>
-      <c r="F46" s="8" t="n"/>
-    </row>
-    <row r="47" ht="143" customHeight="1">
-      <c r="A47" s="11" t="n"/>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="24" t="inlineStr">
+      <c r="F64" s="8" t="n"/>
+    </row>
+    <row r="65" ht="143" customHeight="1">
+      <c r="A65" s="11" t="n"/>
+      <c r="B65" s="11" t="n"/>
+      <c r="C65" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D47" s="25" t="inlineStr">
+      <c r="D65" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (4 meetings, 2.5h):
 - Tech Talk || AI Strategy (30 min)
@@ -1787,28 +2019,28 @@
 - Daily Standup (30 min)</t>
         </is>
       </c>
-      <c r="E47" s="26" t="n">
+      <c r="E65" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F47" s="11" t="n"/>
-    </row>
-    <row r="48" ht="143" customHeight="1">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="F65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="143" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>Week 8</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B66" s="15" t="inlineStr">
         <is>
           <t>May 04 – May 08, 2026</t>
         </is>
       </c>
-      <c r="C48" s="27" t="inlineStr">
+      <c r="C66" s="27" t="inlineStr">
         <is>
           <t>RPA Production Support Shift</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>- Reviewed Confluence shift handover log from APAC team.
 - Monitored SD Portal queue and Teams channels for incoming tickets.
@@ -1824,41 +2056,167 @@
 - Checked MESO DB queries for client report status.</t>
         </is>
       </c>
-      <c r="E48" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F48" s="14">
-        <f>SUM(E48:E53)</f>
+      <c r="E66" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" s="14">
+        <f>SUM(E66:E80)</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="143" customHeight="1">
-      <c r="A49" s="18" t="n"/>
-      <c r="B49" s="18" t="n"/>
-      <c r="C49" s="9" t="inlineStr">
+    <row r="67" ht="143" customHeight="1">
+      <c r="A67" s="18" t="n"/>
+      <c r="B67" s="18" t="n"/>
+      <c r="C67" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr"/>
+      <c r="E67" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" s="18" t="n"/>
+    </row>
+    <row r="68" ht="143" customHeight="1">
+      <c r="A68" s="18" t="n"/>
+      <c r="B68" s="18" t="n"/>
+      <c r="C68" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr"/>
+      <c r="E68" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F68" s="18" t="n"/>
+    </row>
+    <row r="69" ht="143" customHeight="1">
+      <c r="A69" s="18" t="n"/>
+      <c r="B69" s="18" t="n"/>
+      <c r="C69" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr"/>
+      <c r="E69" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="18" t="n"/>
+    </row>
+    <row r="70" ht="143" customHeight="1">
+      <c r="A70" s="18" t="n"/>
+      <c r="B70" s="18" t="n"/>
+      <c r="C70" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr"/>
+      <c r="E70" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" s="18" t="n"/>
+    </row>
+    <row r="71" ht="143" customHeight="1">
+      <c r="A71" s="18" t="n"/>
+      <c r="B71" s="18" t="n"/>
+      <c r="C71" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr"/>
+      <c r="E71" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F71" s="18" t="n"/>
+    </row>
+    <row r="72" ht="143" customHeight="1">
+      <c r="A72" s="18" t="n"/>
+      <c r="B72" s="18" t="n"/>
+      <c r="C72" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr"/>
+      <c r="E72" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F72" s="18" t="n"/>
+    </row>
+    <row r="73" ht="143" customHeight="1">
+      <c r="A73" s="18" t="n"/>
+      <c r="B73" s="18" t="n"/>
+      <c r="C73" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr"/>
+      <c r="E73" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" s="18" t="n"/>
+    </row>
+    <row r="74" ht="143" customHeight="1">
+      <c r="A74" s="18" t="n"/>
+      <c r="B74" s="18" t="n"/>
+      <c r="C74" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr"/>
+      <c r="E74" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" s="18" t="n"/>
+    </row>
+    <row r="75" ht="143" customHeight="1">
+      <c r="A75" s="18" t="n"/>
+      <c r="B75" s="18" t="n"/>
+      <c r="C75" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr"/>
+      <c r="E75" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" s="18" t="n"/>
+    </row>
+    <row r="76" ht="143" customHeight="1">
+      <c r="A76" s="18" t="n"/>
+      <c r="B76" s="18" t="n"/>
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>EC2 Overview Widget Layout Fix</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D76" s="9" t="inlineStr">
         <is>
           <t>- Adjusted widget heights and y-offsets for the EC2 overview dashboard for better visual layout.</t>
         </is>
       </c>
-      <c r="E49" s="10" t="n">
+      <c r="E76" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="18" t="n"/>
-    </row>
-    <row r="50" ht="143" customHeight="1">
-      <c r="A50" s="18" t="n"/>
-      <c r="B50" s="18" t="n"/>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="F76" s="18" t="n"/>
+    </row>
+    <row r="77" ht="143" customHeight="1">
+      <c r="A77" s="18" t="n"/>
+      <c r="B77" s="18" t="n"/>
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>BudgetCode-First Discovery &amp; ECS Filter</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t>- Implemented BudgetCode-first discovery with AppName-fallback for flexible resource identification.
 - Added input sanitization to protect against invalid query parameters.
@@ -1866,38 +2224,38 @@
 - Fixed test mocks to align with the new filtering logic.</t>
         </is>
       </c>
-      <c r="E50" s="10" t="n">
+      <c r="E77" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="18" t="n"/>
-    </row>
-    <row r="51" ht="143" customHeight="1">
-      <c r="A51" s="18" t="n"/>
-      <c r="B51" s="18" t="n"/>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="F77" s="18" t="n"/>
+    </row>
+    <row r="78" ht="143" customHeight="1">
+      <c r="A78" s="18" t="n"/>
+      <c r="B78" s="18" t="n"/>
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>MERIDIAN ECS Cluster-Based Fallback</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>- Added cluster-based fallback for ECS service discovery when tag-based discovery fails — required for MERIDIAN platform where 5 of 6 ECS clusters are untagged and need name-based discovery.</t>
         </is>
       </c>
-      <c r="E51" s="10" t="n">
+      <c r="E78" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="18" t="n"/>
-    </row>
-    <row r="52" ht="143" customHeight="1">
-      <c r="A52" s="18" t="n"/>
-      <c r="B52" s="18" t="n"/>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="F78" s="18" t="n"/>
+    </row>
+    <row r="79" ht="143" customHeight="1">
+      <c r="A79" s="18" t="n"/>
+      <c r="B79" s="18" t="n"/>
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>Lambda Dashboard Budget Summary &amp; API Fixes</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="D79" s="9" t="inlineStr">
         <is>
           <t>- Removed the TopK dashboard variable widget from Lambda dashboards.
 - Merged upstream changes from release/SRE into the Lambda monitoring dashboard feature branch.
@@ -1906,46 +2264,46 @@
 - Implemented clickable Lambda inventory at top with budget summary at bottom for improved dashboard layout.</t>
         </is>
       </c>
-      <c r="E52" s="10" t="n">
+      <c r="E79" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="18" t="n"/>
-    </row>
-    <row r="53" ht="143" customHeight="1">
-      <c r="A53" s="21" t="n"/>
-      <c r="B53" s="21" t="n"/>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="F79" s="18" t="n"/>
+    </row>
+    <row r="80" ht="143" customHeight="1">
+      <c r="A80" s="21" t="n"/>
+      <c r="B80" s="21" t="n"/>
+      <c r="C80" s="12" t="inlineStr">
         <is>
           <t>Lambda Dashboard Widget Position Fix</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
         <is>
           <t>- Swapped widget positions in Lambda dashboards placing summary at top and inventory at bottom for better user experience.</t>
         </is>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E80" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="21" t="n"/>
-    </row>
-    <row r="54" ht="143" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="F80" s="21" t="n"/>
+    </row>
+    <row r="81" ht="143" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>Week 9</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>May 11 – May 15, 2026</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>Full Grafana Infrastructure Deploy</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>- Enforced coding standards including uv package manager, JavaDoc-style docstrings, and strict types.
 - Implemented Human-In-the-Loop (HIL) gate with trigger rules, blocking wait mechanism, and audit trail.
@@ -1957,23 +2315,37 @@
 - Created CloudWatch alarms CFN template with all 17 alerting rules.</t>
         </is>
       </c>
-      <c r="E54" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F54" s="4">
-        <f>SUM(E54:E60)</f>
+      <c r="E81" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" s="4">
+        <f>SUM(E81:E91)</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="143" customHeight="1">
-      <c r="A55" s="8" t="n"/>
-      <c r="B55" s="8" t="n"/>
-      <c r="C55" s="9" t="inlineStr">
+    <row r="82" ht="143" customHeight="1">
+      <c r="A82" s="8" t="n"/>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>Full Grafana Infrastructure Deploy</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr"/>
+      <c r="E82" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" s="8" t="n"/>
+    </row>
+    <row r="83" ht="143" customHeight="1">
+      <c r="A83" s="8" t="n"/>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>Documentation Suite, 99%→100% Coverage &amp; Release Merges</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>- Merged IISS-487 Grafana dashboard, alarms, CFN, pipeline, deploy scripts, and SSL fix into release.
 - Added release notes for IISS-487 SRE observability milestone.
@@ -1985,20 +2357,34 @@
 - Added permission fixes, IAM workarounds, and bootstrap transparency note for CFN execution role.</t>
         </is>
       </c>
-      <c r="E55" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F55" s="8" t="n"/>
-    </row>
-    <row r="56" ht="143" customHeight="1">
-      <c r="A56" s="8" t="n"/>
-      <c r="B56" s="8" t="n"/>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="E83" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" s="8" t="n"/>
+    </row>
+    <row r="84" ht="143" customHeight="1">
+      <c r="A84" s="8" t="n"/>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>Documentation Suite, 99%→100% Coverage &amp; Release Merges</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr"/>
+      <c r="E84" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F84" s="8" t="n"/>
+    </row>
+    <row r="85" ht="143" customHeight="1">
+      <c r="A85" s="8" t="n"/>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>SQS Panel Fixes, Grafana 12.4 Upgrade &amp; Pipeline Refactor</t>
         </is>
       </c>
-      <c r="D56" s="9" t="inlineStr">
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>- Fixed Queue Depth, Messages In-Flight, Age of Oldest Message, and DLQ Depth panels with per-queue breakdown and QueueName legends.
 - Achieved 100% test coverage on Row 2 SQS panels.
@@ -2010,38 +2396,38 @@
 - Added --pipeline flag to deploy.py and deleted deploy_pipeline.ps1/.sh.</t>
         </is>
       </c>
-      <c r="E56" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F56" s="8" t="n"/>
-    </row>
-    <row r="57" ht="143" customHeight="1">
-      <c r="A57" s="8" t="n"/>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="E85" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F85" s="8" t="n"/>
+    </row>
+    <row r="86" ht="143" customHeight="1">
+      <c r="A86" s="8" t="n"/>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="9" t="inlineStr">
         <is>
           <t>ia_ebinder_services: Dockerfile Python Upgrade</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="D86" s="9" t="inlineStr">
         <is>
           <t>- Updated Dockerfile in ia_ebinder_services to use python3.13 image instead of 3.12.</t>
         </is>
       </c>
-      <c r="E57" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F57" s="8" t="n"/>
-    </row>
-    <row r="58" ht="143" customHeight="1">
-      <c r="A58" s="8" t="n"/>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="E86" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F86" s="8" t="n"/>
+    </row>
+    <row r="87" ht="143" customHeight="1">
+      <c r="A87" s="8" t="n"/>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>23-Agent Architecture, Bootstrap Flow, SQS Panels &amp; Auto-sync .env</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
+      <c r="D87" s="9" t="inlineStr">
         <is>
           <t>- Synced feature/IISS-487-pipeline with release/IISS-487-sre-observability multiple times overnight.
 - Added git_expert and grafana_query_expert agents with docs/ knowledge base.
@@ -2053,20 +2439,34 @@
 - Added delegation DAG mermaid diagram to agents README.</t>
         </is>
       </c>
-      <c r="E58" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F58" s="8" t="n"/>
-    </row>
-    <row r="59" ht="143" customHeight="1">
-      <c r="A59" s="8" t="n"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="E87" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F87" s="8" t="n"/>
+    </row>
+    <row r="88" ht="143" customHeight="1">
+      <c r="A88" s="8" t="n"/>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>23-Agent Architecture, Bootstrap Flow, SQS Panels &amp; Auto-sync .env</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr"/>
+      <c r="E88" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F88" s="8" t="n"/>
+    </row>
+    <row r="89" ht="143" customHeight="1">
+      <c r="A89" s="8" t="n"/>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>Lambda Panels, $platform Variable &amp; SQS SQL Migration</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="D89" s="9" t="inlineStr">
         <is>
           <t>- Overhauled the developer-guide by removing manual AWS CLI steps for a cleaner workflow.
 - Fixed SQS panels with Metric Insights GROUP BY without LIMIT, DLQ timeseries, and turned off gauge threshold labels.
@@ -2078,20 +2478,34 @@
 - Fixed Lambda row with all panels using auto period, Throttles as timeseries, noValue handling, and Error Rate labels.</t>
         </is>
       </c>
-      <c r="E59" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F59" s="8" t="n"/>
-    </row>
-    <row r="60" ht="143" customHeight="1">
-      <c r="A60" s="11" t="n"/>
-      <c r="B60" s="11" t="n"/>
-      <c r="C60" s="24" t="inlineStr">
+      <c r="E89" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" s="8" t="n"/>
+    </row>
+    <row r="90" ht="143" customHeight="1">
+      <c r="A90" s="8" t="n"/>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Lambda Panels, $platform Variable &amp; SQS SQL Migration</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="inlineStr"/>
+      <c r="E90" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F90" s="8" t="n"/>
+    </row>
+    <row r="91" ht="143" customHeight="1">
+      <c r="A91" s="11" t="n"/>
+      <c r="B91" s="11" t="n"/>
+      <c r="C91" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D60" s="25" t="inlineStr">
+      <c r="D91" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (8 meetings, 2.5h):
 - MAS - Infrastructure Monitoring Review (60 min)
@@ -2104,28 +2518,28 @@
 - [Demo] RPA Support Agent (30 min)</t>
         </is>
       </c>
-      <c r="E60" s="26" t="n">
+      <c r="E91" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F60" s="11" t="n"/>
-    </row>
-    <row r="61" ht="143" customHeight="1">
-      <c r="A61" s="14" t="inlineStr">
+      <c r="F91" s="11" t="n"/>
+    </row>
+    <row r="92" ht="143" customHeight="1">
+      <c r="A92" s="14" t="inlineStr">
         <is>
           <t>Week 10</t>
         </is>
       </c>
-      <c r="B61" s="15" t="inlineStr">
+      <c r="B92" s="15" t="inlineStr">
         <is>
           <t>May 18 – May 22, 2026</t>
         </is>
       </c>
-      <c r="C61" s="16" t="inlineStr">
+      <c r="C92" s="16" t="inlineStr">
         <is>
           <t>Rows 5-8 SQL Migration, $platform Variable, Collapsed Rows &amp; Docs</t>
         </is>
       </c>
-      <c r="D61" s="16" t="inlineStr">
+      <c r="D92" s="16" t="inlineStr">
         <is>
           <t>- Migrated Row 5 ECS APIs to SQL with per-target-group breakdown; split into p50/p95/p99 panels.
 - Added $platform variable filter to Row 5 ECS APIs and shifted rows 06-10 gridPos.
@@ -2137,23 +2551,37 @@
 - Added renameByRegex to all rows; separated Queue Depth from DLQ Depth filters in Row 2 SQS.</t>
         </is>
       </c>
-      <c r="E61" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="F61" s="14">
-        <f>SUM(E61:E65)</f>
+      <c r="E92" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F92" s="14">
+        <f>SUM(E92:E101)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="143" customHeight="1">
-      <c r="A62" s="18" t="n"/>
-      <c r="B62" s="18" t="n"/>
-      <c r="C62" s="19" t="inlineStr">
+    <row r="93" ht="143" customHeight="1">
+      <c r="A93" s="18" t="n"/>
+      <c r="B93" s="18" t="n"/>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>Rows 5-8 SQL Migration, $platform Variable, Collapsed Rows &amp; Docs</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="inlineStr"/>
+      <c r="E93" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F93" s="18" t="n"/>
+    </row>
+    <row r="94" ht="143" customHeight="1">
+      <c r="A94" s="18" t="n"/>
+      <c r="B94" s="18" t="n"/>
+      <c r="C94" s="19" t="inlineStr">
         <is>
           <t>Rows 7-9 SQL Migration, Aurora/RDS Row, SQS Inventory &amp; Agent Roles</t>
         </is>
       </c>
-      <c r="D62" s="19" t="inlineStr">
+      <c r="D94" s="19" t="inlineStr">
         <is>
           <t>- Added DBCluster vs DBInstance explanation to concepts-explained documentation.
 - Added tag-based filtering notes to workflow steering document.
@@ -2165,20 +2593,34 @@
 - Removed filterFieldsByName from Row 5 ALB panels (ALB names don't contain 'meridian').</t>
         </is>
       </c>
-      <c r="E62" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F62" s="18" t="n"/>
-    </row>
-    <row r="63" ht="143" customHeight="1">
-      <c r="A63" s="18" t="n"/>
-      <c r="B63" s="18" t="n"/>
-      <c r="C63" s="19" t="inlineStr">
+      <c r="E94" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F94" s="18" t="n"/>
+    </row>
+    <row r="95" ht="143" customHeight="1">
+      <c r="A95" s="18" t="n"/>
+      <c r="B95" s="18" t="n"/>
+      <c r="C95" s="19" t="inlineStr">
+        <is>
+          <t>Rows 7-9 SQL Migration, Aurora/RDS Row, SQS Inventory &amp; Agent Roles</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="inlineStr"/>
+      <c r="E95" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" s="18" t="n"/>
+    </row>
+    <row r="96" ht="143" customHeight="1">
+      <c r="A96" s="18" t="n"/>
+      <c r="B96" s="18" t="n"/>
+      <c r="C96" s="19" t="inlineStr">
         <is>
           <t>ECS Row 4, $platform Variable, SQS Health &amp; Agentic AI Test Fixes</t>
         </is>
       </c>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="D96" s="19" t="inlineStr">
         <is>
           <t>- Updated SQS panels to use Metric Insights SQL with filterFieldsByName and fixed allValue for meridian filter.
 - Added $platform variable for multi-platform filtering using filterFieldsByName.
@@ -2190,20 +2632,34 @@
 - Split Row 4 ECS multi-query panels, removed blank labels, bumped provisioner to v71.</t>
         </is>
       </c>
-      <c r="E63" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F63" s="18" t="n"/>
-    </row>
-    <row r="64" ht="143" customHeight="1">
-      <c r="A64" s="18" t="n"/>
-      <c r="B64" s="18" t="n"/>
-      <c r="C64" s="19" t="inlineStr">
+      <c r="E96" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" s="18" t="n"/>
+    </row>
+    <row r="97" ht="143" customHeight="1">
+      <c r="A97" s="18" t="n"/>
+      <c r="B97" s="18" t="n"/>
+      <c r="C97" s="19" t="inlineStr">
+        <is>
+          <t>ECS Row 4, $platform Variable, SQS Health &amp; Agentic AI Test Fixes</t>
+        </is>
+      </c>
+      <c r="D97" s="19" t="inlineStr"/>
+      <c r="E97" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F97" s="18" t="n"/>
+    </row>
+    <row r="98" ht="143" customHeight="1">
+      <c r="A98" s="18" t="n"/>
+      <c r="B98" s="18" t="n"/>
+      <c r="C98" s="19" t="inlineStr">
         <is>
           <t>Agentic AI Test Suite Completion, Health Overview &amp; SSL Fix</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="D98" s="19" t="inlineStr">
         <is>
           <t>- Updated SQS row tests for new SQL expression format and added cfnlint API preflight checks.
 - Wrapped all CloudwatchAlarmsExpert instantiations in mock_aws for proper test isolation.
@@ -2215,20 +2671,34 @@
 - Added SQS Health stat panel showing sum of meridian queue maximums with 80/100 alert thresholds.</t>
         </is>
       </c>
-      <c r="E64" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F64" s="18" t="n"/>
-    </row>
-    <row r="65" ht="143" customHeight="1">
-      <c r="A65" s="21" t="n"/>
-      <c r="B65" s="21" t="n"/>
-      <c r="C65" s="24" t="inlineStr">
+      <c r="E98" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" s="18" t="n"/>
+    </row>
+    <row r="99" ht="143" customHeight="1">
+      <c r="A99" s="18" t="n"/>
+      <c r="B99" s="18" t="n"/>
+      <c r="C99" s="19" t="inlineStr">
+        <is>
+          <t>Agentic AI Test Suite Completion, Health Overview &amp; SSL Fix</t>
+        </is>
+      </c>
+      <c r="D99" s="19" t="inlineStr"/>
+      <c r="E99" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" s="18" t="n"/>
+    </row>
+    <row r="100" ht="143" customHeight="1">
+      <c r="A100" s="18" t="n"/>
+      <c r="B100" s="18" t="n"/>
+      <c r="C100" s="29" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D65" s="25" t="inlineStr">
+      <c r="D100" s="30" t="inlineStr">
         <is>
           <t>Meetings this week (9 meetings, 6.0h):
 - Daily Standup (30 min)
@@ -2242,28 +2712,42 @@
 - Innovation IT - AWS Centralized Dashboard Planning (30 min)</t>
         </is>
       </c>
-      <c r="E65" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="F65" s="21" t="n"/>
-    </row>
-    <row r="66" ht="143" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="E100" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F100" s="18" t="n"/>
+    </row>
+    <row r="101" ht="143" customHeight="1">
+      <c r="A101" s="21" t="n"/>
+      <c r="B101" s="21" t="n"/>
+      <c r="C101" s="24" t="inlineStr">
+        <is>
+          <t>Meetings &amp; Standups</t>
+        </is>
+      </c>
+      <c r="D101" s="25" t="inlineStr"/>
+      <c r="E101" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="21" t="n"/>
+    </row>
+    <row r="102" ht="143" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>Week 11</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>May 25 – May 29, 2026</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>Health Panels, S3 Dashboard Storage Migration &amp; Performance Overview</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
+      <c r="D102" s="6" t="inlineStr">
         <is>
           <t>- Added DocumentDB, Neptune DB, RDS/Aurora, and OpenSearch health panels with CPU 60/80% thresholds.
 - OpenSearch health panel shows Green/Degraded status based on ClusterStatus.green metric.
@@ -2275,23 +2759,37 @@
 - Added tests for deploy_stacks.py and deploy.py — achieved 100% test coverage.</t>
         </is>
       </c>
-      <c r="E66" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F66" s="4">
-        <f>SUM(E66:E72)</f>
+      <c r="E102" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F102" s="4">
+        <f>SUM(E102:E112)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="143" customHeight="1">
-      <c r="A67" s="8" t="n"/>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="9" t="inlineStr">
+    <row r="103" ht="143" customHeight="1">
+      <c r="A103" s="8" t="n"/>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="9" t="inlineStr">
+        <is>
+          <t>Health Panels, S3 Dashboard Storage Migration &amp; Performance Overview</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr"/>
+      <c r="E103" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F103" s="8" t="n"/>
+    </row>
+    <row r="104" ht="143" customHeight="1">
+      <c r="A104" s="8" t="n"/>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>Redis/Valkey Row, MSK Fix, Datasources, Visual Polish &amp; CLI Refactor</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>- Added Retro LCD bar gauges with duration units across all time panels for cleaner visual style.
 - Added renameByRegex to Performance Overview bar gauges for cleaner legend labels.
@@ -2303,20 +2801,34 @@
 - Refactored CLI — replaced --dry-run/--validate-only with unified --validate flag and added --smoke-test option.</t>
         </is>
       </c>
-      <c r="E67" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F67" s="8" t="n"/>
-    </row>
-    <row r="68" ht="143" customHeight="1">
-      <c r="A68" s="8" t="n"/>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="E104" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F104" s="8" t="n"/>
+    </row>
+    <row r="105" ht="143" customHeight="1">
+      <c r="A105" s="8" t="n"/>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>Redis/Valkey Row, MSK Fix, Datasources, Visual Polish &amp; CLI Refactor</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr"/>
+      <c r="E105" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F105" s="8" t="n"/>
+    </row>
+    <row r="106" ht="143" customHeight="1">
+      <c r="A106" s="8" t="n"/>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="9" t="inlineStr">
         <is>
           <t>Alarms Guide, Redis VPC, $platform Refactor, SNS KMS &amp; Alarm Panels</t>
         </is>
       </c>
-      <c r="D68" s="9" t="inlineStr">
+      <c r="D106" s="9" t="inlineStr">
         <is>
           <t>- Documented VPC datasource requirements and updated OpenSearch endpoint references.
 - Added Redis plugin placeholder panels noting VPC dependency for full connectivity.
@@ -2328,20 +2840,34 @@
 - Created comprehensive alarms and notifications guide; updated notification email to bbhagat@citco.com.</t>
         </is>
       </c>
-      <c r="E68" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F68" s="8" t="n"/>
-    </row>
-    <row r="69" ht="143" customHeight="1">
-      <c r="A69" s="8" t="n"/>
-      <c r="B69" s="8" t="n"/>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="E106" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" s="8" t="n"/>
+    </row>
+    <row r="107" ht="143" customHeight="1">
+      <c r="A107" s="8" t="n"/>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>Alarms Guide, Redis VPC, $platform Refactor, SNS KMS &amp; Alarm Panels</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="inlineStr"/>
+      <c r="E107" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" s="8" t="n"/>
+    </row>
+    <row r="108" ht="143" customHeight="1">
+      <c r="A108" s="8" t="n"/>
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="9" t="inlineStr">
         <is>
           <t>EventBridge + Lambda Alarm Panels &amp; Decision Docs</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
+      <c r="D108" s="9" t="inlineStr">
         <is>
           <t>- Documented alarm dashboard panel implementation options — EventBridge vs Scheduled Lambda.
 - Documented decision to proceed with Option A (EventBridge + Lambda) for real-time alarm panel updates.
@@ -2350,38 +2876,38 @@
 - Added table panel transformations and alarm dimension fields for richer data display.</t>
         </is>
       </c>
-      <c r="E69" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F69" s="8" t="n"/>
-    </row>
-    <row r="70" ht="143" customHeight="1">
-      <c r="A70" s="8" t="n"/>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="9" t="inlineStr">
+      <c r="E108" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" s="8" t="n"/>
+    </row>
+    <row r="109" ht="143" customHeight="1">
+      <c r="A109" s="8" t="n"/>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="9" t="inlineStr">
         <is>
           <t>ia_common_utility: Bitbucket Pipelines CI/CD Setup</t>
         </is>
       </c>
-      <c r="D70" s="9" t="inlineStr">
+      <c r="D109" s="9" t="inlineStr">
         <is>
           <t>- Added Bitbucket Pipelines CI/CD configuration and environment example file to ia_common_utility repo.</t>
         </is>
       </c>
-      <c r="E70" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F70" s="8" t="n"/>
-    </row>
-    <row r="71" ht="143" customHeight="1">
-      <c r="A71" s="8" t="n"/>
-      <c r="B71" s="8" t="n"/>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="E109" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" s="8" t="n"/>
+    </row>
+    <row r="110" ht="143" customHeight="1">
+      <c r="A110" s="8" t="n"/>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="9" t="inlineStr">
         <is>
           <t>Alarm Panels, Scheduled Lambda, Grafana Alert Provisioning &amp; LCD Barga</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D110" s="9" t="inlineStr">
         <is>
           <t>- Replaced state-timeline panel with retro LCD bar gauge for a more compact alarm state view.
 - Added scheduled Lambda with dynamic SQS alarms and panel improvements to the alerts row.
@@ -2393,20 +2919,34 @@
 - Removed filterFieldsByName from bargauge panel that was causing NO DATA.</t>
         </is>
       </c>
-      <c r="E71" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F71" s="8" t="n"/>
-    </row>
-    <row r="72" ht="143" customHeight="1">
-      <c r="A72" s="11" t="n"/>
-      <c r="B72" s="11" t="n"/>
-      <c r="C72" s="24" t="inlineStr">
+      <c r="E110" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" s="8" t="n"/>
+    </row>
+    <row r="111" ht="143" customHeight="1">
+      <c r="A111" s="8" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>Alarm Panels, Scheduled Lambda, Grafana Alert Provisioning &amp; LCD Barga</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="inlineStr"/>
+      <c r="E111" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F111" s="8" t="n"/>
+    </row>
+    <row r="112" ht="143" customHeight="1">
+      <c r="A112" s="11" t="n"/>
+      <c r="B112" s="11" t="n"/>
+      <c r="C112" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D72" s="25" t="inlineStr">
+      <c r="D112" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (10 meetings, 2.5h):
 - Daily Standup (30 min)
@@ -2421,28 +2961,28 @@
 - Innovation IT - AWS Centralized Dashboard Planning (30 min)</t>
         </is>
       </c>
-      <c r="E72" s="26" t="n">
+      <c r="E112" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F72" s="11" t="n"/>
-    </row>
-    <row r="73" ht="143" customHeight="1">
-      <c r="A73" s="14" t="inlineStr">
+      <c r="F112" s="11" t="n"/>
+    </row>
+    <row r="113" ht="143" customHeight="1">
+      <c r="A113" s="14" t="inlineStr">
         <is>
           <t>Week 12</t>
         </is>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="B113" s="15" t="inlineStr">
         <is>
           <t>Jun 01 – Jun 05, 2026</t>
         </is>
       </c>
-      <c r="C73" s="27" t="inlineStr">
+      <c r="C113" s="27" t="inlineStr">
         <is>
           <t>RPA Production Support Shift</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>- Reviewed APAC handover log and opened the SD Portal queue for the start of Week 12 rotation.
 - Monitored UiPath Orchestrator for overnight queue items and job statuses across all active processes.
@@ -2458,70 +2998,196 @@
 - Auto Rec Download — CAPULA2 Config Update: Checked the CITCORECS_AUTO_REC_DOWNLOAD\SCRIPT UiPath share location. Created a backup of config.ini renamed to config-backup-2026-06-03.ini. Copied the file</t>
         </is>
       </c>
-      <c r="E73" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F73" s="14">
-        <f>SUM(E73:E75)</f>
+      <c r="E113" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F113" s="14">
+        <f>SUM(E113:E124)</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="143" customHeight="1">
-      <c r="A74" s="18" t="n"/>
-      <c r="B74" s="18" t="n"/>
-      <c r="C74" s="9" t="inlineStr">
+    <row r="114" ht="143" customHeight="1">
+      <c r="A114" s="18" t="n"/>
+      <c r="B114" s="18" t="n"/>
+      <c r="C114" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="inlineStr"/>
+      <c r="E114" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" s="18" t="n"/>
+    </row>
+    <row r="115" ht="143" customHeight="1">
+      <c r="A115" s="18" t="n"/>
+      <c r="B115" s="18" t="n"/>
+      <c r="C115" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="inlineStr"/>
+      <c r="E115" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" s="18" t="n"/>
+    </row>
+    <row r="116" ht="143" customHeight="1">
+      <c r="A116" s="18" t="n"/>
+      <c r="B116" s="18" t="n"/>
+      <c r="C116" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="inlineStr"/>
+      <c r="E116" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F116" s="18" t="n"/>
+    </row>
+    <row r="117" ht="143" customHeight="1">
+      <c r="A117" s="18" t="n"/>
+      <c r="B117" s="18" t="n"/>
+      <c r="C117" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr"/>
+      <c r="E117" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F117" s="18" t="n"/>
+    </row>
+    <row r="118" ht="143" customHeight="1">
+      <c r="A118" s="18" t="n"/>
+      <c r="B118" s="18" t="n"/>
+      <c r="C118" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="inlineStr"/>
+      <c r="E118" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F118" s="18" t="n"/>
+    </row>
+    <row r="119" ht="143" customHeight="1">
+      <c r="A119" s="18" t="n"/>
+      <c r="B119" s="18" t="n"/>
+      <c r="C119" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="inlineStr"/>
+      <c r="E119" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F119" s="18" t="n"/>
+    </row>
+    <row r="120" ht="143" customHeight="1">
+      <c r="A120" s="18" t="n"/>
+      <c r="B120" s="18" t="n"/>
+      <c r="C120" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="inlineStr"/>
+      <c r="E120" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F120" s="18" t="n"/>
+    </row>
+    <row r="121" ht="143" customHeight="1">
+      <c r="A121" s="18" t="n"/>
+      <c r="B121" s="18" t="n"/>
+      <c r="C121" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="inlineStr"/>
+      <c r="E121" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F121" s="18" t="n"/>
+    </row>
+    <row r="122" ht="143" customHeight="1">
+      <c r="A122" s="18" t="n"/>
+      <c r="B122" s="18" t="n"/>
+      <c r="C122" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="inlineStr"/>
+      <c r="E122" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F122" s="18" t="n"/>
+    </row>
+    <row r="123" ht="143" customHeight="1">
+      <c r="A123" s="18" t="n"/>
+      <c r="B123" s="18" t="n"/>
+      <c r="C123" s="9" t="inlineStr">
         <is>
           <t>Alarm Bargauge Deduplication</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>- Fixed alarm state history deduplication in the Grafana bargauge panel by applying a merge transformation.
 - Simplified the bargauge panel by removing filter and merge transformations, switching to a clean GROUP BY AlarmName only query.</t>
         </is>
       </c>
-      <c r="E74" s="10" t="n">
+      <c r="E123" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F74" s="18" t="n"/>
-    </row>
-    <row r="75" ht="143" customHeight="1">
-      <c r="A75" s="21" t="n"/>
-      <c r="B75" s="21" t="n"/>
-      <c r="C75" s="12" t="inlineStr">
+      <c r="F123" s="18" t="n"/>
+    </row>
+    <row r="124" ht="143" customHeight="1">
+      <c r="A124" s="21" t="n"/>
+      <c r="B124" s="21" t="n"/>
+      <c r="C124" s="12" t="inlineStr">
         <is>
           <t>Alarm Panel</t>
         </is>
       </c>
-      <c r="D75" s="12" t="inlineStr">
+      <c r="D124" s="12" t="inlineStr">
         <is>
           <t>- Fixed duplicate alarms in the bargauge panel by correcting the GROUP BY clause and refining the regex pattern.
 - Added AlarmStateEncoded metric to support the LCD bargauge panel for visual alarm state representation.
 - Replaced the bargauge panel with a state-timeline panel for alarm history — provides a cleaner time-based view of alarm state changes.</t>
         </is>
       </c>
-      <c r="E75" s="13" t="n">
+      <c r="E124" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F75" s="21" t="n"/>
-    </row>
-    <row r="76" ht="143" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
+      <c r="F124" s="21" t="n"/>
+    </row>
+    <row r="125" ht="143" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>Week 13</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B125" s="5" t="inlineStr">
         <is>
           <t>Jun 08 – Jun 12, 2026</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>CAIS Deadline SMBAuthenticationError Hotfix</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
+      <c r="D125" s="6" t="inlineStr">
         <is>
           <t>- Fixed UCM credential validation by adding checks at startup and before SMB connections to catch SpnegoError authentication failures early — root cause of the CAIS Deadline filing failure.
 - Added a guard to prevent empty deadline_ids from generating an invalid SQL IN() clause.
@@ -2533,23 +3199,37 @@
 - Fixed email_function tests by mocking the constants module before import to avoid side effects.</t>
         </is>
       </c>
-      <c r="E76" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F76" s="4">
-        <f>SUM(E76:E82)</f>
+      <c r="E125" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F125" s="4">
+        <f>SUM(E125:E135)</f>
         <v/>
       </c>
     </row>
-    <row r="77" ht="143" customHeight="1">
-      <c r="A77" s="8" t="n"/>
-      <c r="B77" s="8" t="n"/>
-      <c r="C77" s="9" t="inlineStr">
+    <row r="126" ht="143" customHeight="1">
+      <c r="A126" s="8" t="n"/>
+      <c r="B126" s="8" t="n"/>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>CAIS Deadline SMBAuthenticationError Hotfix</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="inlineStr"/>
+      <c r="E126" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F126" s="8" t="n"/>
+    </row>
+    <row r="127" ht="143" customHeight="1">
+      <c r="A127" s="8" t="n"/>
+      <c r="B127" s="8" t="n"/>
+      <c r="C127" s="9" t="inlineStr">
         <is>
           <t>EC2 Monitoring Row &amp; Instance Mapper Lambda</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr">
+      <c r="D127" s="9" t="inlineStr">
         <is>
           <t>- Added new EC2 monitoring row with health and performance overview panels.
 - Corrected EC2 row position — placed before ECS Infrastructure for logical ordering.
@@ -2561,39 +3241,67 @@
 - Bumped ProvisionerVersion after deploying EC2 monitoring changes.</t>
         </is>
       </c>
-      <c r="E77" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F77" s="8" t="n"/>
-    </row>
-    <row r="78" ht="143" customHeight="1">
-      <c r="A78" s="8" t="n"/>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="E127" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" s="8" t="n"/>
+    </row>
+    <row r="128" ht="143" customHeight="1">
+      <c r="A128" s="8" t="n"/>
+      <c r="B128" s="8" t="n"/>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>EC2 Monitoring Row &amp; Instance Mapper Lambda</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="inlineStr"/>
+      <c r="E128" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F128" s="8" t="n"/>
+    </row>
+    <row r="129" ht="143" customHeight="1">
+      <c r="A129" s="8" t="n"/>
+      <c r="B129" s="8" t="n"/>
+      <c r="C129" s="9" t="inlineStr">
         <is>
           <t>Health Row Split &amp; CFN S3 Deploy Fix</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
+      <c r="D129" s="9" t="inlineStr">
         <is>
           <t>- Refactored row_01_health by splitting it into individual per-panel files for better maintainability and modularity, consistent with the pattern used in other rows.
 - Fixed CloudFormation template deployment by uploading templates via S3 to work around the 51,200-byte inline template size limit.</t>
         </is>
       </c>
-      <c r="E78" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F78" s="8" t="n"/>
-    </row>
-    <row r="79" ht="143" customHeight="1">
-      <c r="A79" s="8" t="n"/>
-      <c r="B79" s="8" t="n"/>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="E129" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F129" s="8" t="n"/>
+    </row>
+    <row r="130" ht="143" customHeight="1">
+      <c r="A130" s="8" t="n"/>
+      <c r="B130" s="8" t="n"/>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>Health Row Split &amp; CFN S3 Deploy Fix</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="inlineStr"/>
+      <c r="E130" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F130" s="8" t="n"/>
+    </row>
+    <row r="131" ht="143" customHeight="1">
+      <c r="A131" s="8" t="n"/>
+      <c r="B131" s="8" t="n"/>
+      <c r="C131" s="9" t="inlineStr">
         <is>
           <t>Lambda/SQS SCHEMA SQL, Tooltip &amp; Docs</t>
         </is>
       </c>
-      <c r="D79" s="9" t="inlineStr">
+      <c r="D131" s="9" t="inlineStr">
         <is>
           <t>- Updated e2e alarm tests to match the actual alarms.yaml file containing 18 alarms.
 - Fixed the Lambda row to use SCHEMA SQL syntax across all 37 meridian functions.
@@ -2604,20 +3312,20 @@
 - Fixed the SQS row to use SCHEMA SQL syntax and added Row 3 SQS panel explanations.</t>
         </is>
       </c>
-      <c r="E79" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F79" s="8" t="n"/>
-    </row>
-    <row r="80" ht="143" customHeight="1">
-      <c r="A80" s="8" t="n"/>
-      <c r="B80" s="8" t="n"/>
-      <c r="C80" s="9" t="inlineStr">
+      <c r="E131" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F131" s="8" t="n"/>
+    </row>
+    <row r="132" ht="143" customHeight="1">
+      <c r="A132" s="8" t="n"/>
+      <c r="B132" s="8" t="n"/>
+      <c r="C132" s="9" t="inlineStr">
         <is>
           <t>ia-it-sre-infrastructure-inventory Initial Scaffold</t>
         </is>
       </c>
-      <c r="D80" s="9" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
         <is>
           <t>- Created new ia-it-sre-infrastructure-inventory repository — first commits for IISS-507.
 - Built initial Flask async API for resource inventory with async route handlers.
@@ -2625,38 +3333,52 @@
 - Added Kiro steering files, project documentation, and pre-commit configuration.</t>
         </is>
       </c>
-      <c r="E80" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F80" s="8" t="n"/>
-    </row>
-    <row r="81" ht="143" customHeight="1">
-      <c r="A81" s="8" t="n"/>
-      <c r="B81" s="8" t="n"/>
-      <c r="C81" s="9" t="inlineStr">
+      <c r="E132" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F132" s="8" t="n"/>
+    </row>
+    <row r="133" ht="143" customHeight="1">
+      <c r="A133" s="8" t="n"/>
+      <c r="B133" s="8" t="n"/>
+      <c r="C133" s="9" t="inlineStr">
         <is>
           <t>SQS Monitoring Dashboards &amp; Platform Filter</t>
         </is>
       </c>
-      <c r="D81" s="9" t="inlineStr">
+      <c r="D133" s="9" t="inlineStr">
         <is>
           <t>- Added SQS monitoring dashboards to ia-resources-monitoring with platform filter support across all resource types, extending CloudWatch dashboard coverage to SQS queues.</t>
         </is>
       </c>
-      <c r="E81" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F81" s="8" t="n"/>
-    </row>
-    <row r="82" ht="143" customHeight="1">
-      <c r="A82" s="11" t="n"/>
-      <c r="B82" s="11" t="n"/>
-      <c r="C82" s="24" t="inlineStr">
+      <c r="E133" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" s="8" t="n"/>
+    </row>
+    <row r="134" ht="143" customHeight="1">
+      <c r="A134" s="8" t="n"/>
+      <c r="B134" s="8" t="n"/>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>SQS Monitoring Dashboards &amp; Platform Filter</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="inlineStr"/>
+      <c r="E134" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F134" s="8" t="n"/>
+    </row>
+    <row r="135" ht="143" customHeight="1">
+      <c r="A135" s="11" t="n"/>
+      <c r="B135" s="11" t="n"/>
+      <c r="C135" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D82" s="25" t="inlineStr">
+      <c r="D135" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (8 meetings, 2.5h):
 - Innovation IT - AWS Centralized Dashboard Planning (30 min)
@@ -2669,28 +3391,28 @@
 - Daily Standup - Innovation IT (30 min)</t>
         </is>
       </c>
-      <c r="E82" s="26" t="n">
+      <c r="E135" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F82" s="11" t="n"/>
-    </row>
-    <row r="83" ht="143" customHeight="1">
-      <c r="A83" s="14" t="inlineStr">
+      <c r="F135" s="11" t="n"/>
+    </row>
+    <row r="136" ht="143" customHeight="1">
+      <c r="A136" s="14" t="inlineStr">
         <is>
           <t>Week 14</t>
         </is>
       </c>
-      <c r="B83" s="15" t="inlineStr">
+      <c r="B136" s="15" t="inlineStr">
         <is>
           <t>Jun 15 – Jun 19, 2026</t>
         </is>
       </c>
-      <c r="C83" s="16" t="inlineStr">
+      <c r="C136" s="16" t="inlineStr">
         <is>
           <t>Resource Tables, Row Layout Restructure &amp; Drill-Down Links</t>
         </is>
       </c>
-      <c r="D83" s="16" t="inlineStr">
+      <c r="D136" s="16" t="inlineStr">
         <is>
           <t>- Added missing panel documentation for rows 7-10 and numbered inventory files by row for easier navigation.
 - Added data links from Row 1 health panels to Row 2 performance panels for drill-down navigation.
@@ -2702,43 +3424,43 @@
 - Removed sortBy from SQS tables and used max reducer for the DLQ table.</t>
         </is>
       </c>
-      <c r="E83" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F83" s="14">
-        <f>SUM(E83:E92)</f>
+      <c r="E136" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F136" s="14">
+        <f>SUM(E136:E148)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="143" customHeight="1">
-      <c r="A84" s="18" t="n"/>
-      <c r="B84" s="18" t="n"/>
-      <c r="C84" s="19" t="inlineStr">
+    <row r="137" ht="143" customHeight="1">
+      <c r="A137" s="18" t="n"/>
+      <c r="B137" s="18" t="n"/>
+      <c r="C137" s="19" t="inlineStr">
         <is>
           <t>Inventory API Coroutine Fix &amp; All Discoverers</t>
         </is>
       </c>
-      <c r="D84" s="19" t="inlineStr">
+      <c r="D137" s="19" t="inlineStr">
         <is>
           <t>- Fixed coroutine serialization issue in the inventory API.
 - Implemented all resource discoverers.
 - Added profile and metrics support to the inventory API.</t>
         </is>
       </c>
-      <c r="E84" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F84" s="18" t="n"/>
-    </row>
-    <row r="85" ht="143" customHeight="1">
-      <c r="A85" s="18" t="n"/>
-      <c r="B85" s="18" t="n"/>
-      <c r="C85" s="19" t="inlineStr">
+      <c r="E137" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F137" s="18" t="n"/>
+    </row>
+    <row r="138" ht="143" customHeight="1">
+      <c r="A138" s="18" t="n"/>
+      <c r="B138" s="18" t="n"/>
+      <c r="C138" s="19" t="inlineStr">
         <is>
           <t>Deep-Links, Legend Fixes, Rows 10-13 Restructure &amp; Performance Row</t>
         </is>
       </c>
-      <c r="D85" s="19" t="inlineStr">
+      <c r="D138" s="19" t="inlineStr">
         <is>
           <t>- Fixed all ECS APIs panels to display clean target group names in legends.
 - Fixed request throughput, HTTP 4xx/5xx, and p50/p95/p99 panels to show clean ALB and target group names.
@@ -2750,20 +3472,34 @@
 - Added EC2 panels with deep-links and moved EC2 row before ECS; documented EC2 memory limitations.</t>
         </is>
       </c>
-      <c r="E85" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F85" s="18" t="n"/>
-    </row>
-    <row r="86" ht="143" customHeight="1">
-      <c r="A86" s="18" t="n"/>
-      <c r="B86" s="18" t="n"/>
-      <c r="C86" s="19" t="inlineStr">
+      <c r="E138" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F138" s="18" t="n"/>
+    </row>
+    <row r="139" ht="143" customHeight="1">
+      <c r="A139" s="18" t="n"/>
+      <c r="B139" s="18" t="n"/>
+      <c r="C139" s="19" t="inlineStr">
+        <is>
+          <t>Deep-Links, Legend Fixes, Rows 10-13 Restructure &amp; Performance Row</t>
+        </is>
+      </c>
+      <c r="D139" s="19" t="inlineStr"/>
+      <c r="E139" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F139" s="18" t="n"/>
+    </row>
+    <row r="140" ht="143" customHeight="1">
+      <c r="A140" s="18" t="n"/>
+      <c r="B140" s="18" t="n"/>
+      <c r="C140" s="19" t="inlineStr">
         <is>
           <t>Redis Restructure, OpenSearch Status Tables, Health Row Deep-Links &amp; P</t>
         </is>
       </c>
-      <c r="D86" s="19" t="inlineStr">
+      <c r="D140" s="19" t="inlineStr">
         <is>
           <t>- Reorganised Row 11 Redis into 12 panels across 3 visual rows; replaced Redis CPU bargauge in Performance row with Memory Usage and Cache Hit Rate using inverted thresholds for worst-first display — ProvisionerVersion 698
 - Updated panel documentation for Redis row and performance row including AVG vs MAX rationale.
@@ -2775,20 +3511,34 @@
 - Fixed RDS health panel to collapse multiple DB instances into a single MAX value via two-step reduce transformation.</t>
         </is>
       </c>
-      <c r="E86" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F86" s="18" t="n"/>
-    </row>
-    <row r="87" ht="143" customHeight="1">
-      <c r="A87" s="18" t="n"/>
-      <c r="B87" s="18" t="n"/>
-      <c r="C87" s="19" t="inlineStr">
+      <c r="E140" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F140" s="18" t="n"/>
+    </row>
+    <row r="141" ht="143" customHeight="1">
+      <c r="A141" s="18" t="n"/>
+      <c r="B141" s="18" t="n"/>
+      <c r="C141" s="19" t="inlineStr">
+        <is>
+          <t>Redis Restructure, OpenSearch Status Tables, Health Row Deep-Links &amp; P</t>
+        </is>
+      </c>
+      <c r="D141" s="19" t="inlineStr"/>
+      <c r="E141" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F141" s="18" t="n"/>
+    </row>
+    <row r="142" ht="143" customHeight="1">
+      <c r="A142" s="18" t="n"/>
+      <c r="B142" s="18" t="n"/>
+      <c r="C142" s="19" t="inlineStr">
         <is>
           <t>Lambda/SQS/EC2 Variable Filters, Tested &amp; Reverted Approaches</t>
         </is>
       </c>
-      <c r="D87" s="19" t="inlineStr">
+      <c r="D142" s="19" t="inlineStr">
         <is>
           <t>- Added lambda_function and sqs_queue dashboard variables for cross-panel filtering.
 - Documented limitations of table filters vs dashboard variables for future reference.
@@ -2796,77 +3546,77 @@
 - Tested and reverted CloudWatch label override experiment — confirmed broken with Metric Insights SQL mode; documented as known limitation.</t>
         </is>
       </c>
-      <c r="E87" s="20" t="n">
+      <c r="E142" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F87" s="18" t="n"/>
-    </row>
-    <row r="88" ht="143" customHeight="1">
-      <c r="A88" s="18" t="n"/>
-      <c r="B88" s="18" t="n"/>
-      <c r="C88" s="19" t="inlineStr">
+      <c r="F142" s="18" t="n"/>
+    </row>
+    <row r="143" ht="143" customHeight="1">
+      <c r="A143" s="18" t="n"/>
+      <c r="B143" s="18" t="n"/>
+      <c r="C143" s="19" t="inlineStr">
         <is>
           <t>ECS Service &amp; Target Group Variables</t>
         </is>
       </c>
-      <c r="D88" s="19" t="inlineStr">
+      <c r="D143" s="19" t="inlineStr">
         <is>
           <t>- Added ecs_service and ecs_target_group variables for cross-panel filtering across ECS rows.
 - Fixed ECS Infra legend format to match resource table and applied anchored regex filter.
 - Fixed ECS APIs target group names in dropdown and cleaned p50/p95/p99 legends.</t>
         </is>
       </c>
-      <c r="E88" s="20" t="n">
+      <c r="E143" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F88" s="18" t="n"/>
-    </row>
-    <row r="89" ht="143" customHeight="1">
-      <c r="A89" s="18" t="n"/>
-      <c r="B89" s="18" t="n"/>
-      <c r="C89" s="19" t="inlineStr">
+      <c r="F143" s="18" t="n"/>
+    </row>
+    <row r="144" ht="143" customHeight="1">
+      <c r="A144" s="18" t="n"/>
+      <c r="B144" s="18" t="n"/>
+      <c r="C144" s="19" t="inlineStr">
         <is>
           <t>MSK Consumer Group Variable</t>
         </is>
       </c>
-      <c r="D89" s="19" t="inlineStr">
+      <c r="D144" s="19" t="inlineStr">
         <is>
           <t>- Added msk_consumer_group variable for filtering consumer lag data in the MSK row — key SLI from the April 17 Meridian Incident.</t>
         </is>
       </c>
-      <c r="E89" s="20" t="n">
+      <c r="E144" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F89" s="18" t="n"/>
-    </row>
-    <row r="90" ht="143" customHeight="1">
-      <c r="A90" s="18" t="n"/>
-      <c r="B90" s="18" t="n"/>
-      <c r="C90" s="19" t="inlineStr">
+      <c r="F144" s="18" t="n"/>
+    </row>
+    <row r="145" ht="143" customHeight="1">
+      <c r="A145" s="18" t="n"/>
+      <c r="B145" s="18" t="n"/>
+      <c r="C145" s="19" t="inlineStr">
         <is>
           <t>DB Instance Variables (DocumentDB, RDS, Redis, Neptune, OpenSearch)</t>
         </is>
       </c>
-      <c r="D90" s="19" t="inlineStr">
+      <c r="D145" s="19" t="inlineStr">
         <is>
           <t>- Added docdb_instance, rds_instance (with Aurora regex to exclude DocumentDB), redis_cluster, neptune_instance, and opensearch_domain dashboard variables — completing row-level filtering across all database service rows.
 - rds_instance variable uses Aurora regex pattern to correctly exclude DocumentDB instances from the RDS dropdown.</t>
         </is>
       </c>
-      <c r="E90" s="20" t="n">
+      <c r="E145" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F90" s="18" t="n"/>
-    </row>
-    <row r="91" ht="143" customHeight="1">
-      <c r="A91" s="18" t="n"/>
-      <c r="B91" s="18" t="n"/>
-      <c r="C91" s="19" t="inlineStr">
+      <c r="F145" s="18" t="n"/>
+    </row>
+    <row r="146" ht="143" customHeight="1">
+      <c r="A146" s="18" t="n"/>
+      <c r="B146" s="18" t="n"/>
+      <c r="C146" s="19" t="inlineStr">
         <is>
           <t>Performance Row SCHEMA SQL Migration, Freeable Memory Panels &amp; EC2 Var</t>
         </is>
       </c>
-      <c r="D91" s="19" t="inlineStr">
+      <c r="D146" s="19" t="inlineStr">
         <is>
           <t>- Migrated 6 legacy SQL panels to SCHEMA syntax; reduced all performance row bar gauges from top-10 to top-5 with names displayed above bars.
 - Fixed missing end-of-file newlines in 19 JSON panel files and applied ruff formatting cleanup.
@@ -2878,20 +3628,34 @@
 - Removed unused LambdaCodeBucket/Key CloudFormation parameters and renamed the ECS panel.</t>
         </is>
       </c>
-      <c r="E91" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F91" s="18" t="n"/>
-    </row>
-    <row r="92" ht="143" customHeight="1">
-      <c r="A92" s="21" t="n"/>
-      <c r="B92" s="21" t="n"/>
-      <c r="C92" s="24" t="inlineStr">
+      <c r="E146" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F146" s="18" t="n"/>
+    </row>
+    <row r="147" ht="143" customHeight="1">
+      <c r="A147" s="18" t="n"/>
+      <c r="B147" s="18" t="n"/>
+      <c r="C147" s="19" t="inlineStr">
+        <is>
+          <t>Performance Row SCHEMA SQL Migration, Freeable Memory Panels &amp; EC2 Var</t>
+        </is>
+      </c>
+      <c r="D147" s="19" t="inlineStr"/>
+      <c r="E147" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F147" s="18" t="n"/>
+    </row>
+    <row r="148" ht="143" customHeight="1">
+      <c r="A148" s="21" t="n"/>
+      <c r="B148" s="21" t="n"/>
+      <c r="C148" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D92" s="25" t="inlineStr">
+      <c r="D148" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (10 meetings, 2.5h):
 - Innovation IT - AWS Centralized Dashboard Planning (30 min)
@@ -2906,50 +3670,50 @@
 - Instrument Expiry - Support Exception Handling (30 min)</t>
         </is>
       </c>
-      <c r="E92" s="26" t="n">
+      <c r="E148" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F92" s="21" t="n"/>
-    </row>
-    <row r="93" ht="143" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="F148" s="21" t="n"/>
+    </row>
+    <row r="149" ht="143" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>Week 15</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B149" s="5" t="inlineStr">
         <is>
           <t>Jun 22 – Jun 26, 2026</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C149" s="6" t="inlineStr">
         <is>
           <t>EC2 Variable Filter &amp; Mapper Deploy</t>
         </is>
       </c>
-      <c r="D93" s="6" t="inlineStr">
+      <c r="D149" s="6" t="inlineStr">
         <is>
           <t>- Added EC2 variable filtering to EC2 health, performance, and resource table panels — shows only meridian-tagged instances.
 - Merged feature/IISS-487-link-panels into release, completing the deep-link and variable filtering feature set.</t>
         </is>
       </c>
-      <c r="E93" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F93" s="4">
-        <f>SUM(E93:E102)</f>
+      <c r="E149" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F149" s="4">
+        <f>SUM(E149:E159)</f>
         <v/>
       </c>
     </row>
-    <row r="94" ht="143" customHeight="1">
-      <c r="A94" s="8" t="n"/>
-      <c r="B94" s="8" t="n"/>
-      <c r="C94" s="9" t="inlineStr">
+    <row r="150" ht="143" customHeight="1">
+      <c r="A150" s="8" t="n"/>
+      <c r="B150" s="8" t="n"/>
+      <c r="C150" s="9" t="inlineStr">
         <is>
           <t>SQS Queue Mapper Lambda &amp; Panel Filtering</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
+      <c r="D150" s="9" t="inlineStr">
         <is>
           <t>- Fixed SQS panel filters to use case-insensitive regex — resolved issue where ia-bpo platform showed only 2 of 55 queues due to uppercase/lowercase mismatch.
 - Researched Infinity plugin as SQS integration approach — documented planning, connectivity options, and postmortem (abandoned due to unresolvable Go HTTP client timeout issue).
@@ -2961,20 +3725,20 @@
 - Moved EC2 and SQS mapper Lambdas to dedicated resource-mappers.yaml CFN stack.</t>
         </is>
       </c>
-      <c r="E94" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F94" s="8" t="n"/>
-    </row>
-    <row r="95" ht="143" customHeight="1">
-      <c r="A95" s="8" t="n"/>
-      <c r="B95" s="8" t="n"/>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="E150" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F150" s="8" t="n"/>
+    </row>
+    <row r="151" ht="143" customHeight="1">
+      <c r="A151" s="8" t="n"/>
+      <c r="B151" s="8" t="n"/>
+      <c r="C151" s="9" t="inlineStr">
         <is>
           <t>Lambda/MSK Mapper Lambdas, Idle State, Variable Filtering &amp; MSK Deep-L</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr">
+      <c r="D151" s="9" t="inlineStr">
         <is>
           <t>- Fixed health panels to show 'Idle' instead of 'No data' when no metrics are available; added noValue='Idle' to all SQS row panels for consistent empty-state display.
 - Built Lambda function mapper Lambda — discovers Lambda functions and updates the dashboard variable and panels accordingly.
@@ -2986,40 +3750,40 @@
 - Removed platform filter from MSK panels and fixed ARN-based deep-links using percent-encoding.</t>
         </is>
       </c>
-      <c r="E95" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F95" s="8" t="n"/>
-    </row>
-    <row r="96" ht="143" customHeight="1">
-      <c r="A96" s="8" t="n"/>
-      <c r="B96" s="8" t="n"/>
-      <c r="C96" s="9" t="inlineStr">
+      <c r="E151" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F151" s="8" t="n"/>
+    </row>
+    <row r="152" ht="143" customHeight="1">
+      <c r="A152" s="8" t="n"/>
+      <c r="B152" s="8" t="n"/>
+      <c r="C152" s="9" t="inlineStr">
         <is>
           <t>Inventory API Standardisation &amp; Bulk Tag Discovery</t>
         </is>
       </c>
-      <c r="D96" s="9" t="inlineStr">
+      <c r="D152" s="9" t="inlineStr">
         <is>
           <t>- Standardised inventory API resource response format and added a CLI entry point.
 - Migrated all discoverers to the Resource Groups Tagging API for bulk tag discovery.
 - Fixed per-resource tag checks with throttle handling to match the mapper Lambda pattern.</t>
         </is>
       </c>
-      <c r="E96" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F96" s="8" t="n"/>
-    </row>
-    <row r="97" ht="143" customHeight="1">
-      <c r="A97" s="8" t="n"/>
-      <c r="B97" s="8" t="n"/>
-      <c r="C97" s="9" t="inlineStr">
+      <c r="E152" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F152" s="8" t="n"/>
+    </row>
+    <row r="153" ht="143" customHeight="1">
+      <c r="A153" s="8" t="n"/>
+      <c r="B153" s="8" t="n"/>
+      <c r="C153" s="9" t="inlineStr">
         <is>
           <t>MSK Deep-Links Complete, Mapper Schedule, Consumer Lag Split &amp; Deploy</t>
         </is>
       </c>
-      <c r="D97" s="9" t="inlineStr">
+      <c r="D153" s="9" t="inlineStr">
         <is>
           <t>- Iterated on MSK cluster mapper schedule — tested 6-hour, 5-minute, and finally CloudTrail event-driven triggers for CreateCluster/DeleteCluster events; made schedule rate configurable via CFN parameter.
 - Added comprehensive resource mappers documentation covering all mapper Lambdas, deploy order, and known limitations.
@@ -3031,20 +3795,34 @@
 - Implemented Option B for MSK consumer lag deep-links — added ClusterArn as a third dimension to MSK mapper metrics, enabling chained variable for ARN resolution.</t>
         </is>
       </c>
-      <c r="E97" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F97" s="8" t="n"/>
-    </row>
-    <row r="98" ht="143" customHeight="1">
-      <c r="A98" s="8" t="n"/>
-      <c r="B98" s="8" t="n"/>
-      <c r="C98" s="9" t="inlineStr">
+      <c r="E153" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F153" s="8" t="n"/>
+    </row>
+    <row r="154" ht="143" customHeight="1">
+      <c r="A154" s="8" t="n"/>
+      <c r="B154" s="8" t="n"/>
+      <c r="C154" s="9" t="inlineStr">
+        <is>
+          <t>MSK Deep-Links Complete, Mapper Schedule, Consumer Lag Split &amp; Deploy</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="inlineStr"/>
+      <c r="E154" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F154" s="8" t="n"/>
+    </row>
+    <row r="155" ht="143" customHeight="1">
+      <c r="A155" s="8" t="n"/>
+      <c r="B155" s="8" t="n"/>
+      <c r="C155" s="9" t="inlineStr">
         <is>
           <t>6 Resource Mapper Lambdas, EC2 Row Restructure &amp; Deploy Script Fixes</t>
         </is>
       </c>
-      <c r="D98" s="9" t="inlineStr">
+      <c r="D155" s="9" t="inlineStr">
         <is>
           <t>- Added Broker CPU Max panel to MSK row — broker row now 4 panels at w=6 for consistent layout.
 - Created planning document for expanding resource mappers to ECS, DocDB, RDS, Redis, Neptune, and OpenSearch.
@@ -3056,38 +3834,38 @@
 - Fixed deploy script: proper exit codes, command logging, and UPDATE_IN_PROGRESS state detection.</t>
         </is>
       </c>
-      <c r="E98" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F98" s="8" t="n"/>
-    </row>
-    <row r="99" ht="143" customHeight="1">
-      <c r="A99" s="8" t="n"/>
-      <c r="B99" s="8" t="n"/>
-      <c r="C99" s="9" t="inlineStr">
+      <c r="E155" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F155" s="8" t="n"/>
+    </row>
+    <row r="156" ht="143" customHeight="1">
+      <c r="A156" s="8" t="n"/>
+      <c r="B156" s="8" t="n"/>
+      <c r="C156" s="9" t="inlineStr">
         <is>
           <t>Concurrent Tag Discovery</t>
         </is>
       </c>
-      <c r="D99" s="9" t="inlineStr">
+      <c r="D156" s="9" t="inlineStr">
         <is>
           <t>- Added concurrent tag discovery with 10 worker threads (client-per-thread pattern) to the inventory API for significantly improved performance on large fleets.</t>
         </is>
       </c>
-      <c r="E99" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F99" s="8" t="n"/>
-    </row>
-    <row r="100" ht="143" customHeight="1">
-      <c r="A100" s="8" t="n"/>
-      <c r="B100" s="8" t="n"/>
-      <c r="C100" s="9" t="inlineStr">
+      <c r="E156" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F156" s="8" t="n"/>
+    </row>
+    <row r="157" ht="143" customHeight="1">
+      <c r="A157" s="8" t="n"/>
+      <c r="B157" s="8" t="n"/>
+      <c r="C157" s="9" t="inlineStr">
         <is>
           <t>Lambda Deploy Fix, Row Structure Refactor, Health/Performance Overview</t>
         </is>
       </c>
-      <c r="D100" s="9" t="inlineStr">
+      <c r="D157" s="9" t="inlineStr">
         <is>
           <t>- Fixed critical Lambda code deployment gap — introduced SHA256 content-hash S3 keys so CloudFormation detects actual code changes instead of silently skipping unchanged Lambdas.
 - Removed redis-datasource plugin references from dashboard — VPC connectivity no longer needed.
@@ -3099,20 +3877,20 @@
 - Merged row structure refactor into release and reordered dashboard variables to match row order.</t>
         </is>
       </c>
-      <c r="E100" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F100" s="8" t="n"/>
-    </row>
-    <row r="101" ht="143" customHeight="1">
-      <c r="A101" s="8" t="n"/>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="9" t="inlineStr">
+      <c r="E157" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F157" s="8" t="n"/>
+    </row>
+    <row r="158" ht="143" customHeight="1">
+      <c r="A158" s="8" t="n"/>
+      <c r="B158" s="8" t="n"/>
+      <c r="C158" s="9" t="inlineStr">
         <is>
           <t>127 Unit Tests, CLI Entry Point, State Tracking &amp; Docs</t>
         </is>
       </c>
-      <c r="D101" s="9" t="inlineStr">
+      <c r="D158" s="9" t="inlineStr">
         <is>
           <t>- Renumbered inventory discoverers and renamed service types to align with Grafana dashboard row naming.
 - Added CLI entry point with --env flag and automatic corporate certificate check on startup.
@@ -3123,20 +3901,20 @@
 - Added state/status tracking to MSK and OpenSearch discoverers for richer resource information.</t>
         </is>
       </c>
-      <c r="E101" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F101" s="8" t="n"/>
-    </row>
-    <row r="102" ht="143" customHeight="1">
-      <c r="A102" s="11" t="n"/>
-      <c r="B102" s="11" t="n"/>
-      <c r="C102" s="24" t="inlineStr">
+      <c r="E158" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F158" s="8" t="n"/>
+    </row>
+    <row r="159" ht="143" customHeight="1">
+      <c r="A159" s="11" t="n"/>
+      <c r="B159" s="11" t="n"/>
+      <c r="C159" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D102" s="25" t="inlineStr">
+      <c r="D159" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (11 meetings, 2.5h):
 - Innovation IT - AWS Centralized Dashboard Planning (30 min)
@@ -3152,28 +3930,28 @@
 - Daily Standup - Innovation IT (30 min)</t>
         </is>
       </c>
-      <c r="E102" s="26" t="n">
+      <c r="E159" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F102" s="11" t="n"/>
-    </row>
-    <row r="103" ht="143" customHeight="1">
-      <c r="A103" s="14" t="inlineStr">
+      <c r="F159" s="11" t="n"/>
+    </row>
+    <row r="160" ht="143" customHeight="1">
+      <c r="A160" s="14" t="inlineStr">
         <is>
           <t>Week 16</t>
         </is>
       </c>
-      <c r="B103" s="15" t="inlineStr">
+      <c r="B160" s="15" t="inlineStr">
         <is>
           <t>Jun 29 – Jul 03, 2026</t>
         </is>
       </c>
-      <c r="C103" s="27" t="inlineStr">
+      <c r="C160" s="27" t="inlineStr">
         <is>
           <t>RPA Production Support Shift</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="D160" s="6" t="inlineStr">
         <is>
           <t>- Reviewed APAC handover log and opened the SD Portal queue for the start of Week 16 rotation.
 - SD Ticket #15103842 — Corporate Actions new client onboarding (Leeside): Checked Confluence page for Corporate Actions Processes — confirmed process migrated to UiPath. Checked UiPath Cloud CoE/HedgeF
@@ -3189,23 +3967,149 @@
 - Reviewed APAC handover log; lighter queue expected due to Canada Day public holiday.</t>
         </is>
       </c>
-      <c r="E103" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F103" s="14">
-        <f>SUM(E103:E104)</f>
+      <c r="E160" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F160" s="14">
+        <f>SUM(E160:E170)</f>
         <v/>
       </c>
     </row>
-    <row r="104" ht="143" customHeight="1">
-      <c r="A104" s="21" t="n"/>
-      <c r="B104" s="21" t="n"/>
-      <c r="C104" s="12" t="inlineStr">
+    <row r="161" ht="143" customHeight="1">
+      <c r="A161" s="18" t="n"/>
+      <c r="B161" s="18" t="n"/>
+      <c r="C161" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="inlineStr"/>
+      <c r="E161" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F161" s="18" t="n"/>
+    </row>
+    <row r="162" ht="143" customHeight="1">
+      <c r="A162" s="18" t="n"/>
+      <c r="B162" s="18" t="n"/>
+      <c r="C162" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="inlineStr"/>
+      <c r="E162" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F162" s="18" t="n"/>
+    </row>
+    <row r="163" ht="143" customHeight="1">
+      <c r="A163" s="18" t="n"/>
+      <c r="B163" s="18" t="n"/>
+      <c r="C163" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="inlineStr"/>
+      <c r="E163" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F163" s="18" t="n"/>
+    </row>
+    <row r="164" ht="143" customHeight="1">
+      <c r="A164" s="18" t="n"/>
+      <c r="B164" s="18" t="n"/>
+      <c r="C164" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="inlineStr"/>
+      <c r="E164" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F164" s="18" t="n"/>
+    </row>
+    <row r="165" ht="143" customHeight="1">
+      <c r="A165" s="18" t="n"/>
+      <c r="B165" s="18" t="n"/>
+      <c r="C165" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="inlineStr"/>
+      <c r="E165" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F165" s="18" t="n"/>
+    </row>
+    <row r="166" ht="143" customHeight="1">
+      <c r="A166" s="18" t="n"/>
+      <c r="B166" s="18" t="n"/>
+      <c r="C166" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="inlineStr"/>
+      <c r="E166" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F166" s="18" t="n"/>
+    </row>
+    <row r="167" ht="143" customHeight="1">
+      <c r="A167" s="18" t="n"/>
+      <c r="B167" s="18" t="n"/>
+      <c r="C167" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="inlineStr"/>
+      <c r="E167" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F167" s="18" t="n"/>
+    </row>
+    <row r="168" ht="143" customHeight="1">
+      <c r="A168" s="18" t="n"/>
+      <c r="B168" s="18" t="n"/>
+      <c r="C168" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="inlineStr"/>
+      <c r="E168" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F168" s="18" t="n"/>
+    </row>
+    <row r="169" ht="143" customHeight="1">
+      <c r="A169" s="18" t="n"/>
+      <c r="B169" s="18" t="n"/>
+      <c r="C169" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="inlineStr"/>
+      <c r="E169" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F169" s="18" t="n"/>
+    </row>
+    <row r="170" ht="143" customHeight="1">
+      <c r="A170" s="21" t="n"/>
+      <c r="B170" s="21" t="n"/>
+      <c r="C170" s="12" t="inlineStr">
         <is>
           <t>Health Overview Optimisation, MSK Consumer Lag &amp; Mapper Rename</t>
         </is>
       </c>
-      <c r="D104" s="12" t="inlineStr">
+      <c r="D170" s="12" t="inlineStr">
         <is>
           <t>- Refactored mapper Lambda folders with row number prefixes for consistent naming alignment with the dashboard.
 - Removed MonitoringBucket from CloudFormation (now managed externally) and fixed mapper-to-parameter name mappings.
@@ -3217,89 +4121,89 @@
 - Added consumer lag by topic panel with GROUP BY Cluster Name + Topic and cluster/topic legends.</t>
         </is>
       </c>
-      <c r="E104" s="13" t="n">
+      <c r="E170" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F104" s="21" t="n"/>
-    </row>
-    <row r="105" ht="143" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="F170" s="21" t="n"/>
+    </row>
+    <row r="171" ht="143" customHeight="1">
+      <c r="A171" s="4" t="inlineStr">
         <is>
           <t>Week 17</t>
         </is>
       </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="B171" s="5" t="inlineStr">
         <is>
           <t>Jul 06 – Jul 10, 2026</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="C171" s="6" t="inlineStr">
         <is>
           <t>MSK Health Stat Alignment</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D171" s="6" t="inlineStr">
         <is>
           <t>- Improved MSK health stat panel to GROUP BY Cluster Name + Consumer Group with msk_cluster:pipe filtering.
 - Aligned MSK performance panel to use the same GROUP BY and filter for consistency.</t>
         </is>
       </c>
-      <c r="E105" s="7" t="n">
+      <c r="E171" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F105" s="4">
-        <f>SUM(E105:E117)</f>
+      <c r="F171" s="4">
+        <f>SUM(E171:E184)</f>
         <v/>
       </c>
     </row>
-    <row r="106" ht="143" customHeight="1">
-      <c r="A106" s="8" t="n"/>
-      <c r="B106" s="8" t="n"/>
-      <c r="C106" s="9" t="inlineStr">
+    <row r="172" ht="143" customHeight="1">
+      <c r="A172" s="8" t="n"/>
+      <c r="B172" s="8" t="n"/>
+      <c r="C172" s="9" t="inlineStr">
         <is>
           <t>ECR Monitoring Row</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D172" s="9" t="inlineStr">
         <is>
           <t>- Added complete ECR monitoring row — mapper Lambda, resource table panels, dashboard variables, and deep-links.
 - Added X-Ray tracing implementation estimate document.</t>
         </is>
       </c>
-      <c r="E106" s="10" t="n">
+      <c r="E172" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F106" s="8" t="n"/>
-    </row>
-    <row r="107" ht="143" customHeight="1">
-      <c r="A107" s="8" t="n"/>
-      <c r="B107" s="8" t="n"/>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="F172" s="8" t="n"/>
+    </row>
+    <row r="173" ht="143" customHeight="1">
+      <c r="A173" s="8" t="n"/>
+      <c r="B173" s="8" t="n"/>
+      <c r="C173" s="9" t="inlineStr">
         <is>
           <t>EKS Monitoring Row</t>
         </is>
       </c>
-      <c r="D107" s="9" t="inlineStr">
+      <c r="D173" s="9" t="inlineStr">
         <is>
           <t>- Added complete EKS monitoring row — mapper Lambda, real metric panels, dashboard variable, and deep-links.
 - Removed unused msk_consumer_group variable and updated related documentation.
 - Fixed MSK performance panel link to use correct AWS Console URL format.</t>
         </is>
       </c>
-      <c r="E107" s="10" t="n">
+      <c r="E173" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F107" s="8" t="n"/>
-    </row>
-    <row r="108" ht="143" customHeight="1">
-      <c r="A108" s="8" t="n"/>
-      <c r="B108" s="8" t="n"/>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="F173" s="8" t="n"/>
+    </row>
+    <row r="174" ht="143" customHeight="1">
+      <c r="A174" s="8" t="n"/>
+      <c r="B174" s="8" t="n"/>
+      <c r="C174" s="9" t="inlineStr">
         <is>
           <t>S3 Cache Layer, CI/CD Pipeline, Naming Convention &amp; SSL Fix</t>
         </is>
       </c>
-      <c r="D108" s="9" t="inlineStr">
+      <c r="D174" s="9" t="inlineStr">
         <is>
           <t>- Merged S3 cache layer, CI/CD pipeline, and deployment scripts into release.
 - Added CI/CD pipeline for citcodevops01 account with full deployment guide.
@@ -3311,20 +4215,20 @@
 - Replaced hardcoded account IDs with placeholders across all .env example files.</t>
         </is>
       </c>
-      <c r="E108" s="10" t="n">
+      <c r="E174" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F108" s="8" t="n"/>
-    </row>
-    <row r="109" ht="143" customHeight="1">
-      <c r="A109" s="8" t="n"/>
-      <c r="B109" s="8" t="n"/>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="F174" s="8" t="n"/>
+    </row>
+    <row r="175" ht="143" customHeight="1">
+      <c r="A175" s="8" t="n"/>
+      <c r="B175" s="8" t="n"/>
+      <c r="C175" s="9" t="inlineStr">
         <is>
           <t>Panel Link Fix, Semantic Versioning, X-Ray Spec &amp; Inventory Comparison</t>
         </is>
       </c>
-      <c r="D109" s="9" t="inlineStr">
+      <c r="D175" s="9" t="inlineStr">
         <is>
           <t>- Fixed health panel links to panel-level and added . wildcards to all :pipe variable filters for correct multi-value interpolation.
 - Added semantic versioning steering rules to the project documentation.
@@ -3335,20 +4239,34 @@
 - Completed mapper vs inventory repo comparison document.</t>
         </is>
       </c>
-      <c r="E109" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F109" s="8" t="n"/>
-    </row>
-    <row r="110" ht="143" customHeight="1">
-      <c r="A110" s="8" t="n"/>
-      <c r="B110" s="8" t="n"/>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="E175" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F175" s="8" t="n"/>
+    </row>
+    <row r="176" ht="143" customHeight="1">
+      <c r="A176" s="8" t="n"/>
+      <c r="B176" s="8" t="n"/>
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>Panel Link Fix, Semantic Versioning, X-Ray Spec &amp; Inventory Comparison</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="inlineStr"/>
+      <c r="E176" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F176" s="8" t="n"/>
+    </row>
+    <row r="177" ht="143" customHeight="1">
+      <c r="A177" s="8" t="n"/>
+      <c r="B177" s="8" t="n"/>
+      <c r="C177" s="9" t="inlineStr">
         <is>
           <t>CloudWatch Metrics Publishing, Pydantic Models &amp; S3 Key Refactor</t>
         </is>
       </c>
-      <c r="D110" s="9" t="inlineStr">
+      <c r="D177" s="9" t="inlineStr">
         <is>
           <t>- Added CloudWatch metrics publishing from inventory cache Lambda — deployed 597 metrics across 6 platforms to DEV.
 - Fixed MSK to publish cluster names (not topics) and Redis to publish cache node IDs (not replication group IDs) to match what Grafana dashboard variables expect.
@@ -3360,20 +4278,20 @@
 - Refactored S3 keys to use {platform}/{row_name}/ structure for easier browsing.</t>
         </is>
       </c>
-      <c r="E110" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F110" s="8" t="n"/>
-    </row>
-    <row r="111" ht="143" customHeight="1">
-      <c r="A111" s="8" t="n"/>
-      <c r="B111" s="8" t="n"/>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="E177" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F177" s="8" t="n"/>
+    </row>
+    <row r="178" ht="143" customHeight="1">
+      <c r="A178" s="8" t="n"/>
+      <c r="B178" s="8" t="n"/>
+      <c r="C178" s="9" t="inlineStr">
         <is>
           <t>Platform-Agnostic Rename (ia-it-sre Convention) &amp; Docs Reorganisation</t>
         </is>
       </c>
-      <c r="D111" s="9" t="inlineStr">
+      <c r="D178" s="9" t="inlineStr">
         <is>
           <t>- Updated rename spec with full migration plan covering Phases 8-18.
 - Renamed all CloudFormation stack names, Grafana execution role, workspace IAM roles, Lambda functions, dashboard UID, alarm descriptions, and pipeline stack names from meridian to the ia-it-sre naming convention.
@@ -3383,20 +4301,20 @@
 - Fixed e2e and CloudFormation tests to pass with the new ia-it-sre naming.</t>
         </is>
       </c>
-      <c r="E111" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F111" s="8" t="n"/>
-    </row>
-    <row r="112" ht="143" customHeight="1">
-      <c r="A112" s="8" t="n"/>
-      <c r="B112" s="8" t="n"/>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="E178" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F178" s="8" t="n"/>
+    </row>
+    <row r="179" ht="143" customHeight="1">
+      <c r="A179" s="8" t="n"/>
+      <c r="B179" s="8" t="n"/>
+      <c r="C179" s="9" t="inlineStr">
         <is>
           <t>Infinity Datasource Migration, Platform Rename Complete, EC2 Name Tag</t>
         </is>
       </c>
-      <c r="D112" s="9" t="inlineStr">
+      <c r="D179" s="9" t="inlineStr">
         <is>
           <t>- Completed overnight test/refactor: replaced stale row folder tests with dynamic validation, fixed docs_generator row numbering, and split generators/ into rows/ and inventory/ subpackages.
 - Fixed preflight to fall back to workspace API check when CFN stack not found — handles first-deploy scenario.
@@ -3408,20 +4326,20 @@
 - Completed platform-agnostic rename across all remaining phases — workspace template, IAM roles, provisioner policy, pipeline stacks, alarms, docs, tests, and remaining code references.</t>
         </is>
       </c>
-      <c r="E112" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F112" s="8" t="n"/>
-    </row>
-    <row r="113" ht="143" customHeight="1">
-      <c r="A113" s="8" t="n"/>
-      <c r="B113" s="8" t="n"/>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="E179" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F179" s="8" t="n"/>
+    </row>
+    <row r="180" ht="143" customHeight="1">
+      <c r="A180" s="8" t="n"/>
+      <c r="B180" s="8" t="n"/>
+      <c r="C180" s="9" t="inlineStr">
         <is>
           <t>CloudFront S3 Proxy, DB Discoverer Enhancements &amp; Package Refactor (v1</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr">
+      <c r="D180" s="9" t="inlineStr">
         <is>
           <t>- Added Infinity datasource + mapper decommission spec and CloudFront S3 proxy spec for Grafana variables.
 - Added CloudFront + S3 OAC proxy CFN template for serving inventory JSON to Grafana without client-side SigV4.
@@ -3433,20 +4351,20 @@
 - Fixed EKS URL to use console link; fixed ECR URL to use console repository link.</t>
         </is>
       </c>
-      <c r="E113" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F113" s="8" t="n"/>
-    </row>
-    <row r="114" ht="143" customHeight="1">
-      <c r="A114" s="8" t="n"/>
-      <c r="B114" s="8" t="n"/>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="E180" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F180" s="8" t="n"/>
+    </row>
+    <row r="181" ht="143" customHeight="1">
+      <c r="A181" s="8" t="n"/>
+      <c r="B181" s="8" t="n"/>
+      <c r="C181" s="9" t="inlineStr">
         <is>
           <t>Hotfix Merge, Health Panel Fixes &amp; Named Exit Codes</t>
         </is>
       </c>
-      <c r="D114" s="9" t="inlineStr">
+      <c r="D181" s="9" t="inlineStr">
         <is>
           <t>- Merged hotfix with variable-based panel filters, alarm fixes, and fresh Grafana workspace provisioning.
 - Added full panel tables for all remaining rows (EC2, ECR, EKS, RDS Aurora, DocumentDB, Neptune) to the Confluence guide.
@@ -3455,20 +4373,20 @@
 - Added named exit code constants to main.py CLI for clearer error handling.</t>
         </is>
       </c>
-      <c r="E114" s="10" t="n">
+      <c r="E181" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F114" s="8" t="n"/>
-    </row>
-    <row r="115" ht="143" customHeight="1">
-      <c r="A115" s="8" t="n"/>
-      <c r="B115" s="8" t="n"/>
-      <c r="C115" s="9" t="inlineStr">
+      <c r="F181" s="8" t="n"/>
+    </row>
+    <row r="182" ht="143" customHeight="1">
+      <c r="A182" s="8" t="n"/>
+      <c r="B182" s="8" t="n"/>
+      <c r="C182" s="9" t="inlineStr">
         <is>
           <t>X-Ray Tracing Row &amp; Documentation</t>
         </is>
       </c>
-      <c r="D115" s="9" t="inlineStr">
+      <c r="D182" s="9" t="inlineStr">
         <is>
           <t>- Built new X-Ray tracing Row 17 with 4 panels: Service Map, Recent Traces, Response Time p50/p95/p99, and Error/Fault Rate using the X-Ray datasource; added xray: read permissions to the Grafana workspace IAM role.
 - Added X-Ray self-service enablement guide with Lambda tracing commands, ALB setup, and cost estimates.
@@ -3476,20 +4394,20 @@
 - Added X-Ray limitations document covering AMG 12.4 constraints plus Application Signals overview for future SLO-based monitoring.</t>
         </is>
       </c>
-      <c r="E115" s="10" t="n">
+      <c r="E182" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F115" s="8" t="n"/>
-    </row>
-    <row r="116" ht="143" customHeight="1">
-      <c r="A116" s="8" t="n"/>
-      <c r="B116" s="8" t="n"/>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="F182" s="8" t="n"/>
+    </row>
+    <row r="183" ht="143" customHeight="1">
+      <c r="A183" s="8" t="n"/>
+      <c r="B183" s="8" t="n"/>
+      <c r="C183" s="9" t="inlineStr">
         <is>
           <t>Confluence Docs, S3 Lifecycle Rules &amp; v1.4.3</t>
         </is>
       </c>
-      <c r="D116" s="9" t="inlineStr">
+      <c r="D183" s="9" t="inlineStr">
         <is>
           <t>- Synced docs with v1.4.1 covering instances-only pattern and EKS/ECR console URLs.
 - Added 5 Confluence documentation pages: executive overview, architecture, API user guide, developer onboarding, and deployment runbook (v1.4.2).
@@ -3497,20 +4415,20 @@
 - Added 7-day S3 lifecycle expiration rules for history/ objects with 78 prefix-based rules across all platforms and services (v1.4.3).</t>
         </is>
       </c>
-      <c r="E116" s="10" t="n">
+      <c r="E183" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="F116" s="8" t="n"/>
-    </row>
-    <row r="117" ht="143" customHeight="1">
-      <c r="A117" s="11" t="n"/>
-      <c r="B117" s="11" t="n"/>
-      <c r="C117" s="24" t="inlineStr">
+      <c r="F183" s="8" t="n"/>
+    </row>
+    <row r="184" ht="143" customHeight="1">
+      <c r="A184" s="11" t="n"/>
+      <c r="B184" s="11" t="n"/>
+      <c r="C184" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D117" s="25" t="inlineStr">
+      <c r="D184" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (11 meetings, 2.5h):
 - IA Config Portal - DEMO (30 min)
@@ -3526,90 +4444,90 @@
 - Daily Standup - Innovation IT (30 min)</t>
         </is>
       </c>
-      <c r="E117" s="26" t="n">
+      <c r="E184" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F117" s="11" t="n"/>
-    </row>
-    <row r="118" ht="143" customHeight="1">
-      <c r="A118" s="14" t="inlineStr">
+      <c r="F184" s="11" t="n"/>
+    </row>
+    <row r="185" ht="143" customHeight="1">
+      <c r="A185" s="14" t="inlineStr">
         <is>
           <t>Week 18</t>
         </is>
       </c>
-      <c r="B118" s="15" t="inlineStr">
+      <c r="B185" s="15" t="inlineStr">
         <is>
           <t>Jul 13 – Jul 17, 2026</t>
         </is>
       </c>
-      <c r="C118" s="16" t="inlineStr">
+      <c r="C185" s="16" t="inlineStr">
         <is>
           <t>EC2 Deep-Links &amp; IISS-485: EKS Deep-Links</t>
         </is>
       </c>
-      <c r="D118" s="16" t="inlineStr">
+      <c r="D185" s="16" t="inlineStr">
         <is>
           <t>- Added AWS Console deep links to EC2 and EKS time series panels.
 - Removed duplicate filterFieldsByName transformations from DB time series panels.</t>
         </is>
       </c>
-      <c r="E118" s="17" t="n">
+      <c r="E185" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="F118" s="14">
-        <f>SUM(E118:E135)</f>
+      <c r="F185" s="14">
+        <f>SUM(E185:E203)</f>
         <v/>
       </c>
     </row>
-    <row r="119" ht="143" customHeight="1">
-      <c r="A119" s="18" t="n"/>
-      <c r="B119" s="18" t="n"/>
-      <c r="C119" s="19" t="inlineStr">
+    <row r="186" ht="143" customHeight="1">
+      <c r="A186" s="18" t="n"/>
+      <c r="B186" s="18" t="n"/>
+      <c r="C186" s="19" t="inlineStr">
         <is>
           <t>ECS Deep-Links, Mapper Decommission &amp; Infinity Migration</t>
         </is>
       </c>
-      <c r="D119" s="19" t="inlineStr">
+      <c r="D186" s="19" t="inlineStr">
         <is>
           <t>- Added AWS Console deep links to ECS service and ALB Target Group time series panels.
 - Decommissioned all mapper Lambda handlers; migrated ECR and ECS resource tables to Infinity datasource.
 - Fixed ecs_target_group variable to remove allValue wildcard that was bypassing platform filtering.</t>
         </is>
       </c>
-      <c r="E119" s="20" t="n">
+      <c r="E186" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F119" s="18" t="n"/>
-    </row>
-    <row r="120" ht="143" customHeight="1">
-      <c r="A120" s="18" t="n"/>
-      <c r="B120" s="18" t="n"/>
-      <c r="C120" s="19" t="inlineStr">
+      <c r="F186" s="18" t="n"/>
+    </row>
+    <row r="187" ht="143" customHeight="1">
+      <c r="A187" s="18" t="n"/>
+      <c r="B187" s="18" t="n"/>
+      <c r="C187" s="19" t="inlineStr">
         <is>
           <t>DB Time Series Deep-Links &amp; Variable Simplification</t>
         </is>
       </c>
-      <c r="D120" s="19" t="inlineStr">
+      <c r="D187" s="19" t="inlineStr">
         <is>
           <t>- Added AWS Console deep links to RDS, DocumentDB, Redis/Valkey, and Neptune time series panels.
 - Simplified DB dashboard variables from 8 (cluster+instance pairs) down to 4 single variables per service.
 - Applied simplified DB variables to assembled dashboard JSON.</t>
         </is>
       </c>
-      <c r="E120" s="20" t="n">
+      <c r="E187" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F120" s="18" t="n"/>
-    </row>
-    <row r="121" ht="143" customHeight="1">
-      <c r="A121" s="18" t="n"/>
-      <c r="B121" s="18" t="n"/>
-      <c r="C121" s="19" t="inlineStr">
+      <c r="F187" s="18" t="n"/>
+    </row>
+    <row r="188" ht="143" customHeight="1">
+      <c r="A188" s="18" t="n"/>
+      <c r="B188" s="18" t="n"/>
+      <c r="C188" s="19" t="inlineStr">
         <is>
           <t>Alarms, Grafana User Management, Custom URL, Agents Extraction &amp; Platf</t>
         </is>
       </c>
-      <c r="D121" s="19" t="inlineStr">
+      <c r="D188" s="19" t="inlineStr">
         <is>
           <t>- Updated Project tag to IA-IT-SRE-Resources-Monitoring; added ECS CPU critical alarm at 80%, lowered warning to 60%.
 - Enhanced Grafana user management CLI with list/add/update/revoke commands and user resolution; documented DL/SSO group limitations and bulk access guidance.
@@ -3621,76 +4539,76 @@
 - Reordered ECR table columns — RepositoryName first, Images second.</t>
         </is>
       </c>
-      <c r="E121" s="20" t="n">
+      <c r="E188" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F121" s="18" t="n"/>
-    </row>
-    <row r="122" ht="143" customHeight="1">
-      <c r="A122" s="18" t="n"/>
-      <c r="B122" s="18" t="n"/>
-      <c r="C122" s="19" t="inlineStr">
+      <c r="F188" s="18" t="n"/>
+    </row>
+    <row r="189" ht="143" customHeight="1">
+      <c r="A189" s="18" t="n"/>
+      <c r="B189" s="18" t="n"/>
+      <c r="C189" s="19" t="inlineStr">
         <is>
           <t>MSK Inventory-Driven Deep-Links</t>
         </is>
       </c>
-      <c r="D122" s="19" t="inlineStr">
+      <c r="D189" s="19" t="inlineStr">
         <is>
           <t>- Migrated MSK row to inventory-driven deep-links using the Infinity datasource for all MSK panels.</t>
         </is>
       </c>
-      <c r="E122" s="20" t="n">
+      <c r="E189" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F122" s="18" t="n"/>
-    </row>
-    <row r="123" ht="143" customHeight="1">
-      <c r="A123" s="18" t="n"/>
-      <c r="B123" s="18" t="n"/>
-      <c r="C123" s="19" t="inlineStr">
+      <c r="F189" s="18" t="n"/>
+    </row>
+    <row r="190" ht="143" customHeight="1">
+      <c r="A190" s="18" t="n"/>
+      <c r="B190" s="18" t="n"/>
+      <c r="C190" s="19" t="inlineStr">
         <is>
           <t>ia-it-sre-agent-orchestration Initial Commit</t>
         </is>
       </c>
-      <c r="D123" s="19" t="inlineStr">
+      <c r="D190" s="19" t="inlineStr">
         <is>
           <t>- Created new ia-it-sre-agent-orchestration repository — agents package extracted from the monitoring repo for standalone reuse.
 - Added agentic AI guide from the monitoring repo.</t>
         </is>
       </c>
-      <c r="E123" s="20" t="n">
+      <c r="E190" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F123" s="18" t="n"/>
-    </row>
-    <row r="124" ht="143" customHeight="1">
-      <c r="A124" s="18" t="n"/>
-      <c r="B124" s="18" t="n"/>
-      <c r="C124" s="19" t="inlineStr">
+      <c r="F190" s="18" t="n"/>
+    </row>
+    <row r="191" ht="143" customHeight="1">
+      <c r="A191" s="18" t="n"/>
+      <c r="B191" s="18" t="n"/>
+      <c r="C191" s="19" t="inlineStr">
         <is>
           <t>MSK Topics Filter</t>
         </is>
       </c>
-      <c r="D124" s="19" t="inlineStr">
+      <c r="D191" s="19" t="inlineStr">
         <is>
           <t>- Filtered internal Kafka topics (__ prefix) from the inventory API.
 - Scoped topics to their platform's name patterns for cleaner results (v1.4.4).</t>
         </is>
       </c>
-      <c r="E124" s="20" t="n">
+      <c r="E191" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="F124" s="18" t="n"/>
-    </row>
-    <row r="125" ht="143" customHeight="1">
-      <c r="A125" s="18" t="n"/>
-      <c r="B125" s="18" t="n"/>
-      <c r="C125" s="19" t="inlineStr">
+      <c r="F191" s="18" t="n"/>
+    </row>
+    <row r="192" ht="143" customHeight="1">
+      <c r="A192" s="18" t="n"/>
+      <c r="B192" s="18" t="n"/>
+      <c r="C192" s="19" t="inlineStr">
         <is>
           <t>Dynamic Alarm Provisioner, S3-Backed Alarm Lambdas &amp; Notification Form</t>
         </is>
       </c>
-      <c r="D125" s="19" t="inlineStr">
+      <c r="D192" s="19" t="inlineStr">
         <is>
           <t>- Built full S3-backed alarm Lambda architecture: alarm_notifier, alarm_re_notifier, and alarm_state_publisher with shared models/formatter layer.
 - Implemented dynamic alarm provisioner Lambda — reads resource inventory from S3 and automatically creates/updates per-resource CloudWatch alarms for all 6 platforms.
@@ -3702,56 +4620,56 @@
 - Iterated on notification formatting: emoji-based → ASCII table → clean key-value fixed-width label format.</t>
         </is>
       </c>
-      <c r="E125" s="20" t="n">
+      <c r="E192" s="20" t="n">
         <v>2.75</v>
       </c>
-      <c r="F125" s="18" t="n"/>
-    </row>
-    <row r="126" ht="143" customHeight="1">
-      <c r="A126" s="18" t="n"/>
-      <c r="B126" s="18" t="n"/>
-      <c r="C126" s="19" t="inlineStr">
+      <c r="F192" s="18" t="n"/>
+    </row>
+    <row r="193" ht="143" customHeight="1">
+      <c r="A193" s="18" t="n"/>
+      <c r="B193" s="18" t="n"/>
+      <c r="C193" s="19" t="inlineStr">
         <is>
           <t>SQS Panel Updates</t>
         </is>
       </c>
-      <c r="D126" s="19" t="inlineStr">
+      <c r="D193" s="19" t="inlineStr">
         <is>
           <t>- Updated SQS health and queues table panels.</t>
         </is>
       </c>
-      <c r="E126" s="20" t="n">
+      <c r="E193" s="20" t="n">
         <v>2.75</v>
       </c>
-      <c r="F126" s="18" t="n"/>
-    </row>
-    <row r="127" ht="143" customHeight="1">
-      <c r="A127" s="18" t="n"/>
-      <c r="B127" s="18" t="n"/>
-      <c r="C127" s="19" t="inlineStr">
+      <c r="F193" s="18" t="n"/>
+    </row>
+    <row r="194" ht="143" customHeight="1">
+      <c r="A194" s="18" t="n"/>
+      <c r="B194" s="18" t="n"/>
+      <c r="C194" s="19" t="inlineStr">
         <is>
           <t>ALB Target Group Discoverer</t>
         </is>
       </c>
-      <c r="D127" s="19" t="inlineStr">
+      <c r="D194" s="19" t="inlineStr">
         <is>
           <t>- Added ALB target group discoverer to the inventory API — enables dashboard variable migration from ECS mapper Lambda to Infinity datasource for ecs_target_group filtering.</t>
         </is>
       </c>
-      <c r="E127" s="20" t="n">
+      <c r="E194" s="20" t="n">
         <v>2.75</v>
       </c>
-      <c r="F127" s="18" t="n"/>
-    </row>
-    <row r="128" ht="143" customHeight="1">
-      <c r="A128" s="18" t="n"/>
-      <c r="B128" s="18" t="n"/>
-      <c r="C128" s="19" t="inlineStr">
+      <c r="F194" s="18" t="n"/>
+    </row>
+    <row r="195" ht="143" customHeight="1">
+      <c r="A195" s="18" t="n"/>
+      <c r="B195" s="18" t="n"/>
+      <c r="C195" s="19" t="inlineStr">
         <is>
           <t>Alarm Panel Fixes, Lambda Rename &amp; Alarm Definition Refactor</t>
         </is>
       </c>
-      <c r="D128" s="19" t="inlineStr">
+      <c r="D195" s="19" t="inlineStr">
         <is>
           <t>- Fixed alarm state history panel height, enabled scroll for overflow, and filtered to show only fired alarms for the selected platform with the correct IA-IT-SRE regex pattern.
 - Reverted unsupported SQL WHERE clause on metric values — landed on ORDER BY MAX() DESC LIMIT 50 as the working approach.
@@ -3763,20 +4681,20 @@
 - Fixed alarm name assertions in tests to match new row-based ID prefix format.</t>
         </is>
       </c>
-      <c r="E128" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F128" s="18" t="n"/>
-    </row>
-    <row r="129" ht="143" customHeight="1">
-      <c r="A129" s="18" t="n"/>
-      <c r="B129" s="18" t="n"/>
-      <c r="C129" s="19" t="inlineStr">
+      <c r="E195" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F195" s="18" t="n"/>
+    </row>
+    <row r="196" ht="143" customHeight="1">
+      <c r="A196" s="18" t="n"/>
+      <c r="B196" s="18" t="n"/>
+      <c r="C196" s="19" t="inlineStr">
         <is>
           <t>X-Ray Groups, SDK Instrumentation &amp; Grafana Datasource</t>
         </is>
       </c>
-      <c r="D129" s="19" t="inlineStr">
+      <c r="D196" s="19" t="inlineStr">
         <is>
           <t>- Created X-Ray tracing groups for all 6 platforms (meridian, citcoworks, automationhub, ia-bpo, bpm, rpacfs1) and enabled Active tracing on all 4 alarm Lambdas.
 - Documented X-Ray enablement status — groups deployed; Meridian platform tracing pending team action.
@@ -3788,40 +4706,40 @@
 - Rebuilt assembled dashboard JSON (v62, 33 panels) and merged X-Ray feature into release.</t>
         </is>
       </c>
-      <c r="E129" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F129" s="18" t="n"/>
-    </row>
-    <row r="130" ht="143" customHeight="1">
-      <c r="A130" s="18" t="n"/>
-      <c r="B130" s="18" t="n"/>
-      <c r="C130" s="19" t="inlineStr">
+      <c r="E196" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F196" s="18" t="n"/>
+    </row>
+    <row r="197" ht="143" customHeight="1">
+      <c r="A197" s="18" t="n"/>
+      <c r="B197" s="18" t="n"/>
+      <c r="C197" s="19" t="inlineStr">
         <is>
           <t>Alarm Panel Fix &amp; Row 10 Alarm Docs</t>
         </is>
       </c>
-      <c r="D130" s="19" t="inlineStr">
+      <c r="D197" s="19" t="inlineStr">
         <is>
           <t>- Documented Row 10 alarm requirements and their dependency on the inventory repo's Phase 4 target group data.
 - Fixed alarm name regex in the dashboard alarms panel to match the new IA-IT-SRE prefix; switched period to auto for better resolution.
 - Merged alarms-notifications feature into release.</t>
         </is>
       </c>
-      <c r="E130" s="20" t="n">
+      <c r="E197" s="20" t="n">
         <v>2.75</v>
       </c>
-      <c r="F130" s="18" t="n"/>
-    </row>
-    <row r="131" ht="143" customHeight="1">
-      <c r="A131" s="18" t="n"/>
-      <c r="B131" s="18" t="n"/>
-      <c r="C131" s="19" t="inlineStr">
+      <c r="F197" s="18" t="n"/>
+    </row>
+    <row r="198" ht="143" customHeight="1">
+      <c r="A198" s="18" t="n"/>
+      <c r="B198" s="18" t="n"/>
+      <c r="C198" s="19" t="inlineStr">
         <is>
           <t>X-Ray Row Completion, Application Signals Phase 1 &amp; Provisioner Auto-C</t>
         </is>
       </c>
-      <c r="D131" s="19" t="inlineStr">
+      <c r="D198" s="19" t="inlineStr">
         <is>
           <t>- Completed X-Ray dashboard row with 4 panels: Service Map (nodeGraph), Trace Volume Over Time (stacked bars by group), Traces by Group (horizontal bar gauge), and Recent Traces table with clickable trace IDs.
 - Fixed panels 5/6 to use CloudWatch AWS/X-Ray metrics — X-Ray plugin does not support getTimeSeriesServiceStatistics.
@@ -3832,40 +4750,40 @@
 - Renamed Grafana workspace from ia-it-sre-resources-monitoring to ia-it-sre-infrastructure-monitoring; updated all references.</t>
         </is>
       </c>
-      <c r="E131" s="20" t="n">
+      <c r="E198" s="20" t="n">
         <v>2.75</v>
       </c>
-      <c r="F131" s="18" t="n"/>
-    </row>
-    <row r="132" ht="143" customHeight="1">
-      <c r="A132" s="18" t="n"/>
-      <c r="B132" s="18" t="n"/>
-      <c r="C132" s="19" t="inlineStr">
+      <c r="F198" s="18" t="n"/>
+    </row>
+    <row r="199" ht="143" customHeight="1">
+      <c r="A199" s="18" t="n"/>
+      <c r="B199" s="18" t="n"/>
+      <c r="C199" s="19" t="inlineStr">
         <is>
           <t>ECS Target Group Discoverer</t>
         </is>
       </c>
-      <c r="D132" s="19" t="inlineStr">
+      <c r="D199" s="19" t="inlineStr">
         <is>
           <t>- Increased inventory API test coverage from 62% to 99% with 453 tests including Hypothesis property-based tests (v1.4.6).
 - Added target_group_full_name and alb_full_name fields to ECS target group discoverer with ARN-based console URLs (v1.4.7).
 - Renamed row_10_ecs_apis S3 cache path to row_10_ecs_target_groups; documented breaking change migration tasks in Phase 5 spec.</t>
         </is>
       </c>
-      <c r="E132" s="20" t="n">
+      <c r="E199" s="20" t="n">
         <v>2.75</v>
       </c>
-      <c r="F132" s="18" t="n"/>
-    </row>
-    <row r="133" ht="143" customHeight="1">
-      <c r="A133" s="18" t="n"/>
-      <c r="B133" s="18" t="n"/>
-      <c r="C133" s="19" t="inlineStr">
+      <c r="F199" s="18" t="n"/>
+    </row>
+    <row r="200" ht="143" customHeight="1">
+      <c r="A200" s="18" t="n"/>
+      <c r="B200" s="18" t="n"/>
+      <c r="C200" s="19" t="inlineStr">
         <is>
           <t>X-Ray SDK Fix, App Signals Phase 2, Docs Consolidation &amp; Observability</t>
         </is>
       </c>
-      <c r="D133" s="19" t="inlineStr">
+      <c r="D200" s="19" t="inlineStr">
         <is>
           <t>- Renamed Grafana dashboard title to IA IT SRE Infrastructure Monitoring; moved S3 bucket rename to a separate spec.
 - Fixed X-Ray tracing by adding explicit service name configuration via xray_recorder.configure(service=...) to all 4 Lambda handlers — without this, traces exist but are not discoverable by X-Ray groups.
@@ -3877,38 +4795,52 @@
 - Added comparison showing CloudWatch + X-Ray + App Signals achieves 78% parity without Grafana.</t>
         </is>
       </c>
-      <c r="E133" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F133" s="18" t="n"/>
-    </row>
-    <row r="134" ht="143" customHeight="1">
-      <c r="A134" s="18" t="n"/>
-      <c r="B134" s="18" t="n"/>
-      <c r="C134" s="19" t="inlineStr">
+      <c r="E200" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F200" s="18" t="n"/>
+    </row>
+    <row r="201" ht="143" customHeight="1">
+      <c r="A201" s="18" t="n"/>
+      <c r="B201" s="18" t="n"/>
+      <c r="C201" s="19" t="inlineStr">
         <is>
           <t>S3 Cache Region-Aware Prefix Fix</t>
         </is>
       </c>
-      <c r="D134" s="19" t="inlineStr">
+      <c r="D201" s="19" t="inlineStr">
         <is>
           <t>- Fixed inventory S3 cache prefix to be region-aware — ensures correct path structure across multi-region deployments.</t>
         </is>
       </c>
-      <c r="E134" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F134" s="18" t="n"/>
-    </row>
-    <row r="135" ht="143" customHeight="1">
-      <c r="A135" s="21" t="n"/>
-      <c r="B135" s="21" t="n"/>
-      <c r="C135" s="24" t="inlineStr">
+      <c r="E201" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F201" s="18" t="n"/>
+    </row>
+    <row r="202" ht="143" customHeight="1">
+      <c r="A202" s="18" t="n"/>
+      <c r="B202" s="18" t="n"/>
+      <c r="C202" s="19" t="inlineStr">
+        <is>
+          <t>S3 Cache Region-Aware Prefix Fix</t>
+        </is>
+      </c>
+      <c r="D202" s="19" t="inlineStr"/>
+      <c r="E202" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F202" s="18" t="n"/>
+    </row>
+    <row r="203" ht="143" customHeight="1">
+      <c r="A203" s="21" t="n"/>
+      <c r="B203" s="21" t="n"/>
+      <c r="C203" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D135" s="25" t="inlineStr">
+      <c r="D203" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (10 meetings, 2.5h):
 - CORA Support Handoff &lt;&gt; Final Connect (60 min)
@@ -3923,28 +4855,28 @@
 - Daily Standup - Innovation IT (30 min)</t>
         </is>
       </c>
-      <c r="E135" s="26" t="n">
+      <c r="E203" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F135" s="21" t="n"/>
-    </row>
-    <row r="136" ht="143" customHeight="1">
-      <c r="A136" s="4" t="inlineStr">
+      <c r="F203" s="21" t="n"/>
+    </row>
+    <row r="204" ht="143" customHeight="1">
+      <c r="A204" s="4" t="inlineStr">
         <is>
           <t>Week 19</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="B204" s="5" t="inlineStr">
         <is>
           <t>Jul 20 – Jul 24, 2026</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="C204" s="6" t="inlineStr">
         <is>
           <t>X-Ray Datasource Fixes, nodeGraph Workaround &amp; Trace Backends Comparis</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D204" s="6" t="inlineStr">
         <is>
           <t>- Restored X-Ray nodeGraph service map panel and removed duplicate traced services panel.
 - Added trace backends comparison doc: X-Ray vs Tempo vs Jaeger vs Zipkin with feature matrix, cost analysis, and architecture options.
@@ -3953,42 +4885,42 @@
 - Fixed CloudWatch provisioner to use stable 'cloudwatch' UID matching all 100+ panel references; removed unnecessary OpenSearch datasource creation.</t>
         </is>
       </c>
-      <c r="E136" s="7" t="n">
+      <c r="E204" s="7" t="n">
         <v>1.25</v>
       </c>
-      <c r="F136" s="4">
-        <f>SUM(E136:E154)</f>
+      <c r="F204" s="4">
+        <f>SUM(E204:E222)</f>
         <v/>
       </c>
     </row>
-    <row r="137" ht="143" customHeight="1">
-      <c r="A137" s="8" t="n"/>
-      <c r="B137" s="8" t="n"/>
-      <c r="C137" s="9" t="inlineStr">
+    <row r="205" ht="143" customHeight="1">
+      <c r="A205" s="8" t="n"/>
+      <c r="B205" s="8" t="n"/>
+      <c r="C205" s="9" t="inlineStr">
         <is>
           <t>ECS Target Group Alarms &amp; Row Rename</t>
         </is>
       </c>
-      <c r="D137" s="9" t="inlineStr">
+      <c r="D205" s="9" t="inlineStr">
         <is>
           <t>- Implemented ECS target group alarms (rows 10.0-10.3).
 - Renamed row from ecs_apis to ecs_target_groups for consistency with inventory naming.</t>
         </is>
       </c>
-      <c r="E137" s="10" t="n">
+      <c r="E205" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F137" s="8" t="n"/>
-    </row>
-    <row r="138" ht="143" customHeight="1">
-      <c r="A138" s="8" t="n"/>
-      <c r="B138" s="8" t="n"/>
-      <c r="C138" s="9" t="inlineStr">
+      <c r="F205" s="8" t="n"/>
+    </row>
+    <row r="206" ht="143" customHeight="1">
+      <c r="A206" s="8" t="n"/>
+      <c r="B206" s="8" t="n"/>
+      <c r="C206" s="9" t="inlineStr">
         <is>
           <t>Powertools Migration, VPN SSL Hotfixes &amp; Cross-Platform Data Leak Fix</t>
         </is>
       </c>
-      <c r="D138" s="9" t="inlineStr">
+      <c r="D206" s="9" t="inlineStr">
         <is>
           <t>- Migrated all alarm Lambdas from aws-xray-sdk to aws-lambda-powertools for tracing.
 - Added AppName and BudgetCode (IA-BPO) tags to all Lambda functions for cost attribution.
@@ -3998,59 +4930,59 @@
 - Fixed cross-platform data leak: empty variable values caused filterFieldsByName to match all platforms — added allValue='^$' __no_resources__ sentinel across all 13 multi-select variables.</t>
         </is>
       </c>
-      <c r="E138" s="10" t="n">
+      <c r="E206" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F138" s="8" t="n"/>
-    </row>
-    <row r="139" ht="143" customHeight="1">
-      <c r="A139" s="8" t="n"/>
-      <c r="B139" s="8" t="n"/>
-      <c r="C139" s="9" t="inlineStr">
+      <c r="F206" s="8" t="n"/>
+    </row>
+    <row r="207" ht="143" customHeight="1">
+      <c r="A207" s="8" t="n"/>
+      <c r="B207" s="8" t="n"/>
+      <c r="C207" s="9" t="inlineStr">
         <is>
           <t>ECS Target Group Discovery Phase 4 Complete</t>
         </is>
       </c>
-      <c r="D139" s="9" t="inlineStr">
+      <c r="D207" s="9" t="inlineStr">
         <is>
           <t>- Completed ECS Target Group Discovery Phase 4 — ARN-based console URLs, target_group_full_name and alb_full_name fields (v1.4.8).
 - Fixed S3 cache mocking in integration tests to prevent real S3 writes.
 - Added AppName and BudgetCode (IA-BPO) tags to Lambda functions.</t>
         </is>
       </c>
-      <c r="E139" s="10" t="n">
+      <c r="E207" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F139" s="8" t="n"/>
-    </row>
-    <row r="140" ht="143" customHeight="1">
-      <c r="A140" s="8" t="n"/>
-      <c r="B140" s="8" t="n"/>
-      <c r="C140" s="9" t="inlineStr">
+      <c r="F207" s="8" t="n"/>
+    </row>
+    <row r="208" ht="143" customHeight="1">
+      <c r="A208" s="8" t="n"/>
+      <c r="B208" s="8" t="n"/>
+      <c r="C208" s="9" t="inlineStr">
         <is>
           <t>X-Ray Powertools Instrumentation &amp; Lambda Trigger Classification</t>
         </is>
       </c>
-      <c r="D140" s="9" t="inlineStr">
+      <c r="D208" s="9" t="inlineStr">
         <is>
           <t>- Added X-Ray tracing via AWS Lambda Powertools to inventory service with platform/service/environment annotations (v1.4.9).
 - Added trigger_type classification field and spec to Lambda resource model.</t>
         </is>
       </c>
-      <c r="E140" s="10" t="n">
+      <c r="E208" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F140" s="8" t="n"/>
-    </row>
-    <row r="141" ht="143" customHeight="1">
-      <c r="A141" s="8" t="n"/>
-      <c r="B141" s="8" t="n"/>
-      <c r="C141" s="9" t="inlineStr">
+      <c r="F208" s="8" t="n"/>
+    </row>
+    <row r="209" ht="143" customHeight="1">
+      <c r="A209" s="8" t="n"/>
+      <c r="B209" s="8" t="n"/>
+      <c r="C209" s="9" t="inlineStr">
         <is>
           <t>Lambda API Migration v1.5.0</t>
         </is>
       </c>
-      <c r="D141" s="9" t="inlineStr">
+      <c r="D209" s="9" t="inlineStr">
         <is>
           <t>- Deprecated Flask API and migrated to 4 dedicated Lambda handlers behind API Gateway (v1.5.0).
 - Added CloudFormation template and deploy-api CLI command for the new Lambda API.
@@ -4059,40 +4991,40 @@
 - Added /refresh endpoint supporting per-platform, per-service, and full refresh targeting.</t>
         </is>
       </c>
-      <c r="E141" s="10" t="n">
+      <c r="E209" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F141" s="8" t="n"/>
-    </row>
-    <row r="142" ht="143" customHeight="1">
-      <c r="A142" s="8" t="n"/>
-      <c r="B142" s="8" t="n"/>
-      <c r="C142" s="9" t="inlineStr">
+      <c r="F209" s="8" t="n"/>
+    </row>
+    <row r="210" ht="143" customHeight="1">
+      <c r="A210" s="8" t="n"/>
+      <c r="B210" s="8" t="n"/>
+      <c r="C210" s="9" t="inlineStr">
         <is>
           <t>Variable Fix, VPN Cert Deploy &amp; noValue Fallback</t>
         </is>
       </c>
-      <c r="D142" s="9" t="inlineStr">
+      <c r="D210" s="9" t="inlineStr">
         <is>
           <t>- Fixed health row panels to remove trace links and corrected allValue from __no_resources__ to . for all multi-select variables — resolves panels showing Idle/no data when resources exist.
 - Fixed deploy script to auto-patch venv certificates with the corporate CA bundle and switched Lambda packaging to use venv pip — resolves VPN SSL failures during deploy.
 - Added noValue fallback text to all Infinity resource tables for graceful empty-state handling.</t>
         </is>
       </c>
-      <c r="E142" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F142" s="8" t="n"/>
-    </row>
-    <row r="143" ht="143" customHeight="1">
-      <c r="A143" s="8" t="n"/>
-      <c r="B143" s="8" t="n"/>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="E210" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F210" s="8" t="n"/>
+    </row>
+    <row r="211" ht="143" customHeight="1">
+      <c r="A211" s="8" t="n"/>
+      <c r="B211" s="8" t="n"/>
+      <c r="C211" s="9" t="inlineStr">
         <is>
           <t>Resource Tables to Infinity Datasource, Lambda Tags &amp; Pipeline Auto-De</t>
         </is>
       </c>
-      <c r="D143" s="9" t="inlineStr">
+      <c r="D211" s="9" t="inlineStr">
         <is>
           <t>- Converted all resource tables across the dashboard from CloudWatch-based queries to the Infinity datasource pulling from the S3/CloudFront inventory API — tables now show all discovered resources regardless of CloudWatch
 - Standardised Lambda tags with AppName=ia-it-sre-resources-inventory and BudgetCode=ia-bpo.
@@ -4100,38 +5032,38 @@
 - Updated Bitbucket pipeline to deploy the Lambda API stack automatically and invoke the refresh Lambda post-deploy to pre-populate the S3 cache.</t>
         </is>
       </c>
-      <c r="E143" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F143" s="8" t="n"/>
-    </row>
-    <row r="144" ht="143" customHeight="1">
-      <c r="A144" s="8" t="n"/>
-      <c r="B144" s="8" t="n"/>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="E211" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F211" s="8" t="n"/>
+    </row>
+    <row r="212" ht="143" customHeight="1">
+      <c r="A212" s="8" t="n"/>
+      <c r="B212" s="8" t="n"/>
+      <c r="C212" s="9" t="inlineStr">
         <is>
           <t>EKS API 5xx Alarm</t>
         </is>
       </c>
-      <c r="D144" s="9" t="inlineStr">
+      <c r="D212" s="9" t="inlineStr">
         <is>
           <t>- Added EKS API 5xx alarm and synced threshold to the performance panel.</t>
         </is>
       </c>
-      <c r="E144" s="10" t="n">
+      <c r="E212" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F144" s="8" t="n"/>
-    </row>
-    <row r="145" ht="143" customHeight="1">
-      <c r="A145" s="8" t="n"/>
-      <c r="B145" s="8" t="n"/>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="F212" s="8" t="n"/>
+    </row>
+    <row r="213" ht="143" customHeight="1">
+      <c r="A213" s="8" t="n"/>
+      <c r="B213" s="8" t="n"/>
+      <c r="C213" s="9" t="inlineStr">
         <is>
           <t>Alarm Panel Fixes, Platform Config, Alert Health Panels, Limitations D</t>
         </is>
       </c>
-      <c r="D145" s="9" t="inlineStr">
+      <c r="D213" s="9" t="inlineStr">
         <is>
           <t>- Added clickable AWS Console links to alarm names in the Active CW Alarms panel using renameByRegex to strip numeric prefix.
 - Fixed alarm panel links and regex patterns to correctly reconstruct full alarm names for console deep-linking.
@@ -4143,20 +5075,20 @@
 - Iterated on health alert panels — fixed platform filtering, alarm severity patterns, label overrides, and reduce transformations for correct firing alarm counts.</t>
         </is>
       </c>
-      <c r="E145" s="10" t="n">
+      <c r="E213" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F145" s="8" t="n"/>
-    </row>
-    <row r="146" ht="143" customHeight="1">
-      <c r="A146" s="8" t="n"/>
-      <c r="B146" s="8" t="n"/>
-      <c r="C146" s="9" t="inlineStr">
+      <c r="F213" s="8" t="n"/>
+    </row>
+    <row r="214" ht="143" customHeight="1">
+      <c r="A214" s="8" t="n"/>
+      <c r="B214" s="8" t="n"/>
+      <c r="C214" s="9" t="inlineStr">
         <is>
           <t>Naming Standardisation, Custom Domain &amp; Test Coverage Restoration</t>
         </is>
       </c>
-      <c r="D146" s="9" t="inlineStr">
+      <c r="D214" s="9" t="inlineStr">
         <is>
           <t>- Fixed property tests to mock _cache preventing real S3 writes during tests.
 - Removed hardcoded API URLs and standardised all naming from ia-sre to ia-it-sre across the repo.
@@ -4167,20 +5099,20 @@
 - Added 50 unit tests for Lambda API handlers and 48 additional tests — restored coverage to 99% with 562 total tests.</t>
         </is>
       </c>
-      <c r="E146" s="10" t="n">
+      <c r="E214" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F146" s="8" t="n"/>
-    </row>
-    <row r="147" ht="143" customHeight="1">
-      <c r="A147" s="8" t="n"/>
-      <c r="B147" s="8" t="n"/>
-      <c r="C147" s="9" t="inlineStr">
+      <c r="F214" s="8" t="n"/>
+    </row>
+    <row r="215" ht="143" customHeight="1">
+      <c r="A215" s="8" t="n"/>
+      <c r="B215" s="8" t="n"/>
+      <c r="C215" s="9" t="inlineStr">
         <is>
           <t>Composite Alarms, Notifier Fixes &amp; Auto-Invoke Provisioner</t>
         </is>
       </c>
-      <c r="D147" s="9" t="inlineStr">
+      <c r="D215" s="9" t="inlineStr">
         <is>
           <t>- Fixed alarm notifier — removed duplicate tracer/import causing WARNING notifications to fail silently.
 - Fixed alarm formatter to remove stale datapoints from ongoing re-notification emails.
@@ -4192,58 +5124,58 @@
 - Rewrote alarms-and-notifications operations documentation with full architecture and provisioner system details.</t>
         </is>
       </c>
-      <c r="E147" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F147" s="8" t="n"/>
-    </row>
-    <row r="148" ht="143" customHeight="1">
-      <c r="A148" s="8" t="n"/>
-      <c r="B148" s="8" t="n"/>
-      <c r="C148" s="9" t="inlineStr">
+      <c r="E215" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F215" s="8" t="n"/>
+    </row>
+    <row r="216" ht="143" customHeight="1">
+      <c r="A216" s="8" t="n"/>
+      <c r="B216" s="8" t="n"/>
+      <c r="C216" s="9" t="inlineStr">
         <is>
           <t>Spec Status Update &amp; infrastructure-inventory Rename</t>
         </is>
       </c>
-      <c r="D148" s="9" t="inlineStr">
+      <c r="D216" s="9" t="inlineStr">
         <is>
           <t>- Updated all spec task files to reflect actual completion status.
 - Renamed inventory project from resources-inventory to infrastructure-inventory across Lambda names, CloudFormation stacks, documentation, and URLs.</t>
         </is>
       </c>
-      <c r="E148" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F148" s="8" t="n"/>
-    </row>
-    <row r="149" ht="143" customHeight="1">
-      <c r="A149" s="8" t="n"/>
-      <c r="B149" s="8" t="n"/>
-      <c r="C149" s="9" t="inlineStr">
+      <c r="E216" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F216" s="8" t="n"/>
+    </row>
+    <row r="217" ht="143" customHeight="1">
+      <c r="A217" s="8" t="n"/>
+      <c r="B217" s="8" t="n"/>
+      <c r="C217" s="9" t="inlineStr">
         <is>
           <t>X-Ray Trace ID Single-Click Fix &amp; Comprehensive Team Requests</t>
         </is>
       </c>
-      <c r="D149" s="9" t="inlineStr">
+      <c r="D217" s="9" t="inlineStr">
         <is>
           <t>- Fixed X-Ray Recent Traces table to use a single plugin-provided trace link on the ID field — removes the custom data link that was causing a popup instead of direct navigation.
 - Added comprehensive X-Ray instrumentation guides for all 13 monitored services, including ready-to-paste Kiro prompts for each team to generate their own instrumentation specs.</t>
         </is>
       </c>
-      <c r="E149" s="10" t="n">
+      <c r="E217" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="F149" s="8" t="n"/>
-    </row>
-    <row r="150" ht="143" customHeight="1">
-      <c r="A150" s="8" t="n"/>
-      <c r="B150" s="8" t="n"/>
-      <c r="C150" s="9" t="inlineStr">
+      <c r="F217" s="8" t="n"/>
+    </row>
+    <row r="218" ht="143" customHeight="1">
+      <c r="A218" s="8" t="n"/>
+      <c r="B218" s="8" t="n"/>
+      <c r="C218" s="9" t="inlineStr">
         <is>
           <t>Composite Alarm Docs, Noise Reduction Specs &amp; Team Requests</t>
         </is>
       </c>
-      <c r="D150" s="9" t="inlineStr">
+      <c r="D218" s="9" t="inlineStr">
         <is>
           <t>- Documented all 6 active composite alarms with naming conventions, suppression behavior, and configuration examples.
 - Added 4 alarm noise reduction specs: notification grouping (platform digest emails), progressive backoff, quiet hours for maintenance windows, and alarm acknowledgement with DynamoDB TTL.
@@ -4253,76 +5185,76 @@
 - Expanded structured logging rationale with comparison table, structlog/Powertools code examples, and required SRE observability fields.</t>
         </is>
       </c>
-      <c r="E150" s="10" t="n">
+      <c r="E218" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="F150" s="8" t="n"/>
-    </row>
-    <row r="151" ht="143" customHeight="1">
-      <c r="A151" s="8" t="n"/>
-      <c r="B151" s="8" t="n"/>
-      <c r="C151" s="9" t="inlineStr">
+      <c r="F218" s="8" t="n"/>
+    </row>
+    <row r="219" ht="143" customHeight="1">
+      <c r="A219" s="8" t="n"/>
+      <c r="B219" s="8" t="n"/>
+      <c r="C219" s="9" t="inlineStr">
         <is>
           <t>Log Group Observability Spec &amp; Saved Queries Script</t>
         </is>
       </c>
-      <c r="D151" s="9" t="inlineStr">
+      <c r="D219" s="9" t="inlineStr">
         <is>
           <t>- Added log group observability spec covering 5 phases: discoverer, API endpoint, alarm email log links, Grafana CloudWatch Logs panel, and CloudWatch saved queries per platform.
 - Built saved queries script creating 30 CloudWatch Logs Insights saved queries per platform (errors, Lambda cold starts, timeouts, OOM, ECS task failures, OpenSearch slow queries).
 - Added log group URL utility for CloudWatch Console deep links, service type classification, and alarm-to-log-group matching.</t>
         </is>
       </c>
-      <c r="E151" s="10" t="n">
+      <c r="E219" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="F151" s="8" t="n"/>
-    </row>
-    <row r="152" ht="143" customHeight="1">
-      <c r="A152" s="8" t="n"/>
-      <c r="B152" s="8" t="n"/>
-      <c r="C152" s="9" t="inlineStr">
+      <c r="F219" s="8" t="n"/>
+    </row>
+    <row r="220" ht="143" customHeight="1">
+      <c r="A220" s="8" t="n"/>
+      <c r="B220" s="8" t="n"/>
+      <c r="C220" s="9" t="inlineStr">
         <is>
           <t>Log Group Discovery Spec</t>
         </is>
       </c>
-      <c r="D152" s="9" t="inlineStr">
+      <c r="D220" s="9" t="inlineStr">
         <is>
           <t>- Added log group discovery spec to inventory repo covering the new LogGroupDiscoverer and /platforms/{platform}/log-groups API endpoint.</t>
         </is>
       </c>
-      <c r="E152" s="10" t="n">
+      <c r="E220" s="10" t="n">
         <v>1.5</v>
       </c>
-      <c r="F152" s="8" t="n"/>
-    </row>
-    <row r="153" ht="143" customHeight="1">
-      <c r="A153" s="8" t="n"/>
-      <c r="B153" s="8" t="n"/>
-      <c r="C153" s="9" t="inlineStr">
+      <c r="F220" s="8" t="n"/>
+    </row>
+    <row r="221" ht="143" customHeight="1">
+      <c r="A221" s="8" t="n"/>
+      <c r="B221" s="8" t="n"/>
+      <c r="C221" s="9" t="inlineStr">
         <is>
           <t>OpenAPI Title Fix</t>
         </is>
       </c>
-      <c r="D153" s="9" t="inlineStr">
+      <c r="D221" s="9" t="inlineStr">
         <is>
           <t>- Updated OpenAPI title assertion test to match renamed infrastructure-inventory service.</t>
         </is>
       </c>
-      <c r="E153" s="10" t="n">
+      <c r="E221" s="10" t="n">
         <v>2.25</v>
       </c>
-      <c r="F153" s="8" t="n"/>
-    </row>
-    <row r="154" ht="143" customHeight="1">
-      <c r="A154" s="11" t="n"/>
-      <c r="B154" s="11" t="n"/>
-      <c r="C154" s="24" t="inlineStr">
+      <c r="F221" s="8" t="n"/>
+    </row>
+    <row r="222" ht="143" customHeight="1">
+      <c r="A222" s="11" t="n"/>
+      <c r="B222" s="11" t="n"/>
+      <c r="C222" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D154" s="25" t="inlineStr">
+      <c r="D222" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (9 meetings, 2.5h):
 - 1:1 with Manager (Deotale) (30 min)
@@ -4336,28 +5268,28 @@
 - Daily Standup - Innovation IT (30 min)</t>
         </is>
       </c>
-      <c r="E154" s="26" t="n">
+      <c r="E222" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="F154" s="11" t="n"/>
-    </row>
-    <row r="155" ht="143" customHeight="1">
-      <c r="A155" s="14" t="inlineStr">
+      <c r="F222" s="11" t="n"/>
+    </row>
+    <row r="223" ht="143" customHeight="1">
+      <c r="A223" s="14" t="inlineStr">
         <is>
           <t>Week 20</t>
         </is>
       </c>
-      <c r="B155" s="15" t="inlineStr">
+      <c r="B223" s="15" t="inlineStr">
         <is>
           <t>Jul 27 – Jul 31, 2026</t>
         </is>
       </c>
-      <c r="C155" s="27" t="inlineStr">
+      <c r="C223" s="27" t="inlineStr">
         <is>
           <t>RPA Production Support Shift</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D223" s="6" t="inlineStr">
         <is>
           <t>- Reviewed APAC handover log and opened the SD Portal queue for the start of Week 20 rotation.
 - FX Closeout SD# 15285857 and SD# 15285410: Handled FX Closeout processing requests. Checked UiPath PortfolioDataops/DATAOPS-FX-CLOSEOUT folder for each client. Verified Daily565 folder — found old rep
@@ -4373,23 +5305,149 @@
 - Reviewed APAC handover log and SD Portal queue; followed up on SD# 15285347 (ASPECT client) — awaiting confirmation from Harsha on column updates.</t>
         </is>
       </c>
-      <c r="E155" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="F155" s="14">
-        <f>SUM(E155:E158)</f>
+      <c r="E223" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F223" s="14">
+        <f>SUM(E223:E235)</f>
         <v/>
       </c>
     </row>
-    <row r="156" ht="143" customHeight="1">
-      <c r="A156" s="18" t="n"/>
-      <c r="B156" s="18" t="n"/>
-      <c r="C156" s="9" t="inlineStr">
+    <row r="224" ht="143" customHeight="1">
+      <c r="A224" s="18" t="n"/>
+      <c r="B224" s="18" t="n"/>
+      <c r="C224" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D224" s="9" t="inlineStr"/>
+      <c r="E224" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F224" s="18" t="n"/>
+    </row>
+    <row r="225" ht="143" customHeight="1">
+      <c r="A225" s="18" t="n"/>
+      <c r="B225" s="18" t="n"/>
+      <c r="C225" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D225" s="9" t="inlineStr"/>
+      <c r="E225" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F225" s="18" t="n"/>
+    </row>
+    <row r="226" ht="143" customHeight="1">
+      <c r="A226" s="18" t="n"/>
+      <c r="B226" s="18" t="n"/>
+      <c r="C226" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D226" s="9" t="inlineStr"/>
+      <c r="E226" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F226" s="18" t="n"/>
+    </row>
+    <row r="227" ht="143" customHeight="1">
+      <c r="A227" s="18" t="n"/>
+      <c r="B227" s="18" t="n"/>
+      <c r="C227" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D227" s="9" t="inlineStr"/>
+      <c r="E227" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F227" s="18" t="n"/>
+    </row>
+    <row r="228" ht="143" customHeight="1">
+      <c r="A228" s="18" t="n"/>
+      <c r="B228" s="18" t="n"/>
+      <c r="C228" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D228" s="9" t="inlineStr"/>
+      <c r="E228" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F228" s="18" t="n"/>
+    </row>
+    <row r="229" ht="143" customHeight="1">
+      <c r="A229" s="18" t="n"/>
+      <c r="B229" s="18" t="n"/>
+      <c r="C229" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D229" s="9" t="inlineStr"/>
+      <c r="E229" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F229" s="18" t="n"/>
+    </row>
+    <row r="230" ht="143" customHeight="1">
+      <c r="A230" s="18" t="n"/>
+      <c r="B230" s="18" t="n"/>
+      <c r="C230" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D230" s="9" t="inlineStr"/>
+      <c r="E230" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F230" s="18" t="n"/>
+    </row>
+    <row r="231" ht="143" customHeight="1">
+      <c r="A231" s="18" t="n"/>
+      <c r="B231" s="18" t="n"/>
+      <c r="C231" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D231" s="9" t="inlineStr"/>
+      <c r="E231" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F231" s="18" t="n"/>
+    </row>
+    <row r="232" ht="143" customHeight="1">
+      <c r="A232" s="18" t="n"/>
+      <c r="B232" s="18" t="n"/>
+      <c r="C232" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D232" s="9" t="inlineStr"/>
+      <c r="E232" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F232" s="18" t="n"/>
+    </row>
+    <row r="233" ht="143" customHeight="1">
+      <c r="A233" s="18" t="n"/>
+      <c r="B233" s="18" t="n"/>
+      <c r="C233" s="9" t="inlineStr">
         <is>
           <t>Development Work During Support Week</t>
         </is>
       </c>
-      <c r="D156" s="9" t="inlineStr">
+      <c r="D233" s="9" t="inlineStr">
         <is>
           <t>- Created new ia_meso_process repository for distributed tracing work — added Kiro steering files for project conventions (IISS-837).
 - Added Lambda Powertools X-Ray tracing spec (IISS-838) — defines approach for Lambda function distributed tracing using aws-lambda-powertools[tracer].
@@ -4403,20 +5461,20 @@
 - Added steering rule requiring descriptive messages for all git tags.</t>
         </is>
       </c>
-      <c r="E156" s="10" t="n">
+      <c r="E233" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F156" s="18" t="n"/>
-    </row>
-    <row r="157" ht="143" customHeight="1">
-      <c r="A157" s="18" t="n"/>
-      <c r="B157" s="18" t="n"/>
-      <c r="C157" s="9" t="inlineStr">
+      <c r="F233" s="18" t="n"/>
+    </row>
+    <row r="234" ht="143" customHeight="1">
+      <c r="A234" s="18" t="n"/>
+      <c r="B234" s="18" t="n"/>
+      <c r="C234" s="9" t="inlineStr">
         <is>
           <t>ia_meso_process X-Ray Tracing</t>
         </is>
       </c>
-      <c r="D157" s="9" t="inlineStr">
+      <c r="D234" s="9" t="inlineStr">
         <is>
           <t>- Created new ia_meso_process repository for distributed tracing work — added Kiro steering files for project conventions (IISS-837).
 - Added Lambda Powertools X-Ray tracing spec (IISS-838) — defines approach for Lambda function distributed tracing using aws-lambda-powertools[tracer].
@@ -4426,88 +5484,116 @@
 - Added EC2 standalone instance tracing spec (IISS-844) — defines tracing for non-containerised EC2 workloads.</t>
         </is>
       </c>
-      <c r="E157" s="10" t="n">
+      <c r="E234" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F157" s="18" t="n"/>
-    </row>
-    <row r="158" ht="143" customHeight="1">
-      <c r="A158" s="21" t="n"/>
-      <c r="B158" s="21" t="n"/>
-      <c r="C158" s="12" t="inlineStr">
+      <c r="F234" s="18" t="n"/>
+    </row>
+    <row r="235" ht="143" customHeight="1">
+      <c r="A235" s="21" t="n"/>
+      <c r="B235" s="21" t="n"/>
+      <c r="C235" s="12" t="inlineStr">
         <is>
           <t>Log Group Discovery Feature Merge</t>
         </is>
       </c>
-      <c r="D158" s="12" t="inlineStr">
+      <c r="D235" s="12" t="inlineStr">
         <is>
           <t>- Added temp/ to .gitignore to prevent local working files from being accidentally committed.
 - Merged feature/IISS-487-log-group-discovery — includes composite alarms, saved queries script, and log group URL utilities built on July 24.</t>
         </is>
       </c>
-      <c r="E158" s="13" t="n">
+      <c r="E235" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F158" s="21" t="n"/>
-    </row>
-    <row r="159" ht="143" customHeight="1">
-      <c r="A159" s="4" t="inlineStr">
+      <c r="F235" s="21" t="n"/>
+    </row>
+    <row r="236" ht="143" customHeight="1">
+      <c r="A236" s="4" t="inlineStr">
         <is>
           <t>Week 21</t>
         </is>
       </c>
-      <c r="B159" s="5" t="inlineStr">
+      <c r="B236" s="5" t="inlineStr">
         <is>
           <t>Aug 03 – Aug 07, 2026</t>
         </is>
       </c>
-      <c r="C159" s="6" t="inlineStr">
+      <c r="C236" s="6" t="inlineStr">
         <is>
           <t>Development &amp; Implementation</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
+      <c r="D236" s="6" t="inlineStr">
         <is>
           <t>- Continued development work and implementation tasks.</t>
         </is>
       </c>
-      <c r="E159" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F159" s="4">
-        <f>SUM(E159:E172)</f>
+      <c r="E236" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F236" s="4">
+        <f>SUM(E236:E252)</f>
         <v/>
       </c>
     </row>
-    <row r="160" ht="143" customHeight="1">
-      <c r="A160" s="8" t="n"/>
-      <c r="B160" s="8" t="n"/>
-      <c r="C160" s="9" t="inlineStr">
+    <row r="237" ht="143" customHeight="1">
+      <c r="A237" s="8" t="n"/>
+      <c r="B237" s="8" t="n"/>
+      <c r="C237" s="9" t="inlineStr">
+        <is>
+          <t>Development &amp; Implementation</t>
+        </is>
+      </c>
+      <c r="D237" s="9" t="inlineStr"/>
+      <c r="E237" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F237" s="8" t="n"/>
+    </row>
+    <row r="238" ht="143" customHeight="1">
+      <c r="A238" s="8" t="n"/>
+      <c r="B238" s="8" t="n"/>
+      <c r="C238" s="9" t="inlineStr">
         <is>
           <t>Knowledge Base Organisation &amp; Documentation</t>
         </is>
       </c>
-      <c r="D160" s="9" t="inlineStr">
+      <c r="D238" s="9" t="inlineStr">
         <is>
           <t>- Added comprehensive dev JIRA summary, timeline, and incident report to the knowledge base.
 - Added .kiro/settings to gitignore for clean repository hygiene.
 - Organised knowledge base structure with onboarding, infra, dashboard, and RPA support sections.</t>
         </is>
       </c>
-      <c r="E160" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F160" s="8" t="n"/>
-    </row>
-    <row r="161" ht="143" customHeight="1">
-      <c r="A161" s="8" t="n"/>
-      <c r="B161" s="8" t="n"/>
-      <c r="C161" s="9" t="inlineStr">
+      <c r="E238" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F238" s="8" t="n"/>
+    </row>
+    <row r="239" ht="143" customHeight="1">
+      <c r="A239" s="8" t="n"/>
+      <c r="B239" s="8" t="n"/>
+      <c r="C239" s="9" t="inlineStr">
+        <is>
+          <t>Knowledge Base Organisation &amp; Documentation</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="inlineStr"/>
+      <c r="E239" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F239" s="8" t="n"/>
+    </row>
+    <row r="240" ht="143" customHeight="1">
+      <c r="A240" s="8" t="n"/>
+      <c r="B240" s="8" t="n"/>
+      <c r="C240" s="9" t="inlineStr">
         <is>
           <t>LLM Agent Critical Bug Fixes, Memory Increase &amp; SSL/Timeout Reliabilit</t>
         </is>
       </c>
-      <c r="D161" s="9" t="inlineStr">
+      <c r="D240" s="9" t="inlineStr">
         <is>
           <t>- Added FastAPI improvements documentation and modern Python project structure migration plan.
 - Rewrote README to reflect current FastAPI application state.
@@ -4519,58 +5605,58 @@
 - Added event-service-reliability-fixes spec and Python .gitignore.</t>
         </is>
       </c>
-      <c r="E161" s="10" t="n">
+      <c r="E240" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F161" s="8" t="n"/>
-    </row>
-    <row r="162" ht="143" customHeight="1">
-      <c r="A162" s="8" t="n"/>
-      <c r="B162" s="8" t="n"/>
-      <c r="C162" s="9" t="inlineStr">
+      <c r="F240" s="8" t="n"/>
+    </row>
+    <row r="241" ht="143" customHeight="1">
+      <c r="A241" s="8" t="n"/>
+      <c r="B241" s="8" t="n"/>
+      <c r="C241" s="9" t="inlineStr">
         <is>
           <t>S3 Rename, Service Name Standardisation &amp; Spec Cleanup</t>
         </is>
       </c>
-      <c r="D162" s="9" t="inlineStr">
+      <c r="D241" s="9" t="inlineStr">
         <is>
           <t>- Renamed S3 bucket from resources-monitoring to infrastructure-monitoring; updated repo name to ia-it-sre-infrastructure-monitoring-amg.
 - Cleaned up stale meridian- stack names; deleted old row_10_ecs_apis S3 objects.
 - Audited and tracked .kiro/specs in git.</t>
         </is>
       </c>
-      <c r="E162" s="10" t="n">
+      <c r="E241" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F162" s="8" t="n"/>
-    </row>
-    <row r="163" ht="143" customHeight="1">
-      <c r="A163" s="8" t="n"/>
-      <c r="B163" s="8" t="n"/>
-      <c r="C163" s="9" t="inlineStr">
+      <c r="F241" s="8" t="n"/>
+    </row>
+    <row r="242" ht="143" customHeight="1">
+      <c r="A242" s="8" t="n"/>
+      <c r="B242" s="8" t="n"/>
+      <c r="C242" s="9" t="inlineStr">
         <is>
           <t>S3 Rename &amp; Initial Spec Audit</t>
         </is>
       </c>
-      <c r="D163" s="9" t="inlineStr">
+      <c r="D242" s="9" t="inlineStr">
         <is>
           <t>- Renamed S3 bucket; moved Flask to dev dependencies; audited spec task completion.</t>
         </is>
       </c>
-      <c r="E163" s="10" t="n">
+      <c r="E242" s="10" t="n">
         <v>2.75</v>
       </c>
-      <c r="F163" s="8" t="n"/>
-    </row>
-    <row r="164" ht="143" customHeight="1">
-      <c r="A164" s="8" t="n"/>
-      <c r="B164" s="8" t="n"/>
-      <c r="C164" s="9" t="inlineStr">
+      <c r="F242" s="8" t="n"/>
+    </row>
+    <row r="243" ht="143" customHeight="1">
+      <c r="A243" s="8" t="n"/>
+      <c r="B243" s="8" t="n"/>
+      <c r="C243" s="9" t="inlineStr">
         <is>
           <t>Mapper Stack Cleanup, Service Rename &amp; .env Cleanup</t>
         </is>
       </c>
-      <c r="D164" s="9" t="inlineStr">
+      <c r="D243" s="9" t="inlineStr">
         <is>
           <t>- Deleted resource mapper stack and all related stale scripts/docs after migrating to inventory API.
 - Marked superseded specs; renamed dashboard title and service/app name to ia-it-sre-infrastructure-monitoring-amg.
@@ -4578,20 +5664,20 @@
 - Updated AWS_CA_BUNDLE guidance to use Windows user environment variable.</t>
         </is>
       </c>
-      <c r="E164" s="10" t="n">
+      <c r="E243" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F164" s="8" t="n"/>
-    </row>
-    <row r="165" ht="143" customHeight="1">
-      <c r="A165" s="8" t="n"/>
-      <c r="B165" s="8" t="n"/>
-      <c r="C165" s="9" t="inlineStr">
+      <c r="F243" s="8" t="n"/>
+    </row>
+    <row r="244" ht="143" customHeight="1">
+      <c r="A244" s="8" t="n"/>
+      <c r="B244" s="8" t="n"/>
+      <c r="C244" s="9" t="inlineStr">
         <is>
           <t>Spec Closures, CW Metrics Live, IAM Fix &amp; Retire Mappers</t>
         </is>
       </c>
-      <c r="D165" s="9" t="inlineStr">
+      <c r="D244" s="9" t="inlineStr">
         <is>
           <t>- Marked specs complete: ECS target group discovery Phase 5, CloudFront S3 proxy phases 1-3, lambda-api-migration tasks N/A.
 - Added retire-mappers spec; Phase 4 complete — mapper stack deleted.
@@ -4599,59 +5685,59 @@
 - Fixed elasticloadbalancing IAM permissions; renamed stack to infrastructure-inventory.</t>
         </is>
       </c>
-      <c r="E165" s="10" t="n">
+      <c r="E244" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F165" s="8" t="n"/>
-    </row>
-    <row r="166" ht="143" customHeight="1">
-      <c r="A166" s="8" t="n"/>
-      <c r="B166" s="8" t="n"/>
-      <c r="C166" s="9" t="inlineStr">
+      <c r="F244" s="8" t="n"/>
+    </row>
+    <row r="245" ht="143" customHeight="1">
+      <c r="A245" s="8" t="n"/>
+      <c r="B245" s="8" t="n"/>
+      <c r="C245" s="9" t="inlineStr">
         <is>
           <t>CloudWatch Log Group Discoverer (row_16)</t>
         </is>
       </c>
-      <c r="D166" s="9" t="inlineStr">
+      <c r="D245" s="9" t="inlineStr">
         <is>
           <t>- Added CloudWatch Log Group discoverer (row_16) to the infrastructure inventory API.
 - Merged inventory-tasks feature branch covering cache guard improvements, log-group discovery, and spec audits.</t>
         </is>
       </c>
-      <c r="E166" s="10" t="n">
+      <c r="E245" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F166" s="8" t="n"/>
-    </row>
-    <row r="167" ht="143" customHeight="1">
-      <c r="A167" s="8" t="n"/>
-      <c r="B167" s="8" t="n"/>
-      <c r="C167" s="9" t="inlineStr">
+      <c r="F245" s="8" t="n"/>
+    </row>
+    <row r="246" ht="143" customHeight="1">
+      <c r="A246" s="8" t="n"/>
+      <c r="B246" s="8" t="n"/>
+      <c r="C246" s="9" t="inlineStr">
         <is>
           <t>API Stack Rename Spec &amp; Implementation</t>
         </is>
       </c>
-      <c r="D167" s="9" t="inlineStr">
+      <c r="D246" s="9" t="inlineStr">
         <is>
           <t>- Added api-stack-rename spec with detailed task list.
 - Renamed inventory API CloudFormation stack to infrastructure-inventory naming convention.
 - Added force-update mechanism for Lambda deployments.</t>
         </is>
       </c>
-      <c r="E167" s="10" t="n">
+      <c r="E246" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F167" s="8" t="n"/>
-    </row>
-    <row r="168" ht="143" customHeight="1">
-      <c r="A168" s="8" t="n"/>
-      <c r="B168" s="8" t="n"/>
-      <c r="C168" s="9" t="inlineStr">
+      <c r="F246" s="8" t="n"/>
+    </row>
+    <row r="247" ht="143" customHeight="1">
+      <c r="A247" s="8" t="n"/>
+      <c r="B247" s="8" t="n"/>
+      <c r="C247" s="9" t="inlineStr">
         <is>
           <t>LLM Agent Major Refactor</t>
         </is>
       </c>
-      <c r="D168" s="9" t="inlineStr">
+      <c r="D247" s="9" t="inlineStr">
         <is>
           <t>- Added pyproject.toml, requirements/ folder, .env.example; archived dead code; externalised WIKI_LIBRARIES to S3 JSON config.
 - Added Kiro hooks and quality gates to buildspec; added idempotent KB sync with SharePoint Modified timestamp detection (Phase 1).
@@ -4662,38 +5748,38 @@
 - Renamed secrets.py → event_service_secrets.py; fixed 96 ruff lint issues automatically.</t>
         </is>
       </c>
-      <c r="E168" s="10" t="n">
+      <c r="E247" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F168" s="8" t="n"/>
-    </row>
-    <row r="169" ht="143" customHeight="1">
-      <c r="A169" s="8" t="n"/>
-      <c r="B169" s="8" t="n"/>
-      <c r="C169" s="9" t="inlineStr">
+      <c r="F247" s="8" t="n"/>
+    </row>
+    <row r="248" ht="143" customHeight="1">
+      <c r="A248" s="8" t="n"/>
+      <c r="B248" s="8" t="n"/>
+      <c r="C248" s="9" t="inlineStr">
         <is>
           <t>ECS Task Allocation Prod Alignment</t>
         </is>
       </c>
-      <c r="D169" s="9" t="inlineStr">
+      <c r="D248" s="9" t="inlineStr">
         <is>
           <t>- Fixed ECS task-level CPU and memory allocation to match container limits (512 CPU / 1024MB) and align exactly with production. Bumped to v1.1.55.</t>
         </is>
       </c>
-      <c r="E169" s="10" t="n">
+      <c r="E248" s="10" t="n">
         <v>1.25</v>
       </c>
-      <c r="F169" s="8" t="n"/>
-    </row>
-    <row r="170" ht="143" customHeight="1">
-      <c r="A170" s="8" t="n"/>
-      <c r="B170" s="8" t="n"/>
-      <c r="C170" s="9" t="inlineStr">
+      <c r="F248" s="8" t="n"/>
+    </row>
+    <row r="249" ht="143" customHeight="1">
+      <c r="A249" s="8" t="n"/>
+      <c r="B249" s="8" t="n"/>
+      <c r="C249" s="9" t="inlineStr">
         <is>
           <t>handler_utils Decorators, SRP Refactor, CFN Nested Stack &amp; 233 Tests</t>
         </is>
       </c>
-      <c r="D170" s="9" t="inlineStr">
+      <c r="D249" s="9" t="inlineStr">
         <is>
           <t>- Reached 199 tests with 100% coverage; built shared handler_utils with log_handler, scheduled_handler, cfn_handler decorators — applied to all Lambda handlers (v1.1.35, 217 tests).
 - Grew test suite: 199 → 217 → 225 → 233 tests through SRP refactors, type hint completion, CFN response coverage, and ircoekb SRP refactor (v1.1.35–v1.1.39).
@@ -4705,40 +5791,54 @@
 - Standardised .yml → .yaml; removed incorrect S3 object expiry rules to retain KB content indefinitely (v1.1.52–v1.1.53).</t>
         </is>
       </c>
-      <c r="E170" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F170" s="8" t="n"/>
-    </row>
-    <row r="171" ht="143" customHeight="1">
-      <c r="A171" s="8" t="n"/>
-      <c r="B171" s="8" t="n"/>
-      <c r="C171" s="9" t="inlineStr">
+      <c r="E249" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F249" s="8" t="n"/>
+    </row>
+    <row r="250" ht="143" customHeight="1">
+      <c r="A250" s="8" t="n"/>
+      <c r="B250" s="8" t="n"/>
+      <c r="C250" s="9" t="inlineStr">
         <is>
           <t>CW Metrics Spec Complete &amp; Cache Guard</t>
         </is>
       </c>
-      <c r="D171" s="9" t="inlineStr">
+      <c r="D250" s="9" t="inlineStr">
         <is>
           <t>- Updated all four inventory task specs with accurate current state.
 - Marked cloudwatch-metrics-publishing ALL PHASES COMPLETE.
 - Added API-refresh guard to prevent 0-resource cache overwrites.</t>
         </is>
       </c>
-      <c r="E171" s="10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="F171" s="8" t="n"/>
-    </row>
-    <row r="172" ht="143" customHeight="1">
-      <c r="A172" s="11" t="n"/>
-      <c r="B172" s="11" t="n"/>
-      <c r="C172" s="24" t="inlineStr">
+      <c r="E250" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F250" s="8" t="n"/>
+    </row>
+    <row r="251" ht="143" customHeight="1">
+      <c r="A251" s="8" t="n"/>
+      <c r="B251" s="8" t="n"/>
+      <c r="C251" s="9" t="inlineStr">
+        <is>
+          <t>CW Metrics Spec Complete &amp; Cache Guard</t>
+        </is>
+      </c>
+      <c r="D251" s="9" t="inlineStr"/>
+      <c r="E251" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F251" s="8" t="n"/>
+    </row>
+    <row r="252" ht="143" customHeight="1">
+      <c r="A252" s="11" t="n"/>
+      <c r="B252" s="11" t="n"/>
+      <c r="C252" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D172" s="25" t="inlineStr">
+      <c r="D252" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (5 meetings, 1.5h):
 - Daily Standup - Innovation IT (30 min)
@@ -4748,28 +5848,28 @@
 - Daily Standup - Innovation IT (30 min)</t>
         </is>
       </c>
-      <c r="E172" s="26" t="n">
+      <c r="E252" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="F172" s="11" t="n"/>
-    </row>
-    <row r="173" ht="143" customHeight="1">
-      <c r="A173" s="14" t="inlineStr">
+      <c r="F252" s="11" t="n"/>
+    </row>
+    <row r="253" ht="143" customHeight="1">
+      <c r="A253" s="14" t="inlineStr">
         <is>
           <t>Week 22</t>
         </is>
       </c>
-      <c r="B173" s="15" t="inlineStr">
+      <c r="B253" s="15" t="inlineStr">
         <is>
           <t>Aug 10 – Aug 14, 2026</t>
         </is>
       </c>
-      <c r="C173" s="16" t="inlineStr">
+      <c r="C253" s="16" t="inlineStr">
         <is>
           <t>KB Content Upload Script, Bedrock Agent Instruction Externalisation &amp;</t>
         </is>
       </c>
-      <c r="D173" s="16" t="inlineStr">
+      <c r="D253" s="16" t="inlineStr">
         <is>
           <t>- Added kb-content/ folder structure and upload_kb_content.py script for manually uploading NAV Checklist PDFs to the Bedrock Knowledge Base S3 bucket (v1.1.56).
 - Updated kb-content folder to mirror Confluence hierarchy with faq/ subfolder; upload script now recurses subfolders.
@@ -4781,42 +5881,42 @@
 - Fixed KB sync to always use us-east-1 for sync Lambda regardless of S3 upload region.</t>
         </is>
       </c>
-      <c r="E173" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="F173" s="14">
-        <f>SUM(E173:E181)</f>
+      <c r="E253" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F253" s="14">
+        <f>SUM(E253:E263)</f>
         <v/>
       </c>
     </row>
-    <row r="174" ht="143" customHeight="1">
-      <c r="A174" s="18" t="n"/>
-      <c r="B174" s="18" t="n"/>
-      <c r="C174" s="19" t="inlineStr">
+    <row r="254" ht="143" customHeight="1">
+      <c r="A254" s="18" t="n"/>
+      <c r="B254" s="18" t="n"/>
+      <c r="C254" s="19" t="inlineStr">
         <is>
           <t>API Stack Rename &amp; Force-Update Lambda</t>
         </is>
       </c>
-      <c r="D174" s="19" t="inlineStr">
+      <c r="D254" s="19" t="inlineStr">
         <is>
           <t>- Renamed inventory API CloudFormation stack to infrastructure-inventory naming convention.
 - Added force-update mechanism for Lambda deployments to ensure code changes are always picked up on deploy.</t>
         </is>
       </c>
-      <c r="E174" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F174" s="18" t="n"/>
-    </row>
-    <row r="175" ht="143" customHeight="1">
-      <c r="A175" s="18" t="n"/>
-      <c r="B175" s="18" t="n"/>
-      <c r="C175" s="19" t="inlineStr">
+      <c r="E254" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F254" s="18" t="n"/>
+    </row>
+    <row r="255" ht="143" customHeight="1">
+      <c r="A255" s="18" t="n"/>
+      <c r="B255" s="18" t="n"/>
+      <c r="C255" s="19" t="inlineStr">
         <is>
           <t>Buildspec YAML Fixes, KB Upload CLI Tests &amp; Critical Bug Fixes</t>
         </is>
       </c>
-      <c r="D175" s="19" t="inlineStr">
+      <c r="D255" s="19" t="inlineStr">
         <is>
           <t>- Added 30 unit tests for upload_kb_content.py CLI covering _get_kb_ids, cmd_status, cmd_upload, and main functions.
 - Fixed multiple YAML_FILE_ERROR issues in buildspec.yml — replaced unicode box-drawing characters with ASCII, quoted echo commands containing colons, and replaced ${COMMIT_HASH:=latest} with if/else block.
@@ -4826,20 +5926,34 @@
 - Reverted buildspec.yml to PR 3015 state after multiple failed fix iterations, then applied clean hotfix for update_json.py path (functions/ → scripts/).</t>
         </is>
       </c>
-      <c r="E175" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F175" s="18" t="n"/>
-    </row>
-    <row r="176" ht="143" customHeight="1">
-      <c r="A176" s="18" t="n"/>
-      <c r="B176" s="18" t="n"/>
-      <c r="C176" s="19" t="inlineStr">
+      <c r="E255" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F255" s="18" t="n"/>
+    </row>
+    <row r="256" ht="143" customHeight="1">
+      <c r="A256" s="18" t="n"/>
+      <c r="B256" s="18" t="n"/>
+      <c r="C256" s="19" t="inlineStr">
+        <is>
+          <t>Buildspec YAML Fixes, KB Upload CLI Tests &amp; Critical Bug Fixes</t>
+        </is>
+      </c>
+      <c r="D256" s="19" t="inlineStr"/>
+      <c r="E256" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F256" s="18" t="n"/>
+    </row>
+    <row r="257" ht="143" customHeight="1">
+      <c r="A257" s="18" t="n"/>
+      <c r="B257" s="18" t="n"/>
+      <c r="C257" s="19" t="inlineStr">
         <is>
           <t>Buildspec cp Hotfix, Safe Dict Access &amp; Bedrock Guardrail Streaming Fi</t>
         </is>
       </c>
-      <c r="D176" s="19" t="inlineStr">
+      <c r="D257" s="19" t="inlineStr">
         <is>
           <t>- Fixed buildspec to add cp commands packaging cfn_response.py into Lambda deployment zips — upload, Athena, and OpenSearch functions were failing with ModuleNotFoundError without it.
 - Fixed unsafe dictionary key accesses in event_service — replaced direct key lookups with .get() and try/except guards.
@@ -4850,20 +5964,34 @@
 - Improved streaming guardrail handling to buffer all chunks before sending — if a guardrail fires at any point, the entire partial response is discarded and a clean message is sent instead.</t>
         </is>
       </c>
-      <c r="E176" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="F176" s="18" t="n"/>
-    </row>
-    <row r="177" ht="143" customHeight="1">
-      <c r="A177" s="18" t="n"/>
-      <c r="B177" s="18" t="n"/>
-      <c r="C177" s="19" t="inlineStr">
+      <c r="E257" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F257" s="18" t="n"/>
+    </row>
+    <row r="258" ht="143" customHeight="1">
+      <c r="A258" s="18" t="n"/>
+      <c r="B258" s="18" t="n"/>
+      <c r="C258" s="19" t="inlineStr">
+        <is>
+          <t>Buildspec cp Hotfix, Safe Dict Access &amp; Bedrock Guardrail Streaming Fi</t>
+        </is>
+      </c>
+      <c r="D258" s="19" t="inlineStr"/>
+      <c r="E258" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F258" s="18" t="n"/>
+    </row>
+    <row r="259" ht="143" customHeight="1">
+      <c r="A259" s="18" t="n"/>
+      <c r="B259" s="18" t="n"/>
+      <c r="C259" s="19" t="inlineStr">
         <is>
           <t>ECR Image MVC Refactor, Local Dev Auth &amp; Guardrail Fixes</t>
         </is>
       </c>
-      <c r="D177" s="19" t="inlineStr">
+      <c r="D259" s="19" t="inlineStr">
         <is>
           <t>- Added LOCAL_DEV_USER environment variable to bypass AD authentication for local testing.
 - Added python-dotenv to auto-load .env files — developers no longer need to manually source environment variables.
@@ -4872,20 +6000,20 @@
 - Completed full MVC refactor through three iterations — src/app/ package → root app/ package → full MVC structure with structlog, pydantic-settings, and proper package layout.</t>
         </is>
       </c>
-      <c r="E177" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F177" s="18" t="n"/>
-    </row>
-    <row r="178" ht="143" customHeight="1">
-      <c r="A178" s="18" t="n"/>
-      <c r="B178" s="18" t="n"/>
-      <c r="C178" s="19" t="inlineStr">
+      <c r="E259" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F259" s="18" t="n"/>
+    </row>
+    <row r="260" ht="143" customHeight="1">
+      <c r="A260" s="18" t="n"/>
+      <c r="B260" s="18" t="n"/>
+      <c r="C260" s="19" t="inlineStr">
         <is>
           <t>ircoekb SharePoint Timestamp Sync &amp; BuildSpec CodeBuild Fixes</t>
         </is>
       </c>
-      <c r="D178" s="19" t="inlineStr">
+      <c r="D260" s="19" t="inlineStr">
         <is>
           <t>- Added hash-based idempotent sync for ircoekb KB pages; upgraded to SharePoint Modified timestamp detection (Phase 1).
 - Added ircoekb sync justification with 93-day evidence and retry pattern analysis; moved ircoekb_config.json from scripts/ to data/.
@@ -4896,20 +6024,20 @@
 - Reverted a direct push to main that bypassed the PR process.</t>
         </is>
       </c>
-      <c r="E178" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F178" s="18" t="n"/>
-    </row>
-    <row r="179" ht="143" customHeight="1">
-      <c r="A179" s="18" t="n"/>
-      <c r="B179" s="18" t="n"/>
-      <c r="C179" s="19" t="inlineStr">
+      <c r="E260" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F260" s="18" t="n"/>
+    </row>
+    <row r="261" ht="143" customHeight="1">
+      <c r="A261" s="18" t="n"/>
+      <c r="B261" s="18" t="n"/>
+      <c r="C261" s="19" t="inlineStr">
         <is>
           <t>BuildSpec Pipeline Fixes, ircoekb Local Config &amp; CFN Template Fixes</t>
         </is>
       </c>
-      <c r="D179" s="19" t="inlineStr">
+      <c r="D261" s="19" t="inlineStr">
         <is>
           <t>- Fixed series of buildspec pipeline issues: account ID extraction from ModelName ARN, S3 upload permission gaps (CodeBuild role lacks permissions), and progressively commented out cfn-lint, ruff, bandit, and unit test qua
 - Fixed duplicate BUCKET_NAME environment variable in event_service Lambda CloudFormation template.
@@ -4918,20 +6046,20 @@
 - Fixed YAML template issues and resolved ECSService integer-as-string CloudFormation validation errors.</t>
         </is>
       </c>
-      <c r="E179" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F179" s="18" t="n"/>
-    </row>
-    <row r="180" ht="143" customHeight="1">
-      <c r="A180" s="18" t="n"/>
-      <c r="B180" s="18" t="n"/>
-      <c r="C180" s="19" t="inlineStr">
+      <c r="E261" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F261" s="18" t="n"/>
+    </row>
+    <row r="262" ht="143" customHeight="1">
+      <c r="A262" s="18" t="n"/>
+      <c r="B262" s="18" t="n"/>
+      <c r="C262" s="19" t="inlineStr">
         <is>
           <t>ECR Image MVC Refactor, Docker Hardening, LDAP/CORS Security &amp; Test Su</t>
         </is>
       </c>
-      <c r="D180" s="19" t="inlineStr">
+      <c r="D262" s="19" t="inlineStr">
         <is>
           <t>- Brought in full MVC refactor: app/ package structure with structlog and pydantic-settings.
 - Added improvement plan for v2.0 release.
@@ -4943,20 +6071,20 @@
 - Added .python-version tracking to git following the uv convention.</t>
         </is>
       </c>
-      <c r="E180" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F180" s="18" t="n"/>
-    </row>
-    <row r="181" ht="143" customHeight="1">
-      <c r="A181" s="21" t="n"/>
-      <c r="B181" s="21" t="n"/>
-      <c r="C181" s="24" t="inlineStr">
+      <c r="E262" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F262" s="18" t="n"/>
+    </row>
+    <row r="263" ht="143" customHeight="1">
+      <c r="A263" s="21" t="n"/>
+      <c r="B263" s="21" t="n"/>
+      <c r="C263" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D181" s="25" t="inlineStr">
+      <c r="D263" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (5 meetings, 1.5h):
 - Daily Standup - Innovation IT (30 min)
@@ -4966,28 +6094,28 @@
 - Daily Standup - Innovation IT (30 min)</t>
         </is>
       </c>
-      <c r="E181" s="26" t="n">
+      <c r="E263" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="F181" s="21" t="n"/>
-    </row>
-    <row r="182" ht="143" customHeight="1">
-      <c r="A182" s="4" t="inlineStr">
+      <c r="F263" s="21" t="n"/>
+    </row>
+    <row r="264" ht="143" customHeight="1">
+      <c r="A264" s="4" t="inlineStr">
         <is>
           <t>Week 23</t>
         </is>
       </c>
-      <c r="B182" s="5" t="inlineStr">
+      <c r="B264" s="5" t="inlineStr">
         <is>
           <t>Aug 17 – Aug 21, 2026</t>
         </is>
       </c>
-      <c r="C182" s="6" t="inlineStr">
+      <c r="C264" s="6" t="inlineStr">
         <is>
           <t>MVC Refactor Complete, 280 Tests 100% Coverage &amp; ircoekb Fixes</t>
         </is>
       </c>
-      <c r="D182" s="6" t="inlineStr">
+      <c r="D264" s="6" t="inlineStr">
         <is>
           <t>- Bumped ircoekb Lambda timeout from 300s to 900s to handle longer processing runs.
 - Updated ircoekb improvements documentation with current status and S3 HEAD optimisation.
@@ -4999,81 +6127,81 @@
 - Progressively improved coverage 60% → 99% → 100% with 234 → 247 → 280 tests.</t>
         </is>
       </c>
-      <c r="E182" s="7" t="n">
+      <c r="E264" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F182" s="4">
-        <f>SUM(E182:E197)</f>
+      <c r="F264" s="4">
+        <f>SUM(E264:E280)</f>
         <v/>
       </c>
     </row>
-    <row r="183" ht="143" customHeight="1">
-      <c r="A183" s="8" t="n"/>
-      <c r="B183" s="8" t="n"/>
-      <c r="C183" s="9" t="inlineStr">
+    <row r="265" ht="143" customHeight="1">
+      <c r="A265" s="8" t="n"/>
+      <c r="B265" s="8" t="n"/>
+      <c r="C265" s="9" t="inlineStr">
         <is>
           <t>ECS ADOT Sidecar X-Ray Tracing</t>
         </is>
       </c>
-      <c r="D183" s="9" t="inlineStr">
+      <c r="D265" s="9" t="inlineStr">
         <is>
           <t>- Added spec for ECS ADOT sidecar X-Ray tracing (IISS-839).
 - Added ECS ADOT sidecar CloudFormation snippet and X-Ray config.
 - Wired X-Ray config into config_manager and run.py; merged into release.</t>
         </is>
       </c>
-      <c r="E183" s="10" t="n">
+      <c r="E265" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F183" s="8" t="n"/>
-    </row>
-    <row r="184" ht="143" customHeight="1">
-      <c r="A184" s="8" t="n"/>
-      <c r="B184" s="8" t="n"/>
-      <c r="C184" s="9" t="inlineStr">
+      <c r="F265" s="8" t="n"/>
+    </row>
+    <row r="266" ht="143" customHeight="1">
+      <c r="A266" s="8" t="n"/>
+      <c r="B266" s="8" t="n"/>
+      <c r="C266" s="9" t="inlineStr">
         <is>
           <t>SQS Trace Header Propagation</t>
         </is>
       </c>
-      <c r="D184" s="9" t="inlineStr">
+      <c r="D266" s="9" t="inlineStr">
         <is>
           <t>- Added spec for SQS trace propagation (IISS-842).
 - Implemented X-Ray trace header propagation to SQS producers.
 - Added improvements backlog (6 items) and documented structlog migration strategy for log call standardisation.</t>
         </is>
       </c>
-      <c r="E184" s="10" t="n">
+      <c r="E266" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F184" s="8" t="n"/>
-    </row>
-    <row r="185" ht="143" customHeight="1">
-      <c r="A185" s="8" t="n"/>
-      <c r="B185" s="8" t="n"/>
-      <c r="C185" s="9" t="inlineStr">
+      <c r="F266" s="8" t="n"/>
+    </row>
+    <row r="267" ht="143" customHeight="1">
+      <c r="A267" s="8" t="n"/>
+      <c r="B267" s="8" t="n"/>
+      <c r="C267" s="9" t="inlineStr">
         <is>
           <t>ia_infrastructure_dashboard Initial Commit</t>
         </is>
       </c>
-      <c r="D185" s="9" t="inlineStr">
+      <c r="D267" s="9" t="inlineStr">
         <is>
           <t>- Created initial commit for the new ia_infrastructure_dashboard BitBucket repository — the Enterprise Custom UI / Infrastructure Monitoring Dashboard (IISS-919).</t>
         </is>
       </c>
-      <c r="E185" s="10" t="n">
+      <c r="E267" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F185" s="8" t="n"/>
-    </row>
-    <row r="186" ht="143" customHeight="1">
-      <c r="A186" s="8" t="n"/>
-      <c r="B186" s="8" t="n"/>
-      <c r="C186" s="9" t="inlineStr">
+      <c r="F267" s="8" t="n"/>
+    </row>
+    <row r="268" ht="143" customHeight="1">
+      <c r="A268" s="8" t="n"/>
+      <c r="B268" s="8" t="n"/>
+      <c r="C268" s="9" t="inlineStr">
         <is>
           <t>Agent Instruction Externalisation, Usage Report Redesign, CFN Nested S</t>
         </is>
       </c>
-      <c r="D186" s="9" t="inlineStr">
+      <c r="D268" s="9" t="inlineStr">
         <is>
           <t>- Externalised Bedrock Agent instruction to agent_instruction.txt in agent/ folder; fixed buildspec to upload via UploadFileFunction (no cross-account S3).
 - Replaced .format() calls with f-strings; migrated upload and opensearch Lambda packages to structlog.
@@ -5085,20 +6213,34 @@
 - Cleaned up repository: removed stale dependencies/, redundant conftest.py, generated HTML reports, and leftover PR docs.</t>
         </is>
       </c>
-      <c r="E186" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F186" s="8" t="n"/>
-    </row>
-    <row r="187" ht="143" customHeight="1">
-      <c r="A187" s="8" t="n"/>
-      <c r="B187" s="8" t="n"/>
-      <c r="C187" s="9" t="inlineStr">
+      <c r="E268" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F268" s="8" t="n"/>
+    </row>
+    <row r="269" ht="143" customHeight="1">
+      <c r="A269" s="8" t="n"/>
+      <c r="B269" s="8" t="n"/>
+      <c r="C269" s="9" t="inlineStr">
+        <is>
+          <t>Agent Instruction Externalisation, Usage Report Redesign, CFN Nested S</t>
+        </is>
+      </c>
+      <c r="D269" s="9" t="inlineStr"/>
+      <c r="E269" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F269" s="8" t="n"/>
+    </row>
+    <row r="270" ht="143" customHeight="1">
+      <c r="A270" s="8" t="n"/>
+      <c r="B270" s="8" t="n"/>
+      <c r="C270" s="9" t="inlineStr">
         <is>
           <t>Lambda Powertools X-Ray Tracer Instrumentation</t>
         </is>
       </c>
-      <c r="D187" s="9" t="inlineStr">
+      <c r="D270" s="9" t="inlineStr">
         <is>
           <t>- Created spec for Lambda Powertools X-Ray Tracer instrumentation.
 - Added @tracer.capture_lambda_handler and @tracer.capture_method decorators to all Lambda functions.
@@ -5106,20 +6248,20 @@
 - Added tracing.md documenting all decorated and undecorated functions with rationale.</t>
         </is>
       </c>
-      <c r="E187" s="10" t="n">
+      <c r="E270" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F187" s="8" t="n"/>
-    </row>
-    <row r="188" ht="143" customHeight="1">
-      <c r="A188" s="8" t="n"/>
-      <c r="B188" s="8" t="n"/>
-      <c r="C188" s="9" t="inlineStr">
+      <c r="F270" s="8" t="n"/>
+    </row>
+    <row r="271" ht="143" customHeight="1">
+      <c r="A271" s="8" t="n"/>
+      <c r="B271" s="8" t="n"/>
+      <c r="C271" s="9" t="inlineStr">
         <is>
           <t>Docs Diagrams, ircoekb Hybrid Sync, Pydantic Models, Kill Switch, Retr</t>
         </is>
       </c>
-      <c r="D188" s="9" t="inlineStr">
+      <c r="D271" s="9" t="inlineStr">
         <is>
           <t>- Upgraded all plain-text docs to box-drawing ASCII art with consistent 2-space padding; added Mermaid diagrams (neo dark theme) to architecture, chunking, and vector-search docs.
 - Added script to fetch IRCOEKB production logs; collected PROD summary data for Aug 15-19.
@@ -5131,56 +6273,56 @@
 - Added tenacity exponential backoff retry logic to all external API calls.</t>
         </is>
       </c>
-      <c r="E188" s="10" t="n">
+      <c r="E271" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F188" s="8" t="n"/>
-    </row>
-    <row r="189" ht="143" customHeight="1">
-      <c r="A189" s="8" t="n"/>
-      <c r="B189" s="8" t="n"/>
-      <c r="C189" s="9" t="inlineStr">
+      <c r="F271" s="8" t="n"/>
+    </row>
+    <row r="272" ht="143" customHeight="1">
+      <c r="A272" s="8" t="n"/>
+      <c r="B272" s="8" t="n"/>
+      <c r="C272" s="9" t="inlineStr">
         <is>
           <t>Dedicated Log Groups API Endpoint</t>
         </is>
       </c>
-      <c r="D189" s="9" t="inlineStr">
+      <c r="D272" s="9" t="inlineStr">
         <is>
           <t>- Added dedicated GET /api/log-groups endpoint to the inventory API — serves log group data for the alarm email log links and Grafana CloudWatch Logs panel (IISS-845 Phase 2).</t>
         </is>
       </c>
-      <c r="E189" s="10" t="n">
+      <c r="E272" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F189" s="8" t="n"/>
-    </row>
-    <row r="190" ht="143" customHeight="1">
-      <c r="A190" s="8" t="n"/>
-      <c r="B190" s="8" t="n"/>
-      <c r="C190" s="9" t="inlineStr">
+      <c r="F272" s="8" t="n"/>
+    </row>
+    <row r="273" ht="143" customHeight="1">
+      <c r="A273" s="8" t="n"/>
+      <c r="B273" s="8" t="n"/>
+      <c r="C273" s="9" t="inlineStr">
         <is>
           <t>ECS ADOT Sidecar Instrumentation Spec</t>
         </is>
       </c>
-      <c r="D190" s="9" t="inlineStr">
+      <c r="D273" s="9" t="inlineStr">
         <is>
           <t>- Added ECS ADOT sidecar instrumentation spec and task list to the ECR image repo.</t>
         </is>
       </c>
-      <c r="E190" s="10" t="n">
+      <c r="E273" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F190" s="8" t="n"/>
-    </row>
-    <row r="191" ht="143" customHeight="1">
-      <c r="A191" s="8" t="n"/>
-      <c r="B191" s="8" t="n"/>
-      <c r="C191" s="9" t="inlineStr">
+      <c r="F273" s="8" t="n"/>
+    </row>
+    <row r="274" ht="143" customHeight="1">
+      <c r="A274" s="8" t="n"/>
+      <c r="B274" s="8" t="n"/>
+      <c r="C274" s="9" t="inlineStr">
         <is>
           <t>Docs Overhaul, Composite Re-Notification &amp; Citco SES HTML Emails</t>
         </is>
       </c>
-      <c r="D191" s="9" t="inlineStr">
+      <c r="D274" s="9" t="inlineStr">
         <is>
           <t>- Completed comprehensive documentation overhaul — updated all docs to reflect current repo state, fixed inventory row numbers, added ECR/EKS/ECS Target Groups inventory docs, removed duplicates, renamed folders.
 - Decommissioned mapper Lambda references from docs; added Mermaid architecture diagrams with consistent dark theme.
@@ -5189,58 +6331,58 @@
 - Built Citco-branded HTML alarm emails via SES with per-platform digest; verified bbhagat@citco.com as DEV SES sender.</t>
         </is>
       </c>
-      <c r="E191" s="10" t="n">
+      <c r="E274" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F191" s="8" t="n"/>
-    </row>
-    <row r="192" ht="143" customHeight="1">
-      <c r="A192" s="8" t="n"/>
-      <c r="B192" s="8" t="n"/>
-      <c r="C192" s="9" t="inlineStr">
+      <c r="F274" s="8" t="n"/>
+    </row>
+    <row r="275" ht="143" customHeight="1">
+      <c r="A275" s="8" t="n"/>
+      <c r="B275" s="8" t="n"/>
+      <c r="C275" s="9" t="inlineStr">
         <is>
           <t>Docs Mermaid Theme &amp; Spec Closures</t>
         </is>
       </c>
-      <c r="D192" s="9" t="inlineStr">
+      <c r="D275" s="9" t="inlineStr">
         <is>
           <t>- Marked completed specs: cfn-restructure, cli-class-refactor, flask-api-cleanup.
 - Removed stale env example files; updated .env.dev.example.
 - Applied consistent neo dark theme to all Mermaid diagrams; fixed subgraph background colour (pink → dark navy).</t>
         </is>
       </c>
-      <c r="E192" s="10" t="n">
+      <c r="E275" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F192" s="8" t="n"/>
-    </row>
-    <row r="193" ht="143" customHeight="1">
-      <c r="A193" s="8" t="n"/>
-      <c r="B193" s="8" t="n"/>
-      <c r="C193" s="9" t="inlineStr">
+      <c r="F275" s="8" t="n"/>
+    </row>
+    <row r="276" ht="143" customHeight="1">
+      <c r="A276" s="8" t="n"/>
+      <c r="B276" s="8" t="n"/>
+      <c r="C276" s="9" t="inlineStr">
         <is>
           <t>@citco/core + @citco/theme Plan</t>
         </is>
       </c>
-      <c r="D193" s="9" t="inlineStr">
+      <c r="D276" s="9" t="inlineStr">
         <is>
           <t>- Added IISS-919 plan to replace shadcn/ui + custom citco-ui with @citco/core + @citco/theme for the Enterprise Infrastructure Monitoring Dashboard.</t>
         </is>
       </c>
-      <c r="E193" s="10" t="n">
+      <c r="E276" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F193" s="8" t="n"/>
-    </row>
-    <row r="194" ht="143" customHeight="1">
-      <c r="A194" s="8" t="n"/>
-      <c r="B194" s="8" t="n"/>
-      <c r="C194" s="9" t="inlineStr">
+      <c r="F276" s="8" t="n"/>
+    </row>
+    <row r="277" ht="143" customHeight="1">
+      <c r="A277" s="8" t="n"/>
+      <c r="B277" s="8" t="n"/>
+      <c r="C277" s="9" t="inlineStr">
         <is>
           <t>SES Failure Notifications, 99% Coverage, Pinned Deps &amp; IA Best Practic</t>
         </is>
       </c>
-      <c r="D194" s="9" t="inlineStr">
+      <c r="D277" s="9" t="inlineStr">
         <is>
           <t>- Added SES failure/status notifications for IRCOEKB and mapping Lambdas with Citco-styled HTML emails and clickable CloudWatch Logs deep-links.
 - Achieved 99% test coverage across all meaningful files including scripts/.
@@ -5251,20 +6393,20 @@
 - Added IA Best Practice verification reports for Aug 5, Aug 19, and Aug 20.</t>
         </is>
       </c>
-      <c r="E194" s="10" t="n">
+      <c r="E277" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F194" s="8" t="n"/>
-    </row>
-    <row r="195" ht="143" customHeight="1">
-      <c r="A195" s="8" t="n"/>
-      <c r="B195" s="8" t="n"/>
-      <c r="C195" s="9" t="inlineStr">
+      <c r="F277" s="8" t="n"/>
+    </row>
+    <row r="278" ht="143" customHeight="1">
+      <c r="A278" s="8" t="n"/>
+      <c r="B278" s="8" t="n"/>
+      <c r="C278" s="9" t="inlineStr">
         <is>
           <t>SMTP Email Delivery, Notifications CLI, Project Rename &amp; AWS Icons</t>
         </is>
       </c>
-      <c r="D195" s="9" t="inlineStr">
+      <c r="D278" s="9" t="inlineStr">
         <is>
           <t>- Merged three feature branches into release and then into main — mapper decommission, composite alarm re-notification, Citco HTML emails.
 - Fixed architecture Mermaid diagram Services subgraph layout to a cleaner 4x2 grid.
@@ -5276,40 +6418,40 @@
 - Renamed project from IA IT SRE Platform Monitoring to IA IT SRE Infrastructure Monitoring across all HTML templates and specs.</t>
         </is>
       </c>
-      <c r="E195" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F195" s="8" t="n"/>
-    </row>
-    <row r="196" ht="143" customHeight="1">
-      <c r="A196" s="8" t="n"/>
-      <c r="B196" s="8" t="n"/>
-      <c r="C196" s="9" t="inlineStr">
+      <c r="E278" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F278" s="8" t="n"/>
+    </row>
+    <row r="279" ht="143" customHeight="1">
+      <c r="A279" s="8" t="n"/>
+      <c r="B279" s="8" t="n"/>
+      <c r="C279" s="9" t="inlineStr">
         <is>
           <t>ia-bpo Platform Grouping &amp; CI/CD Pipeline Spec</t>
         </is>
       </c>
-      <c r="D196" s="9" t="inlineStr">
+      <c r="D279" s="9" t="inlineStr">
         <is>
           <t>- Added ia-it-sre resources under the ia-bpo platform in the inventory API; updated platform config documentation.
 - Removed stale force-update workaround note.
 - Added CI/CD pipeline deployment spec for the DevOps team; promoted LambdaCodeVersion from optional to required in the spec.</t>
         </is>
       </c>
-      <c r="E196" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F196" s="8" t="n"/>
-    </row>
-    <row r="197" ht="143" customHeight="1">
-      <c r="A197" s="11" t="n"/>
-      <c r="B197" s="11" t="n"/>
-      <c r="C197" s="24" t="inlineStr">
+      <c r="E279" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F279" s="8" t="n"/>
+    </row>
+    <row r="280" ht="143" customHeight="1">
+      <c r="A280" s="11" t="n"/>
+      <c r="B280" s="11" t="n"/>
+      <c r="C280" s="24" t="inlineStr">
         <is>
           <t>Meetings &amp; Standups</t>
         </is>
       </c>
-      <c r="D197" s="25" t="inlineStr">
+      <c r="D280" s="25" t="inlineStr">
         <is>
           <t>Meetings this week (5 meetings, 1.5h):
 - Daily Standup - Innovation IT (30 min)
@@ -5319,173 +6461,334 @@
 - Daily Standup - Innovation IT (30 min)</t>
         </is>
       </c>
-      <c r="E197" s="26" t="n">
+      <c r="E280" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="F197" s="11" t="n"/>
-    </row>
-    <row r="198" ht="143" customHeight="1">
-      <c r="A198" s="28" t="inlineStr">
+      <c r="F280" s="11" t="n"/>
+    </row>
+    <row r="281" ht="143" customHeight="1">
+      <c r="A281" s="14" t="inlineStr">
         <is>
           <t>Week 24</t>
         </is>
       </c>
-      <c r="B198" s="29" t="inlineStr">
+      <c r="B281" s="15" t="inlineStr">
         <is>
           <t>Aug 24 – Aug 28, 2026</t>
         </is>
       </c>
-      <c r="C198" s="30" t="inlineStr">
+      <c r="C281" s="27" t="inlineStr">
         <is>
           <t>RPA Production Support Shift</t>
         </is>
       </c>
-      <c r="D198" s="31" t="inlineStr">
-        <is>
-          <t>- Reviewed APAC handover log and opened SD Portal queue for Week 24 rotation start.
-- Monitored UiPath Orchestrator for overnight queue items across all active processes.
-- Triaged incoming tickets; confirmed successful overnight runs for MESO and FX Closeout.
-- Checked VPL queue at 5:00 PM EST — all items processed.
+      <c r="D281" s="6" t="inlineStr">
+        <is>
+          <t>- Reviewed APAC handover log; opened SD Portal queue for Week 24 support rotation start.
+- Handled 4 tickets: Auto Rec Download SFTP config update, FA Audit Pack Big-19 constraint, Ops Transfers trailing whitespace fix, 3x MESO stuck runs (ARISAIG/OPENDOOR - marked FAILED and retriggered).
+- Checked VPL queue at 5:00 PM EST - all items processed.
 - Updated Confluence shift handover log with end-of-day summary.
-- Monitored SD Portal queue and Teams channels throughout shift.
-- Handled MESO process status inquiries via CloudWatch Logs run ID trace.
-- Investigated FX Closeout retrigger — verified Daily565 folder, triggered in UiPath.
-- Reviewed APAC handover and coordinated on pending escalations.
-- Updated Confluence shift handover log.
-- Monitored SD Portal queue and reviewed APAC handover log.
-- Handled Auto Rec Download config request — backed up and updated gridview.py.</t>
-        </is>
-      </c>
-      <c r="E198" s="32" t="n">
-        <v>40</v>
-      </c>
-      <c r="F198" s="28">
-        <f>SUM(E198:E198)</f>
+- SD #15481540 MESO blank reports: task stuck in KILLED status; coordinated with Horace to mark FAILED and retrigger - resolved.
+- SD #15483114 DB exception: investigated logs with Kiro, emailed Jay with findings; Jay escalated to DB team.
+- Reviewed APAC handover; monitored SD Portal and Teams throughout shift.
+- Updated Confluence shift handover log.</t>
+        </is>
+      </c>
+      <c r="E281" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F281" s="14">
+        <f>SUM(E281:E290)</f>
         <v/>
       </c>
     </row>
-    <row r="199" ht="143" customHeight="1">
-      <c r="A199" s="33" t="inlineStr">
+    <row r="282" ht="143" customHeight="1">
+      <c r="A282" s="18" t="n"/>
+      <c r="B282" s="18" t="n"/>
+      <c r="C282" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D282" s="9" t="inlineStr"/>
+      <c r="E282" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F282" s="18" t="n"/>
+    </row>
+    <row r="283" ht="143" customHeight="1">
+      <c r="A283" s="18" t="n"/>
+      <c r="B283" s="18" t="n"/>
+      <c r="C283" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D283" s="9" t="inlineStr"/>
+      <c r="E283" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F283" s="18" t="n"/>
+    </row>
+    <row r="284" ht="143" customHeight="1">
+      <c r="A284" s="18" t="n"/>
+      <c r="B284" s="18" t="n"/>
+      <c r="C284" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift</t>
+        </is>
+      </c>
+      <c r="D284" s="9" t="inlineStr"/>
+      <c r="E284" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F284" s="18" t="n"/>
+    </row>
+    <row r="285" ht="143" customHeight="1">
+      <c r="A285" s="18" t="n"/>
+      <c r="B285" s="18" t="n"/>
+      <c r="C285" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift + IISS-919 Dev</t>
+        </is>
+      </c>
+      <c r="D285" s="9" t="inlineStr">
+        <is>
+          <t>- Support shift: routine monitoring, no escalations.
+- IISS-919: added X-Ray + CloudWatch Alarms observability API handlers to ia-it-sre-infrastructure-inventory (13 files, 3408 insertions).
+- IISS-824: CORA PDF uploaded to LLM KB; fixed CFN changeset hang (log_config.py missing from upload Lambda buildspec); tested GPT-5.6 Luna on DEV agent.
+- Updated Confluence shift handover log.</t>
+        </is>
+      </c>
+      <c r="E285" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F285" s="18" t="n"/>
+    </row>
+    <row r="286" ht="143" customHeight="1">
+      <c r="A286" s="18" t="n"/>
+      <c r="B286" s="18" t="n"/>
+      <c r="C286" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift + IISS-919 Dev</t>
+        </is>
+      </c>
+      <c r="D286" s="9" t="inlineStr"/>
+      <c r="E286" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F286" s="18" t="n"/>
+    </row>
+    <row r="287" ht="143" customHeight="1">
+      <c r="A287" s="18" t="n"/>
+      <c r="B287" s="18" t="n"/>
+      <c r="C287" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift + IISS-824 Refactor</t>
+        </is>
+      </c>
+      <c r="D287" s="9" t="inlineStr">
+        <is>
+          <t>- Support: AVCAB SONA/PICTET trigger (-LOG suffix), FX Closeout SONA trigger, MESO monitoring, stale ticket cleanup.
+- IISS-824: Lambda handler standardisation - Phase 1 (delete 4 shims, update CFN refs) and Phase 2 (rename function.py to handler.py, delete 2 shims). Spec + task list added.
+- Fixed: agent_instruction.txt missing from Lambda package (removed from .gitignore).</t>
+        </is>
+      </c>
+      <c r="E287" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F287" s="18" t="n"/>
+    </row>
+    <row r="288" ht="143" customHeight="1">
+      <c r="A288" s="18" t="n"/>
+      <c r="B288" s="18" t="n"/>
+      <c r="C288" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift + IISS-824 Refactor</t>
+        </is>
+      </c>
+      <c r="D288" s="9" t="inlineStr"/>
+      <c r="E288" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F288" s="18" t="n"/>
+    </row>
+    <row r="289" ht="143" customHeight="1">
+      <c r="A289" s="18" t="n"/>
+      <c r="B289" s="18" t="n"/>
+      <c r="C289" s="28" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift (Final) + IISS-824 Lambda Refactor</t>
+        </is>
+      </c>
+      <c r="D289" s="9" t="inlineStr">
+        <is>
+          <t>- AExeo scheduled reports incident: investigated with Horace - AExeo server unresponsive, reports not delivered. Triggered manually via Postman, confirmed S3 delivery, delivered to business via Teams.
+- IISS-824: Lambda handler standardisation Phase 3 (athena extraction, ALB rename) + Phase 4 (spec complete, function.py deletions staged). Fixed CFN changeset 60min hang (TYPE_CHECKING guard for mypy_boto3_s3 import).
+- ia-it-sre-infrastructure-inventory: migrated to uv venv, pinned Python 3.14.
+- Prepared and published all end-of-placement handover documentation to Confluence.</t>
+        </is>
+      </c>
+      <c r="E289" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F289" s="18" t="n"/>
+    </row>
+    <row r="290" ht="143" customHeight="1">
+      <c r="A290" s="21" t="n"/>
+      <c r="B290" s="21" t="n"/>
+      <c r="C290" s="32" t="inlineStr">
+        <is>
+          <t>RPA Production Support Shift (Final) + IISS-824 Lambda Refactor</t>
+        </is>
+      </c>
+      <c r="D290" s="12" t="inlineStr"/>
+      <c r="E290" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F290" s="21" t="n"/>
+    </row>
+    <row r="291" ht="143" customHeight="1">
+      <c r="A291" s="4" t="inlineStr">
         <is>
           <t>Week 25</t>
         </is>
       </c>
-      <c r="B199" s="34" t="inlineStr">
+      <c r="B291" s="5" t="inlineStr">
         <is>
           <t>Aug 31 – Sep 04, 2026</t>
         </is>
       </c>
-      <c r="C199" s="31" t="inlineStr">
-        <is>
-          <t>Final KT Handover &amp; Infrastructure Monitoring Wrap-up</t>
-        </is>
-      </c>
-      <c r="D199" s="31" t="inlineStr">
-        <is>
-          <t>- Conducted final knowledge transfer session with Horace and Kri on dashboard operating model and alarm runbooks.
-- Documented incident escalation procedures and handover notes for team continuity.
-- Confirmed Mitacs BSI renewal scope for Sep–Dec 2026: X-Ray tracing, log-group discovery, and IISS-919 frontend.
-- Reviewed IISS-919 infrastructure monitoring dashboard final state with Horace.
-- Participated in final Innovation IT standup and team handover session.</t>
-        </is>
-      </c>
-      <c r="E199" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="F199" s="33">
-        <f>SUM(E199:E199)</f>
+      <c r="C291" s="6" t="inlineStr">
+        <is>
+          <t>ad-hoc support (4 tickets) + ia_meso_process ARSPC1 hotfix + ml-rpa-status-llm-agent CFN fixes + final KT handover</t>
+        </is>
+      </c>
+      <c r="D291" s="6" t="inlineStr">
+        <is>
+          <t>- SD #15516869 (Critical): AROHI/ARSPC1 PreMESO Clear Broker type mismatch - full RCA, proposed fix, emailed Horace. Fixed in same-day commits (3 targeted str casts, PR #4 merged).
+- SD #15518565/15518721/15518874 (Low): FX Closeout CQS/WINTON/CPPIB_CPPMEL - standard retrigger procedure (delete lastrun.txt, archive old reports, trigger UiPath job). Informed Katrina.
+- ml-rpa-status-llm-agent: CFN template backport, CICD/CODL account IDs, pre-commit cfn-lint fix, reverted uv-&gt;pip for Lambda packaging.
+- Final KT with Horace and Kri; confirmed Mitacs renewal; submitted SMU deliverables.</t>
+        </is>
+      </c>
+      <c r="E291" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F291" s="4">
+        <f>SUM(E291:E292)</f>
         <v/>
       </c>
     </row>
-    <row r="201" ht="30" customHeight="1">
-      <c r="A201" s="35" t="inlineStr">
+    <row r="292" ht="143" customHeight="1">
+      <c r="A292" s="11" t="n"/>
+      <c r="B292" s="11" t="n"/>
+      <c r="C292" s="12" t="inlineStr">
+        <is>
+          <t>ad-hoc support (4 tickets) + ia_meso_process ARSPC1 hotfix + ml-rpa-status-llm-agent CFN fixes + final KT handover</t>
+        </is>
+      </c>
+      <c r="D292" s="12" t="inlineStr"/>
+      <c r="E292" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F292" s="11" t="n"/>
+    </row>
+    <row r="294" ht="30" customHeight="1">
+      <c r="A294" s="33" t="inlineStr">
         <is>
           <t>TOTAL INTERNSHIP HOURS</t>
         </is>
       </c>
-      <c r="E201" s="36">
-        <f>SUM(E4:E199)</f>
+      <c r="E294" s="34">
+        <f>SUM(E4:E292)</f>
         <v/>
       </c>
-      <c r="F201" s="36">
-        <f>SUM(F4:F199)</f>
+      <c r="F294" s="34">
+        <f>SUM(F4:F292)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="F93:F102"/>
-    <mergeCell ref="B83:B92"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="F103:F104"/>
-    <mergeCell ref="B105:B117"/>
-    <mergeCell ref="F66:F72"/>
-    <mergeCell ref="A83:A92"/>
-    <mergeCell ref="F173:F181"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="A103:A104"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="A159:A172"/>
-    <mergeCell ref="A76:A82"/>
-    <mergeCell ref="A93:A102"/>
-    <mergeCell ref="B155:B158"/>
-    <mergeCell ref="A13:A15"/>
+  <mergeCells count="78">
+    <mergeCell ref="B264:B280"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="A149:A159"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B136:B148"/>
+    <mergeCell ref="A92:A101"/>
+    <mergeCell ref="A171:A184"/>
+    <mergeCell ref="A223:A235"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="A253:A263"/>
+    <mergeCell ref="A236:A252"/>
+    <mergeCell ref="A125:A135"/>
+    <mergeCell ref="A281:A290"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="F113:F124"/>
+    <mergeCell ref="A204:A222"/>
+    <mergeCell ref="B25:B35"/>
+    <mergeCell ref="A294:D294"/>
+    <mergeCell ref="B66:B80"/>
+    <mergeCell ref="F25:F35"/>
+    <mergeCell ref="B102:B112"/>
+    <mergeCell ref="B185:B203"/>
+    <mergeCell ref="B92:B101"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B171:B184"/>
+    <mergeCell ref="F92:F101"/>
+    <mergeCell ref="B281:B290"/>
+    <mergeCell ref="F223:F235"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="F236:F252"/>
+    <mergeCell ref="F160:F170"/>
+    <mergeCell ref="F291:F292"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B118:B135"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B136:B154"/>
-    <mergeCell ref="F22:F32"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="A105:A117"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="F10:F12"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="F61:F65"/>
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="A118:A135"/>
-    <mergeCell ref="A201:D201"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="F33:F47"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="F182:F197"/>
-    <mergeCell ref="B54:B60"/>
-    <mergeCell ref="B159:B172"/>
-    <mergeCell ref="B76:B82"/>
-    <mergeCell ref="B93:B102"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="F83:F92"/>
-    <mergeCell ref="A22:A32"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="A136:A154"/>
-    <mergeCell ref="A73:A75"/>
-    <mergeCell ref="F105:F117"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="B66:B72"/>
-    <mergeCell ref="A61:A65"/>
-    <mergeCell ref="B173:B181"/>
-    <mergeCell ref="A182:A197"/>
-    <mergeCell ref="A33:A47"/>
-    <mergeCell ref="B33:B47"/>
-    <mergeCell ref="F54:F60"/>
-    <mergeCell ref="A54:A60"/>
-    <mergeCell ref="F155:F158"/>
-    <mergeCell ref="A155:A158"/>
-    <mergeCell ref="F118:F135"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B22:B32"/>
-    <mergeCell ref="F136:F154"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="B61:B65"/>
-    <mergeCell ref="A66:A72"/>
+    <mergeCell ref="F281:F290"/>
+    <mergeCell ref="F81:F91"/>
+    <mergeCell ref="F204:F222"/>
+    <mergeCell ref="A102:A112"/>
+    <mergeCell ref="F15:F19"/>
+    <mergeCell ref="F9:F14"/>
+    <mergeCell ref="A291:A292"/>
+    <mergeCell ref="A36:A48"/>
+    <mergeCell ref="A49:A65"/>
+    <mergeCell ref="B223:B235"/>
+    <mergeCell ref="B253:B263"/>
+    <mergeCell ref="B236:B252"/>
+    <mergeCell ref="B113:B124"/>
+    <mergeCell ref="B291:B292"/>
+    <mergeCell ref="F36:F48"/>
+    <mergeCell ref="A66:A80"/>
+    <mergeCell ref="F149:F159"/>
+    <mergeCell ref="F125:F135"/>
+    <mergeCell ref="F171:F184"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="F264:F280"/>
+    <mergeCell ref="F136:F148"/>
+    <mergeCell ref="F20:F24"/>
+    <mergeCell ref="A185:A203"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="F49:F65"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="A173:A181"/>
-    <mergeCell ref="B182:B197"/>
-    <mergeCell ref="F159:F172"/>
-    <mergeCell ref="F76:F82"/>
+    <mergeCell ref="B160:B170"/>
+    <mergeCell ref="B81:B91"/>
+    <mergeCell ref="B204:B222"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="A160:A170"/>
+    <mergeCell ref="F253:F263"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="F66:F80"/>
+    <mergeCell ref="A81:A91"/>
+    <mergeCell ref="A136:A148"/>
+    <mergeCell ref="F102:F112"/>
+    <mergeCell ref="F185:F203"/>
+    <mergeCell ref="A264:A280"/>
+    <mergeCell ref="B36:B48"/>
+    <mergeCell ref="B49:B65"/>
+    <mergeCell ref="B149:B159"/>
+    <mergeCell ref="A113:A124"/>
+    <mergeCell ref="B125:B135"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>

--- a/output/BhavikBhagat_A00494758_WorkLogs.xlsx
+++ b/output/BhavikBhagat_A00494758_WorkLogs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bbhagat\dev_work\personal_projects\citco-ia-sre-mitacs-coop-smu-bk\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E093B1-CCD3-48B3-927B-56582E317C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B02F715-A0CA-4922-9B12-DBCFAB53CDA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13050" yWindow="-16455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Work Logs" sheetId="1" r:id="rId1"/>
@@ -62,13 +62,6 @@
     <t>IT Onboarding &amp; Account Setup</t>
   </si>
   <si>
-    <t>- Completed Day-1 orientation covering team structure, project scope, and internship expectations with Kishor Deotale.
-- Attended team introduction call with co-interns Sridhar and Soundarya, and company tour.
-- Raised Confluence access request ticket (#14193911).
-- Raised JIRA access tickets (#14193674, #14193943) for the IISS project board.
-- Submitted BitBucket repository access request (#14196961).</t>
-  </si>
-  <si>
     <t>Development Environment Configuration</t>
   </si>
   <si>
@@ -97,9 +90,6 @@
 - Reviewed IA Automation Catalog to understand project registration and tracking processes.
 - Studied the five budget code environments (citcoshareddev01, citcocoredev01, citcosgdev01, coretest01, coreprod01).
 - Explored CloudWatch console to understand existing log groups and metric namespaces.</t>
-  </si>
-  <si>
-    <t>KT session with Horace for RPA Support Queue</t>
   </si>
   <si>
     <t>- Attended BPM Control Questionnaire security review meeting.
@@ -381,17 +371,6 @@
   </si>
   <si>
     <t>Training Week Day 3 (Part 1/2)</t>
-  </si>
-  <si>
-    <t>- Continued Citco corporate training modules.
-- AWS environment walkthrough with Horace (Ho Hoi Leung).
-- Deep dive into Event Routing Service (ERS) architecture
-- Studied ERS-AP registry build process via deployment_specs.yaml
-- Learned Knowledge Graph hierarchy levels (L1-L5: Product to detail)
-- Explored AuthMaster authentication and authorization flow
-- Reviewed CDI (Citco Data Integration) sync mechanisms
-- Documented workflow API service data retrieval patterns
-- Learned optic loader hosting and GraphName concepts</t>
   </si>
   <si>
     <t>Training Week Day 3 (Part 2/2)</t>
@@ -3170,17 +3149,6 @@
     <t>RPA Production Support Shift (Part 3/4)</t>
   </si>
   <si>
-    <t>- SD #15481540 MESO blank reports: task stuck in KILLED status; coordinated with Horace to mark FAILED and retrigger - resolved.
-- SD #15483114 DB exception: investigated logs with Kiro, emailed Jay with findings; Jay escalated to DB team.
-- Analyzed requirements and planned implementation approach
-- Implemented core functionality per specifications
-- Wrote unit tests to verify behavior
-- Conducted code review and incorporated feedback
-- Updated documentation with changes
-- Deployed to development environment for testing
-- Verified functionality meets acceptance criteria</t>
-  </si>
-  <si>
     <t>RPA Production Support Shift (Part 4/4)</t>
   </si>
   <si>
@@ -3252,17 +3220,6 @@
   </si>
   <si>
     <t>RPA Production Support Shift (Final) + IISS-824 Lambda Refactor (Part 1/2)</t>
-  </si>
-  <si>
-    <t>- AExeo scheduled reports incident: investigated with Horace - AExeo server unresponsive, reports not delivered. Triggered manually via Postman, confirmed S3 delivery, delivered to business via Teams.
-- IISS-824: Lambda handler standardisation Phase 3 (athena extraction, ALB rename) + Phase 4 (spec complete, function.py deletions staged). Fixed CFN changeset 60min hang (TYPE_CHECKING guard for mypy_boto3_s3 import).
-- Analyzed Lambda function metrics (duration, errors, throttles)
-- Configured X-Ray tracing for distributed request tracking
-- Implemented CloudWatch embedded metrics for custom data
-- Optimized cold start performance via provisioned concurrency
-- Reviewed memory configuration for cost/performance balance
-- Set up Lambda Insights for enhanced monitoring
-- Documented deployment patterns and environment variables</t>
   </si>
   <si>
     <t>RPA Production Support Shift (Final) + IISS-824 Lambda Refactor (Part 2/2)</t>
@@ -3288,7 +3245,33 @@
     <t>Ad-hoc Support &amp; MESO ARSPC1 Hotfix</t>
   </si>
   <si>
-    <t>- SD #15516869 (Critical): AROHI/ARSPC1 PreMESO Clear Broker type mismatch - full RCA, proposed fix, emailed Horace. Fixed in same-day commits (3 targeted str casts, PR #4 merged).
+    <t>LLM Agent CFN Fixes &amp; KT Handover</t>
+  </si>
+  <si>
+    <t>Internship Period: March 16, 2026 – August 31, 2026  |  SMU MCDA Major Project   |  Citco Technology Management, Halifax NS  |  Supervisor: Mr. Kishor Deotale</t>
+  </si>
+  <si>
+    <t>Mr. Bhavik Kantilal Bhagat (A00494758) — Internship Work Logs</t>
+  </si>
+  <si>
+    <t>TOTAL HOURS</t>
+  </si>
+  <si>
+    <t>KT session with Mr. Horace for RPA Support Queue</t>
+  </si>
+  <si>
+    <t>- AExeo scheduled reports incident: investigated with Mr. Horace - AExeo server unresponsive, reports not delivered. Triggered manually via Postman, confirmed S3 delivery, delivered to business via Teams.
+- IISS-824: Lambda handler standardisation Phase 3 (athena extraction, ALB rename) + Phase 4 (spec complete, function.py deletions staged). Fixed CFN changeset 60min hang (TYPE_CHECKING guard for mypy_boto3_s3 import).
+- Analyzed Lambda function metrics (duration, errors, throttles)
+- Configured X-Ray tracing for distributed request tracking
+- Implemented CloudWatch embedded metrics for custom data
+- Optimized cold start performance via provisioned concurrency
+- Reviewed memory configuration for cost/performance balance
+- Set up Lambda Insights for enhanced monitoring
+- Documented deployment patterns and environment variables</t>
+  </si>
+  <si>
+    <t>- SD #15516869 (Critical): AROHI/ARSPC1 PreMESO Clear Broker type mismatch - full RCA, proposed fix, emailed Mr. Horace. Fixed in same-day commits (3 targeted str casts, PR #4 merged).
 - SD #15518565/15518721/15518874 (Low): FX Closeout CQS/WINTON/CPPIB_CPPMEL - standard retrigger procedure (delete lastrun.txt, archive old reports, trigger UiPath job). Informed Katrina.
 - Investigated MESO process run status and logs
 - Analyzed distributed tracing for request flow
@@ -3299,11 +3282,19 @@
 - Set up CloudWatch alarms for error detection</t>
   </si>
   <si>
-    <t>LLM Agent CFN Fixes &amp; KT Handover</t>
+    <t>- Continued Citco corporate training modules.
+- AWS environment walkthrough with Mr. Horace (Mr. Ho Hoi Leung).
+- Deep dive into Event Routing Service (ERS) architecture
+- Studied ERS-AP registry build process via deployment_specs.yaml
+- Learned Knowledge Graph hierarchy levels (L1-L5: Product to detail)
+- Explored AuthMaster authentication and authorization flow
+- Reviewed CDI (Citco Data Integration) sync mechanisms
+- Documented workflow API service data retrieval patterns
+- Learned optic loader hosting and GraphName concepts</t>
   </si>
   <si>
     <t>- ml-rpa-status-llm-agent: CFN template backport, CICD/CODL account IDs, pre-commit cfn-lint fix, reverted uv-&gt;pip for Lambda packaging.
-- Final KT with Horace and Kri; confirmed Mitacs renewal; submitted SMU deliverables.
+- Final KT with Mr. Horace and Ms. Kri; confirmed Mitacs renewal; submitted SMU deliverables.
 - Investigated MESO process run status and logs
 - Analyzed distributed tracing for request flow
 - Reviewed SQS queue processing patterns
@@ -3313,13 +3304,22 @@
 - Set up CloudWatch alarms for error detection</t>
   </si>
   <si>
-    <t>Internship Period: March 16, 2026 – August 31, 2026  |  SMU MCDA Major Project   |  Citco Technology Management, Halifax NS  |  Supervisor: Mr. Kishor Deotale</t>
-  </si>
-  <si>
-    <t>Mr. Bhavik Kantilal Bhagat (A00494758) — Internship Work Logs</t>
-  </si>
-  <si>
-    <t>TOTAL HOURS</t>
+    <t>- SD #15481540 MESO blank reports: task stuck in KILLED status; coordinated with Mr. Horace to mark FAILED and retrigger - resolved.
+- SD #15483114 DB exception: investigated logs with Kiro, emailed Mr. Jay with findings; Mr. Jay escalated to DB team.
+- Analyzed requirements and planned implementation approach
+- Implemented core functionality per specifications
+- Wrote unit tests to verify behavior
+- Conducted code review and incorporated feedback
+- Updated documentation with changes
+- Deployed to development environment for testing
+- Verified functionality meets acceptance criteria</t>
+  </si>
+  <si>
+    <t>- Completed Day-1 orientation covering team structure, project scope, and internship expectations with Mr. Kishor Deotale.
+- Attended team introduction call with co-interns Mr. Sridhar and Ms. Soundarya, and company tour.
+- Raised Confluence access request ticket (#14193911).
+- Raised JIRA access tickets (#14193674, #14193943) for the IISS project board.
+- Submitted BitBucket repository access request (#14196961).</t>
   </si>
 </sst>
 </file>
@@ -3672,15 +3672,6 @@
   </cellStyleXfs>
   <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3711,46 +3702,34 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3760,6 +3739,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3780,22 +3789,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4109,8 +4109,8 @@
   <dimension ref="A1:F283"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.08984375" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.08984375" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.1796875" customWidth="1"/>
     <col min="4" max="4" width="118.453125" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
@@ -4118,42 +4118,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="26" x14ac:dyDescent="0.35">
-      <c r="A1" s="31" t="s">
-        <v>564</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="33"/>
+      <c r="A1" s="34" t="s">
+        <v>557</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="34" t="s">
-        <v>563</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="36"/>
-    </row>
-    <row r="3" spans="1:6" s="20" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="37" t="s">
+      <c r="A2" s="37" t="s">
+        <v>556</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="39"/>
+    </row>
+    <row r="3" spans="1:6" s="11" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="39" t="s">
+      <c r="E3" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4161,4172 +4161,4172 @@
       <c r="A4" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D4" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="E4" s="2">
         <v>2.5</v>
       </c>
-      <c r="F4" s="41">
+      <c r="F4" s="42">
         <f>SUM(E4:E8)</f>
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="27"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="32"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="F5" s="28"/>
+    </row>
+    <row r="6" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="32"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="7">
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="4">
         <v>2.5</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="27"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="28"/>
+    </row>
+    <row r="7" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="32"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="7">
+      <c r="D7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="4">
         <v>2.5</v>
       </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="27"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="F7" s="28"/>
+    </row>
+    <row r="8" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="33"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="9" t="s">
+        <v>559</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E8" s="10">
+        <v>3</v>
+      </c>
+      <c r="F8" s="29"/>
+    </row>
+    <row r="9" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="8">
         <v>2.5</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="42"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="13">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="11">
-        <v>2.5</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="F9" s="16">
         <f>SUM(E9:E14)</f>
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A10" s="27"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="6" t="s">
+      <c r="A10" s="32"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="F10" s="28"/>
+    </row>
+    <row r="11" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="32"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E11" s="4">
         <v>2.5</v>
       </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="27"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="6" t="s">
+      <c r="F11" s="28"/>
+    </row>
+    <row r="12" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="32"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E12" s="4">
         <v>2.5</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="27"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="6" t="s">
+      <c r="F12" s="28"/>
+    </row>
+    <row r="13" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="32"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E13" s="4">
         <v>2.5</v>
       </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="27"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="6" t="s">
+      <c r="F13" s="28"/>
+    </row>
+    <row r="14" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="33"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E14" s="10">
         <v>2.5</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" ht="78" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="42"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="12" t="s">
+      <c r="F14" s="29"/>
+    </row>
+    <row r="15" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="B15" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="26" t="s">
+      <c r="C15" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="D15" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E15" s="11">
+      <c r="E15" s="8">
         <v>3</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="16">
         <f>SUM(E15:E19)</f>
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="27"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="6" t="s">
+      <c r="A16" s="32"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="4">
+        <v>3</v>
+      </c>
+      <c r="F16" s="28"/>
+    </row>
+    <row r="17" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="32"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E17" s="4">
         <v>3</v>
       </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="27"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="6" t="s">
+      <c r="F17" s="28"/>
+    </row>
+    <row r="18" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="32"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E18" s="4">
         <v>3</v>
       </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="27"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="6" t="s">
+      <c r="F18" s="28"/>
+    </row>
+    <row r="19" spans="1:6" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="33"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D19" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="7">
-        <v>3</v>
-      </c>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="42"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="12" t="s">
+      <c r="E19" s="10">
+        <v>4</v>
+      </c>
+      <c r="F19" s="29"/>
+    </row>
+    <row r="20" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A20" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="B20" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="13">
-        <v>4</v>
-      </c>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A20" s="26" t="s">
+      <c r="C20" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="D20" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="11">
+      <c r="E20" s="8">
         <v>3.5</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="16">
         <f>SUM(E20:E24)</f>
         <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A21" s="27"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="6" t="s">
+      <c r="A21" s="32"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="F21" s="28"/>
+    </row>
+    <row r="22" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A22" s="32"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D22" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E22" s="4">
         <v>3.5</v>
       </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A22" s="27"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="6" t="s">
+      <c r="F22" s="28"/>
+    </row>
+    <row r="23" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A23" s="32"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D23" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E23" s="4">
         <v>3.5</v>
       </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A23" s="27"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="6" t="s">
+      <c r="F23" s="28"/>
+    </row>
+    <row r="24" spans="1:6" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="33"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D24" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E23" s="7">
-        <v>3.5</v>
-      </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="42"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="12" t="s">
+      <c r="E24" s="10">
+        <v>4</v>
+      </c>
+      <c r="F24" s="29"/>
+    </row>
+    <row r="25" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="B25" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E24" s="13">
-        <v>4</v>
-      </c>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="26" t="s">
+      <c r="C25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="D25" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="E25" s="11">
-        <v>4</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="E25" s="8">
+        <v>4</v>
+      </c>
+      <c r="F25" s="16">
         <f>SUM(E25:E35)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="27"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="6" t="s">
+      <c r="A26" s="32"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="4">
+        <v>4</v>
+      </c>
+      <c r="F26" s="28"/>
+    </row>
+    <row r="27" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="32"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="7">
-        <v>4</v>
-      </c>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="27"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="6" t="s">
+      <c r="E27" s="4">
+        <v>4</v>
+      </c>
+      <c r="F27" s="28"/>
+    </row>
+    <row r="28" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="32"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D28" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="7">
-        <v>4</v>
-      </c>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="27"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="6" t="s">
+      <c r="E28" s="4">
+        <v>4</v>
+      </c>
+      <c r="F28" s="28"/>
+    </row>
+    <row r="29" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="32"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D29" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="E29" s="4">
+        <v>4</v>
+      </c>
+      <c r="F29" s="28"/>
+    </row>
+    <row r="30" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="32"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="7">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="27"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="6" t="s">
+      <c r="D30" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="E30" s="4">
+        <v>4</v>
+      </c>
+      <c r="F30" s="28"/>
+    </row>
+    <row r="31" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="32"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E29" s="7">
-        <v>4</v>
-      </c>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="27"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="6" t="s">
+      <c r="D31" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="E31" s="4">
+        <v>4</v>
+      </c>
+      <c r="F31" s="28"/>
+    </row>
+    <row r="32" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="32"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E30" s="7">
-        <v>4</v>
-      </c>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="27"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="6" t="s">
+      <c r="D32" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="E32" s="4">
+        <v>4</v>
+      </c>
+      <c r="F32" s="28"/>
+    </row>
+    <row r="33" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="32"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E31" s="7">
-        <v>4</v>
-      </c>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="27"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="6" t="s">
+      <c r="D33" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="E33" s="4">
+        <v>4</v>
+      </c>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="34" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="32"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E32" s="7">
-        <v>4</v>
-      </c>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="27"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="6" t="s">
+      <c r="D34" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="4">
+        <v>4</v>
+      </c>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="35" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="33"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D35" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E33" s="7">
-        <v>4</v>
-      </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="27"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="6" t="s">
+      <c r="E35" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F35" s="29"/>
+    </row>
+    <row r="36" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E34" s="7">
-        <v>4</v>
-      </c>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="42"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="12" t="s">
+      <c r="B36" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="C36" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E35" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F35" s="3"/>
-    </row>
-    <row r="36" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="26" t="s">
+      <c r="D36" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E36" s="11">
-        <v>4</v>
-      </c>
-      <c r="F36" s="1">
+      <c r="E36" s="8">
+        <v>4</v>
+      </c>
+      <c r="F36" s="16">
         <f>SUM(E36:E48)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="27"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="6" t="s">
+      <c r="A37" s="32"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="4">
+        <v>4</v>
+      </c>
+      <c r="F37" s="28"/>
+    </row>
+    <row r="38" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A38" s="32"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="E38" s="4">
+        <v>4</v>
+      </c>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="39" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="32"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="7">
-        <v>4</v>
-      </c>
-      <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A38" s="27"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="6" t="s">
+      <c r="D39" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="E39" s="4">
+        <v>4</v>
+      </c>
+      <c r="F39" s="28"/>
+    </row>
+    <row r="40" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="32"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E38" s="7">
-        <v>4</v>
-      </c>
-      <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="27"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="6" t="s">
+      <c r="D40" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="E40" s="4">
+        <v>4</v>
+      </c>
+      <c r="F40" s="28"/>
+    </row>
+    <row r="41" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="32"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="7">
-        <v>4</v>
-      </c>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="27"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="6" t="s">
+      <c r="D41" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="E41" s="4">
+        <v>4</v>
+      </c>
+      <c r="F41" s="28"/>
+    </row>
+    <row r="42" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A42" s="32"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E40" s="7">
-        <v>4</v>
-      </c>
-      <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="27"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="6" t="s">
+      <c r="D42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="E42" s="4">
+        <v>4</v>
+      </c>
+      <c r="F42" s="28"/>
+    </row>
+    <row r="43" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="32"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E41" s="7">
-        <v>4</v>
-      </c>
-      <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A42" s="27"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="6" t="s">
+      <c r="D43" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="E43" s="4">
+        <v>4</v>
+      </c>
+      <c r="F43" s="28"/>
+    </row>
+    <row r="44" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A44" s="32"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E42" s="7">
-        <v>4</v>
-      </c>
-      <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="27"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="6" t="s">
+      <c r="D44" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="E44" s="4">
+        <v>2</v>
+      </c>
+      <c r="F44" s="28"/>
+    </row>
+    <row r="45" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="32"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E43" s="7">
-        <v>4</v>
-      </c>
-      <c r="F43" s="2"/>
-    </row>
-    <row r="44" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A44" s="27"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="6" t="s">
+      <c r="D45" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="E45" s="4">
+        <v>2</v>
+      </c>
+      <c r="F45" s="28"/>
+    </row>
+    <row r="46" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="32"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E44" s="7">
+      <c r="D46" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="4">
         <v>2</v>
       </c>
-      <c r="F44" s="2"/>
-    </row>
-    <row r="45" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="27"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" s="6" t="s">
+      <c r="F46" s="28"/>
+    </row>
+    <row r="47" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A47" s="32"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E45" s="7">
+      <c r="D47" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E47" s="4">
         <v>2</v>
       </c>
-      <c r="F45" s="2"/>
-    </row>
-    <row r="46" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="27"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D46" s="6" t="s">
+      <c r="F47" s="28"/>
+    </row>
+    <row r="48" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="33"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E46" s="7">
-        <v>2</v>
-      </c>
-      <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A47" s="27"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="6" t="s">
+      <c r="E48" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F48" s="29"/>
+    </row>
+    <row r="49" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A49" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="B49" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="E47" s="7">
-        <v>2</v>
-      </c>
-      <c r="F47" s="2"/>
-    </row>
-    <row r="48" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="42"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D48" s="12" t="s">
+      <c r="C49" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E48" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F48" s="3"/>
-    </row>
-    <row r="49" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A49" s="26" t="s">
+      <c r="D49" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="E49" s="11">
-        <v>4</v>
-      </c>
-      <c r="F49" s="1">
+      <c r="E49" s="8">
+        <v>4</v>
+      </c>
+      <c r="F49" s="16">
         <f>SUM(E49:E65)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="27"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="6" t="s">
+      <c r="A50" s="32"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" s="4">
+        <v>4</v>
+      </c>
+      <c r="F50" s="28"/>
+    </row>
+    <row r="51" spans="1:6" ht="62" x14ac:dyDescent="0.35">
+      <c r="A51" s="32"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="E51" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="F51" s="28"/>
+    </row>
+    <row r="52" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="32"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E50" s="7">
-        <v>4</v>
-      </c>
-      <c r="F50" s="2"/>
-    </row>
-    <row r="51" spans="1:6" ht="62" x14ac:dyDescent="0.35">
-      <c r="A51" s="27"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="6" t="s">
+      <c r="D52" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="E52" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="F52" s="28"/>
+    </row>
+    <row r="53" spans="1:6" ht="62" x14ac:dyDescent="0.35">
+      <c r="A53" s="32"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E51" s="7">
+      <c r="D53" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" s="4">
         <v>1.5</v>
       </c>
-      <c r="F51" s="2"/>
-    </row>
-    <row r="52" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="27"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" s="6" t="s">
+      <c r="F53" s="28"/>
+    </row>
+    <row r="54" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="32"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E52" s="7">
+      <c r="D54" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E54" s="4">
         <v>1.5</v>
       </c>
-      <c r="F52" s="2"/>
-    </row>
-    <row r="53" spans="1:6" ht="62" x14ac:dyDescent="0.35">
-      <c r="A53" s="27"/>
-      <c r="B53" s="15"/>
-      <c r="C53" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D53" s="6" t="s">
+      <c r="F54" s="28"/>
+    </row>
+    <row r="55" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A55" s="32"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E53" s="7">
+      <c r="D55" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E55" s="4">
         <v>1.5</v>
       </c>
-      <c r="F53" s="2"/>
-    </row>
-    <row r="54" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="27"/>
-      <c r="B54" s="15"/>
-      <c r="C54" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D54" s="6" t="s">
+      <c r="F55" s="28"/>
+    </row>
+    <row r="56" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="32"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E54" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="F54" s="2"/>
-    </row>
-    <row r="55" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A55" s="27"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="6" t="s">
+      <c r="D56" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="E56" s="4">
+        <v>4</v>
+      </c>
+      <c r="F56" s="28"/>
+    </row>
+    <row r="57" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="32"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E55" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="F55" s="2"/>
-    </row>
-    <row r="56" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="27"/>
-      <c r="B56" s="15"/>
-      <c r="C56" s="6" t="s">
+      <c r="D57" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="E57" s="4">
+        <v>4</v>
+      </c>
+      <c r="F57" s="28"/>
+    </row>
+    <row r="58" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A58" s="32"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E56" s="7">
-        <v>4</v>
-      </c>
-      <c r="F56" s="2"/>
-    </row>
-    <row r="57" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A57" s="27"/>
-      <c r="B57" s="15"/>
-      <c r="C57" s="6" t="s">
+      <c r="D58" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="E58" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="F58" s="28"/>
+    </row>
+    <row r="59" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A59" s="32"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E57" s="7">
-        <v>4</v>
-      </c>
-      <c r="F57" s="2"/>
-    </row>
-    <row r="58" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A58" s="27"/>
-      <c r="B58" s="15"/>
-      <c r="C58" s="6" t="s">
+      <c r="D59" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="E59" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="F59" s="28"/>
+    </row>
+    <row r="60" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A60" s="32"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E58" s="7">
+      <c r="D60" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E60" s="4">
         <v>2.75</v>
       </c>
-      <c r="F58" s="2"/>
-    </row>
-    <row r="59" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A59" s="27"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D59" s="6" t="s">
+      <c r="F60" s="28"/>
+    </row>
+    <row r="61" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="32"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E59" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="F59" s="2"/>
-    </row>
-    <row r="60" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A60" s="27"/>
-      <c r="B60" s="15"/>
-      <c r="C60" s="6" t="s">
+      <c r="D61" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="E61" s="4">
+        <v>2</v>
+      </c>
+      <c r="F61" s="28"/>
+    </row>
+    <row r="62" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A62" s="32"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E60" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="F60" s="2"/>
-    </row>
-    <row r="61" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="27"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="6" t="s">
+      <c r="D62" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="E62" s="4">
+        <v>2</v>
+      </c>
+      <c r="F62" s="28"/>
+    </row>
+    <row r="63" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A63" s="32"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E61" s="7">
+      <c r="D63" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E63" s="4">
         <v>2</v>
       </c>
-      <c r="F61" s="2"/>
-    </row>
-    <row r="62" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A62" s="27"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D62" s="6" t="s">
+      <c r="F63" s="28"/>
+    </row>
+    <row r="64" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="32"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E62" s="7">
-        <v>2</v>
-      </c>
-      <c r="F62" s="2"/>
-    </row>
-    <row r="63" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A63" s="27"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="6" t="s">
+      <c r="D64" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="E64" s="4">
+        <v>2.25</v>
+      </c>
+      <c r="F64" s="28"/>
+    </row>
+    <row r="65" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="33"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D65" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="E63" s="7">
-        <v>2</v>
-      </c>
-      <c r="F63" s="2"/>
-    </row>
-    <row r="64" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A64" s="27"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="6" t="s">
+      <c r="E65" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F65" s="29"/>
+    </row>
+    <row r="66" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="B66" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="E64" s="7">
-        <v>2.25</v>
-      </c>
-      <c r="F64" s="2"/>
-    </row>
-    <row r="65" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="42"/>
-      <c r="B65" s="18"/>
-      <c r="C65" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D65" s="12" t="s">
+      <c r="C66" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="E65" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F65" s="3"/>
-    </row>
-    <row r="66" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="26" t="s">
+      <c r="D66" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="B66" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E66" s="11">
-        <v>4</v>
-      </c>
-      <c r="F66" s="1">
+      <c r="E66" s="8">
+        <v>4</v>
+      </c>
+      <c r="F66" s="16">
         <f>SUM(E66:E75)</f>
         <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A67" s="27"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="6" t="s">
+      <c r="A67" s="32"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E67" s="4">
+        <v>4</v>
+      </c>
+      <c r="F67" s="28"/>
+    </row>
+    <row r="68" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="32"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E68" s="4">
+        <v>4</v>
+      </c>
+      <c r="F68" s="28"/>
+    </row>
+    <row r="69" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A69" s="32"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D69" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E67" s="7">
-        <v>4</v>
-      </c>
-      <c r="F67" s="2"/>
-    </row>
-    <row r="68" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A68" s="27"/>
-      <c r="B68" s="15"/>
-      <c r="C68" s="6" t="s">
+      <c r="E69" s="4">
+        <v>4</v>
+      </c>
+      <c r="F69" s="28"/>
+    </row>
+    <row r="70" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="32"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E68" s="7">
-        <v>4</v>
-      </c>
-      <c r="F68" s="2"/>
-    </row>
-    <row r="69" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A69" s="27"/>
-      <c r="B69" s="15"/>
-      <c r="C69" s="6" t="s">
+      <c r="D70" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E70" s="4">
+        <v>4</v>
+      </c>
+      <c r="F70" s="28"/>
+    </row>
+    <row r="71" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A71" s="32"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D71" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E69" s="7">
-        <v>4</v>
-      </c>
-      <c r="F69" s="2"/>
-    </row>
-    <row r="70" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A70" s="27"/>
-      <c r="B70" s="15"/>
-      <c r="C70" s="6" t="s">
+      <c r="E71" s="4">
+        <v>4</v>
+      </c>
+      <c r="F71" s="28"/>
+    </row>
+    <row r="72" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A72" s="32"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D70" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E70" s="7">
-        <v>4</v>
-      </c>
-      <c r="F70" s="2"/>
-    </row>
-    <row r="71" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A71" s="27"/>
-      <c r="B71" s="15"/>
-      <c r="C71" s="6" t="s">
+      <c r="D72" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E72" s="4">
+        <v>4</v>
+      </c>
+      <c r="F72" s="28"/>
+    </row>
+    <row r="73" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A73" s="32"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D73" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E71" s="7">
-        <v>4</v>
-      </c>
-      <c r="F71" s="2"/>
-    </row>
-    <row r="72" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A72" s="27"/>
-      <c r="B72" s="15"/>
-      <c r="C72" s="6" t="s">
+      <c r="E73" s="4">
+        <v>4</v>
+      </c>
+      <c r="F73" s="28"/>
+    </row>
+    <row r="74" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="32"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D72" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E72" s="7">
-        <v>4</v>
-      </c>
-      <c r="F72" s="2"/>
-    </row>
-    <row r="73" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A73" s="27"/>
-      <c r="B73" s="15"/>
-      <c r="C73" s="6" t="s">
+      <c r="D74" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E74" s="4">
+        <v>4</v>
+      </c>
+      <c r="F74" s="28"/>
+    </row>
+    <row r="75" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="33"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D75" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="E73" s="7">
-        <v>4</v>
-      </c>
-      <c r="F73" s="2"/>
-    </row>
-    <row r="74" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A74" s="27"/>
-      <c r="B74" s="15"/>
-      <c r="C74" s="6" t="s">
+      <c r="E75" s="10">
+        <v>4</v>
+      </c>
+      <c r="F75" s="29"/>
+    </row>
+    <row r="76" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="D74" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E74" s="7">
-        <v>4</v>
-      </c>
-      <c r="F74" s="2"/>
-    </row>
-    <row r="75" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="42"/>
-      <c r="B75" s="18"/>
-      <c r="C75" s="12" t="s">
+      <c r="B76" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="D75" s="12" t="s">
+      <c r="C76" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="E75" s="13">
-        <v>4</v>
-      </c>
-      <c r="F75" s="3"/>
-    </row>
-    <row r="76" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A76" s="26" t="s">
+      <c r="D76" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B76" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="E76" s="11">
-        <v>4</v>
-      </c>
-      <c r="F76" s="1">
+      <c r="E76" s="8">
+        <v>4</v>
+      </c>
+      <c r="F76" s="16">
         <f>SUM(E76:E86)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A77" s="27"/>
-      <c r="B77" s="15"/>
-      <c r="C77" s="6" t="s">
+      <c r="A77" s="32"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E77" s="4">
+        <v>4</v>
+      </c>
+      <c r="F77" s="28"/>
+    </row>
+    <row r="78" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A78" s="32"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="E78" s="4">
+        <v>4</v>
+      </c>
+      <c r="F78" s="28"/>
+    </row>
+    <row r="79" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A79" s="32"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E77" s="7">
-        <v>4</v>
-      </c>
-      <c r="F77" s="2"/>
-    </row>
-    <row r="78" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A78" s="27"/>
-      <c r="B78" s="15"/>
-      <c r="C78" s="6" t="s">
+      <c r="D79" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="E79" s="4">
+        <v>4</v>
+      </c>
+      <c r="F79" s="28"/>
+    </row>
+    <row r="80" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="32"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E78" s="7">
-        <v>4</v>
-      </c>
-      <c r="F78" s="2"/>
-    </row>
-    <row r="79" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A79" s="27"/>
-      <c r="B79" s="15"/>
-      <c r="C79" s="6" t="s">
+      <c r="D80" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D79" s="6" t="s">
+      <c r="E80" s="4">
+        <v>4</v>
+      </c>
+      <c r="F80" s="28"/>
+    </row>
+    <row r="81" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A81" s="32"/>
+      <c r="B81" s="30"/>
+      <c r="C81" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E79" s="7">
-        <v>4</v>
-      </c>
-      <c r="F79" s="2"/>
-    </row>
-    <row r="80" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A80" s="27"/>
-      <c r="B80" s="15"/>
-      <c r="C80" s="6" t="s">
+      <c r="D81" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="E81" s="4">
+        <v>4</v>
+      </c>
+      <c r="F81" s="28"/>
+    </row>
+    <row r="82" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="32"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="E80" s="7">
-        <v>4</v>
-      </c>
-      <c r="F80" s="2"/>
-    </row>
-    <row r="81" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A81" s="27"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="6" t="s">
+      <c r="D82" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D81" s="6" t="s">
+      <c r="E82" s="4">
+        <v>4</v>
+      </c>
+      <c r="F82" s="28"/>
+    </row>
+    <row r="83" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A83" s="32"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E81" s="7">
-        <v>4</v>
-      </c>
-      <c r="F81" s="2"/>
-    </row>
-    <row r="82" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A82" s="27"/>
-      <c r="B82" s="15"/>
-      <c r="C82" s="6" t="s">
+      <c r="D83" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="E83" s="4">
+        <v>4</v>
+      </c>
+      <c r="F83" s="28"/>
+    </row>
+    <row r="84" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A84" s="32"/>
+      <c r="B84" s="30"/>
+      <c r="C84" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E82" s="7">
-        <v>4</v>
-      </c>
-      <c r="F82" s="2"/>
-    </row>
-    <row r="83" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A83" s="27"/>
-      <c r="B83" s="15"/>
-      <c r="C83" s="6" t="s">
+      <c r="D84" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="E84" s="4">
+        <v>4</v>
+      </c>
+      <c r="F84" s="28"/>
+    </row>
+    <row r="85" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A85" s="32"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E83" s="7">
-        <v>4</v>
-      </c>
-      <c r="F83" s="2"/>
-    </row>
-    <row r="84" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A84" s="27"/>
-      <c r="B84" s="15"/>
-      <c r="C84" s="6" t="s">
+      <c r="D85" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D84" s="6" t="s">
+      <c r="E85" s="4">
+        <v>4</v>
+      </c>
+      <c r="F85" s="28"/>
+    </row>
+    <row r="86" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="33"/>
+      <c r="B86" s="31"/>
+      <c r="C86" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="E84" s="7">
-        <v>4</v>
-      </c>
-      <c r="F84" s="2"/>
-    </row>
-    <row r="85" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A85" s="27"/>
-      <c r="B85" s="15"/>
-      <c r="C85" s="6" t="s">
+      <c r="E86" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F86" s="29"/>
+    </row>
+    <row r="87" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A87" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D85" s="6" t="s">
+      <c r="B87" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="E85" s="7">
-        <v>4</v>
-      </c>
-      <c r="F85" s="2"/>
-    </row>
-    <row r="86" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A86" s="42"/>
-      <c r="B86" s="18"/>
-      <c r="C86" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D86" s="12" t="s">
+      <c r="C87" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="E86" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F86" s="3"/>
-    </row>
-    <row r="87" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A87" s="26" t="s">
+      <c r="D87" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B87" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="D87" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="E87" s="11">
-        <v>4</v>
-      </c>
-      <c r="F87" s="1">
+      <c r="E87" s="8">
+        <v>4</v>
+      </c>
+      <c r="F87" s="16">
         <f>SUM(E87:E96)</f>
         <v>38</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A88" s="27"/>
-      <c r="B88" s="15"/>
-      <c r="C88" s="6" t="s">
+      <c r="A88" s="32"/>
+      <c r="B88" s="30"/>
+      <c r="C88" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E88" s="4">
+        <v>4</v>
+      </c>
+      <c r="F88" s="28"/>
+    </row>
+    <row r="89" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A89" s="32"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="E89" s="4">
+        <v>4</v>
+      </c>
+      <c r="F89" s="28"/>
+    </row>
+    <row r="90" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A90" s="32"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E88" s="7">
-        <v>4</v>
-      </c>
-      <c r="F88" s="2"/>
-    </row>
-    <row r="89" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A89" s="27"/>
-      <c r="B89" s="15"/>
-      <c r="C89" s="6" t="s">
+      <c r="D90" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D89" s="6" t="s">
+      <c r="E90" s="4">
+        <v>4</v>
+      </c>
+      <c r="F90" s="28"/>
+    </row>
+    <row r="91" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A91" s="32"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E89" s="7">
-        <v>4</v>
-      </c>
-      <c r="F89" s="2"/>
-    </row>
-    <row r="90" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A90" s="27"/>
-      <c r="B90" s="15"/>
-      <c r="C90" s="6" t="s">
+      <c r="D91" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D90" s="6" t="s">
+      <c r="E91" s="4">
+        <v>4</v>
+      </c>
+      <c r="F91" s="28"/>
+    </row>
+    <row r="92" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A92" s="32"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E90" s="7">
-        <v>4</v>
-      </c>
-      <c r="F90" s="2"/>
-    </row>
-    <row r="91" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A91" s="27"/>
-      <c r="B91" s="15"/>
-      <c r="C91" s="6" t="s">
+      <c r="D92" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D91" s="6" t="s">
+      <c r="E92" s="4">
+        <v>4</v>
+      </c>
+      <c r="F92" s="28"/>
+    </row>
+    <row r="93" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="32"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E91" s="7">
-        <v>4</v>
-      </c>
-      <c r="F91" s="2"/>
-    </row>
-    <row r="92" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A92" s="27"/>
-      <c r="B92" s="15"/>
-      <c r="C92" s="6" t="s">
+      <c r="D93" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D92" s="6" t="s">
+      <c r="E93" s="4">
+        <v>4</v>
+      </c>
+      <c r="F93" s="28"/>
+    </row>
+    <row r="94" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A94" s="32"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E92" s="7">
-        <v>4</v>
-      </c>
-      <c r="F92" s="2"/>
-    </row>
-    <row r="93" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A93" s="27"/>
-      <c r="B93" s="15"/>
-      <c r="C93" s="6" t="s">
+      <c r="D94" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D93" s="6" t="s">
+      <c r="E94" s="4">
+        <v>4</v>
+      </c>
+      <c r="F94" s="28"/>
+    </row>
+    <row r="95" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A95" s="32"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E93" s="7">
-        <v>4</v>
-      </c>
-      <c r="F93" s="2"/>
-    </row>
-    <row r="94" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A94" s="27"/>
-      <c r="B94" s="15"/>
-      <c r="C94" s="6" t="s">
+      <c r="D95" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="E95" s="4">
+        <v>3</v>
+      </c>
+      <c r="F95" s="28"/>
+    </row>
+    <row r="96" spans="1:6" ht="109" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A96" s="33"/>
+      <c r="B96" s="31"/>
+      <c r="C96" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="E94" s="7">
-        <v>4</v>
-      </c>
-      <c r="F94" s="2"/>
-    </row>
-    <row r="95" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A95" s="27"/>
-      <c r="B95" s="15"/>
-      <c r="C95" s="6" t="s">
+      <c r="D96" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="E96" s="10">
+        <v>3</v>
+      </c>
+      <c r="F96" s="29"/>
+    </row>
+    <row r="97" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A97" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="E95" s="7">
-        <v>3</v>
-      </c>
-      <c r="F95" s="2"/>
-    </row>
-    <row r="96" spans="1:6" ht="109" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A96" s="42"/>
-      <c r="B96" s="18"/>
-      <c r="C96" s="12" t="s">
+      <c r="B97" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="C97" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E96" s="13">
-        <v>3</v>
-      </c>
-      <c r="F96" s="3"/>
-    </row>
-    <row r="97" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A97" s="26" t="s">
+      <c r="D97" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B97" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="E97" s="11">
-        <v>4</v>
-      </c>
-      <c r="F97" s="1">
+      <c r="E97" s="8">
+        <v>4</v>
+      </c>
+      <c r="F97" s="16">
         <f>SUM(E97:E107)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A98" s="27"/>
-      <c r="B98" s="15"/>
-      <c r="C98" s="6" t="s">
+      <c r="A98" s="32"/>
+      <c r="B98" s="30"/>
+      <c r="C98" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E98" s="4">
+        <v>4</v>
+      </c>
+      <c r="F98" s="28"/>
+    </row>
+    <row r="99" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A99" s="32"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="E99" s="4">
+        <v>4</v>
+      </c>
+      <c r="F99" s="28"/>
+    </row>
+    <row r="100" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A100" s="32"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E98" s="7">
-        <v>4</v>
-      </c>
-      <c r="F98" s="2"/>
-    </row>
-    <row r="99" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A99" s="27"/>
-      <c r="B99" s="15"/>
-      <c r="C99" s="6" t="s">
+      <c r="D100" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="E100" s="4">
+        <v>4</v>
+      </c>
+      <c r="F100" s="28"/>
+    </row>
+    <row r="101" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A101" s="32"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E99" s="7">
-        <v>4</v>
-      </c>
-      <c r="F99" s="2"/>
-    </row>
-    <row r="100" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A100" s="27"/>
-      <c r="B100" s="15"/>
-      <c r="C100" s="6" t="s">
+      <c r="D101" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="E101" s="4">
+        <v>4</v>
+      </c>
+      <c r="F101" s="28"/>
+    </row>
+    <row r="102" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A102" s="32"/>
+      <c r="B102" s="30"/>
+      <c r="C102" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E100" s="7">
-        <v>4</v>
-      </c>
-      <c r="F100" s="2"/>
-    </row>
-    <row r="101" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A101" s="27"/>
-      <c r="B101" s="15"/>
-      <c r="C101" s="6" t="s">
+      <c r="D102" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D101" s="6" t="s">
+      <c r="E102" s="4">
+        <v>4</v>
+      </c>
+      <c r="F102" s="28"/>
+    </row>
+    <row r="103" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A103" s="32"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E101" s="7">
-        <v>4</v>
-      </c>
-      <c r="F101" s="2"/>
-    </row>
-    <row r="102" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A102" s="27"/>
-      <c r="B102" s="15"/>
-      <c r="C102" s="6" t="s">
+      <c r="D103" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="E103" s="4">
+        <v>4</v>
+      </c>
+      <c r="F103" s="28"/>
+    </row>
+    <row r="104" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A104" s="32"/>
+      <c r="B104" s="30"/>
+      <c r="C104" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E102" s="7">
-        <v>4</v>
-      </c>
-      <c r="F102" s="2"/>
-    </row>
-    <row r="103" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A103" s="27"/>
-      <c r="B103" s="15"/>
-      <c r="C103" s="6" t="s">
+      <c r="D104" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="E104" s="4">
+        <v>4</v>
+      </c>
+      <c r="F104" s="28"/>
+    </row>
+    <row r="105" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A105" s="32"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E103" s="7">
-        <v>4</v>
-      </c>
-      <c r="F103" s="2"/>
-    </row>
-    <row r="104" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A104" s="27"/>
-      <c r="B104" s="15"/>
-      <c r="C104" s="6" t="s">
+      <c r="D105" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="E105" s="4">
+        <v>4</v>
+      </c>
+      <c r="F105" s="28"/>
+    </row>
+    <row r="106" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A106" s="32"/>
+      <c r="B106" s="30"/>
+      <c r="C106" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E104" s="7">
-        <v>4</v>
-      </c>
-      <c r="F104" s="2"/>
-    </row>
-    <row r="105" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A105" s="27"/>
-      <c r="B105" s="15"/>
-      <c r="C105" s="6" t="s">
+      <c r="D106" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D105" s="6" t="s">
+      <c r="E106" s="4">
+        <v>4</v>
+      </c>
+      <c r="F106" s="28"/>
+    </row>
+    <row r="107" spans="1:6" ht="171" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A107" s="33"/>
+      <c r="B107" s="31"/>
+      <c r="C107" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D107" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E105" s="7">
-        <v>4</v>
-      </c>
-      <c r="F105" s="2"/>
-    </row>
-    <row r="106" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A106" s="27"/>
-      <c r="B106" s="15"/>
-      <c r="C106" s="6" t="s">
+      <c r="E107" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F107" s="29"/>
+    </row>
+    <row r="108" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A108" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="B108" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="E106" s="7">
-        <v>4</v>
-      </c>
-      <c r="F106" s="2"/>
-    </row>
-    <row r="107" spans="1:6" ht="171" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A107" s="42"/>
-      <c r="B107" s="18"/>
-      <c r="C107" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D107" s="12" t="s">
+      <c r="C108" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E107" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F107" s="3"/>
-    </row>
-    <row r="108" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A108" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="B108" s="17" t="s">
-        <v>228</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="D108" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E108" s="11">
-        <v>4</v>
-      </c>
-      <c r="F108" s="1">
+      <c r="D108" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E108" s="8">
+        <v>4</v>
+      </c>
+      <c r="F108" s="16">
         <f>SUM(E108:E117)</f>
         <v>40</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A109" s="27"/>
-      <c r="B109" s="15"/>
-      <c r="C109" s="6" t="s">
+      <c r="A109" s="32"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E109" s="4">
+        <v>4</v>
+      </c>
+      <c r="F109" s="28"/>
+    </row>
+    <row r="110" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A110" s="32"/>
+      <c r="B110" s="30"/>
+      <c r="C110" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E110" s="4">
+        <v>4</v>
+      </c>
+      <c r="F110" s="28"/>
+    </row>
+    <row r="111" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A111" s="32"/>
+      <c r="B111" s="30"/>
+      <c r="C111" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D109" s="6" t="s">
+      <c r="D111" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E109" s="7">
-        <v>4</v>
-      </c>
-      <c r="F109" s="2"/>
-    </row>
-    <row r="110" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A110" s="27"/>
-      <c r="B110" s="15"/>
-      <c r="C110" s="6" t="s">
+      <c r="E111" s="4">
+        <v>4</v>
+      </c>
+      <c r="F111" s="28"/>
+    </row>
+    <row r="112" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A112" s="32"/>
+      <c r="B112" s="30"/>
+      <c r="C112" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D110" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E110" s="7">
-        <v>4</v>
-      </c>
-      <c r="F110" s="2"/>
-    </row>
-    <row r="111" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A111" s="27"/>
-      <c r="B111" s="15"/>
-      <c r="C111" s="6" t="s">
+      <c r="D112" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E112" s="4">
+        <v>4</v>
+      </c>
+      <c r="F112" s="28"/>
+    </row>
+    <row r="113" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A113" s="32"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="D113" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="E111" s="7">
-        <v>4</v>
-      </c>
-      <c r="F111" s="2"/>
-    </row>
-    <row r="112" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A112" s="27"/>
-      <c r="B112" s="15"/>
-      <c r="C112" s="6" t="s">
+      <c r="E113" s="4">
+        <v>4</v>
+      </c>
+      <c r="F113" s="28"/>
+    </row>
+    <row r="114" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A114" s="32"/>
+      <c r="B114" s="30"/>
+      <c r="C114" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D112" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E112" s="7">
-        <v>4</v>
-      </c>
-      <c r="F112" s="2"/>
-    </row>
-    <row r="113" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A113" s="27"/>
-      <c r="B113" s="15"/>
-      <c r="C113" s="6" t="s">
+      <c r="D114" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E114" s="4">
+        <v>4</v>
+      </c>
+      <c r="F114" s="28"/>
+    </row>
+    <row r="115" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A115" s="32"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="D115" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E115" s="4">
+        <v>4</v>
+      </c>
+      <c r="F115" s="28"/>
+    </row>
+    <row r="116" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A116" s="32"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E113" s="7">
-        <v>4</v>
-      </c>
-      <c r="F113" s="2"/>
-    </row>
-    <row r="114" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A114" s="27"/>
-      <c r="B114" s="15"/>
-      <c r="C114" s="6" t="s">
+      <c r="D116" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E116" s="4">
+        <v>4</v>
+      </c>
+      <c r="F116" s="28"/>
+    </row>
+    <row r="117" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="33"/>
+      <c r="B117" s="31"/>
+      <c r="C117" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="D114" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E114" s="7">
-        <v>4</v>
-      </c>
-      <c r="F114" s="2"/>
-    </row>
-    <row r="115" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A115" s="27"/>
-      <c r="B115" s="15"/>
-      <c r="C115" s="6" t="s">
+      <c r="D117" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E117" s="10">
+        <v>4</v>
+      </c>
+      <c r="F117" s="29"/>
+    </row>
+    <row r="118" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A118" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="D115" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E115" s="7">
-        <v>4</v>
-      </c>
-      <c r="F115" s="2"/>
-    </row>
-    <row r="116" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A116" s="27"/>
-      <c r="B116" s="15"/>
-      <c r="C116" s="6" t="s">
+      <c r="B118" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="D116" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E116" s="7">
-        <v>4</v>
-      </c>
-      <c r="F116" s="2"/>
-    </row>
-    <row r="117" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A117" s="42"/>
-      <c r="B117" s="18"/>
-      <c r="C117" s="12" t="s">
+      <c r="C118" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="D117" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="E117" s="13">
-        <v>4</v>
-      </c>
-      <c r="F117" s="3"/>
-    </row>
-    <row r="118" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A118" s="26" t="s">
+      <c r="D118" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B118" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="D118" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="E118" s="11">
-        <v>4</v>
-      </c>
-      <c r="F118" s="1">
+      <c r="E118" s="8">
+        <v>4</v>
+      </c>
+      <c r="F118" s="16">
         <f>SUM(E118:E128)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A119" s="27"/>
-      <c r="B119" s="15"/>
-      <c r="C119" s="6" t="s">
+      <c r="A119" s="32"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E119" s="4">
+        <v>4</v>
+      </c>
+      <c r="F119" s="28"/>
+    </row>
+    <row r="120" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A120" s="32"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="E120" s="4">
+        <v>4</v>
+      </c>
+      <c r="F120" s="28"/>
+    </row>
+    <row r="121" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A121" s="32"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E119" s="7">
-        <v>4</v>
-      </c>
-      <c r="F119" s="2"/>
-    </row>
-    <row r="120" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A120" s="27"/>
-      <c r="B120" s="15"/>
-      <c r="C120" s="6" t="s">
+      <c r="D121" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D120" s="6" t="s">
+      <c r="E121" s="4">
+        <v>4</v>
+      </c>
+      <c r="F121" s="28"/>
+    </row>
+    <row r="122" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A122" s="32"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="E120" s="7">
-        <v>4</v>
-      </c>
-      <c r="F120" s="2"/>
-    </row>
-    <row r="121" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A121" s="27"/>
-      <c r="B121" s="15"/>
-      <c r="C121" s="6" t="s">
+      <c r="D122" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D121" s="6" t="s">
+      <c r="E122" s="4">
+        <v>4</v>
+      </c>
+      <c r="F122" s="28"/>
+    </row>
+    <row r="123" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A123" s="32"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="E121" s="7">
-        <v>4</v>
-      </c>
-      <c r="F121" s="2"/>
-    </row>
-    <row r="122" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A122" s="27"/>
-      <c r="B122" s="15"/>
-      <c r="C122" s="6" t="s">
+      <c r="D123" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D122" s="6" t="s">
+      <c r="E123" s="4">
+        <v>4</v>
+      </c>
+      <c r="F123" s="28"/>
+    </row>
+    <row r="124" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A124" s="32"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E122" s="7">
-        <v>4</v>
-      </c>
-      <c r="F122" s="2"/>
-    </row>
-    <row r="123" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A123" s="27"/>
-      <c r="B123" s="15"/>
-      <c r="C123" s="6" t="s">
+      <c r="D124" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D123" s="6" t="s">
+      <c r="E124" s="4">
+        <v>4</v>
+      </c>
+      <c r="F124" s="28"/>
+    </row>
+    <row r="125" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A125" s="32"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E123" s="7">
-        <v>4</v>
-      </c>
-      <c r="F123" s="2"/>
-    </row>
-    <row r="124" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A124" s="27"/>
-      <c r="B124" s="15"/>
-      <c r="C124" s="6" t="s">
+      <c r="D125" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D124" s="6" t="s">
+      <c r="E125" s="4">
+        <v>4</v>
+      </c>
+      <c r="F125" s="28"/>
+    </row>
+    <row r="126" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A126" s="32"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="E124" s="7">
-        <v>4</v>
-      </c>
-      <c r="F124" s="2"/>
-    </row>
-    <row r="125" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A125" s="27"/>
-      <c r="B125" s="15"/>
-      <c r="C125" s="6" t="s">
+      <c r="D126" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="D125" s="6" t="s">
+      <c r="E126" s="4">
+        <v>4</v>
+      </c>
+      <c r="F126" s="28"/>
+    </row>
+    <row r="127" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A127" s="32"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E125" s="7">
-        <v>4</v>
-      </c>
-      <c r="F125" s="2"/>
-    </row>
-    <row r="126" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A126" s="27"/>
-      <c r="B126" s="15"/>
-      <c r="C126" s="6" t="s">
+      <c r="D127" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E127" s="4">
+        <v>4</v>
+      </c>
+      <c r="F127" s="28"/>
+    </row>
+    <row r="128" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A128" s="33"/>
+      <c r="B128" s="31"/>
+      <c r="C128" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D128" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="D126" s="6" t="s">
+      <c r="E128" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F128" s="29"/>
+    </row>
+    <row r="129" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A129" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="E126" s="7">
-        <v>4</v>
-      </c>
-      <c r="F126" s="2"/>
-    </row>
-    <row r="127" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A127" s="27"/>
-      <c r="B127" s="15"/>
-      <c r="C127" s="6" t="s">
+      <c r="B129" s="18" t="s">
         <v>262</v>
       </c>
-      <c r="D127" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="E127" s="7">
-        <v>4</v>
-      </c>
-      <c r="F127" s="2"/>
-    </row>
-    <row r="128" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A128" s="42"/>
-      <c r="B128" s="18"/>
-      <c r="C128" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D128" s="12" t="s">
+      <c r="C129" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="E128" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F128" s="3"/>
-    </row>
-    <row r="129" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A129" s="26" t="s">
+      <c r="D129" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="B129" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="D129" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="E129" s="11">
-        <v>4</v>
-      </c>
-      <c r="F129" s="1">
+      <c r="E129" s="8">
+        <v>4</v>
+      </c>
+      <c r="F129" s="16">
         <f>SUM(E129:E141)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="130" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A130" s="27"/>
-      <c r="B130" s="15"/>
-      <c r="C130" s="6" t="s">
+      <c r="A130" s="32"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E130" s="4">
+        <v>4</v>
+      </c>
+      <c r="F130" s="28"/>
+    </row>
+    <row r="131" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A131" s="32"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D130" s="6" t="s">
+      <c r="E131" s="4">
+        <v>4</v>
+      </c>
+      <c r="F131" s="28"/>
+    </row>
+    <row r="132" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A132" s="32"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="E130" s="7">
-        <v>4</v>
-      </c>
-      <c r="F130" s="2"/>
-    </row>
-    <row r="131" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A131" s="27"/>
-      <c r="B131" s="15"/>
-      <c r="C131" s="6" t="s">
+      <c r="D132" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D131" s="6" t="s">
+      <c r="E132" s="4">
+        <v>4</v>
+      </c>
+      <c r="F132" s="28"/>
+    </row>
+    <row r="133" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A133" s="32"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E131" s="7">
-        <v>4</v>
-      </c>
-      <c r="F131" s="2"/>
-    </row>
-    <row r="132" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A132" s="27"/>
-      <c r="B132" s="15"/>
-      <c r="C132" s="6" t="s">
+      <c r="D133" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="D132" s="6" t="s">
+      <c r="E133" s="4">
+        <v>4</v>
+      </c>
+      <c r="F133" s="28"/>
+    </row>
+    <row r="134" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A134" s="32"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="E132" s="7">
-        <v>4</v>
-      </c>
-      <c r="F132" s="2"/>
-    </row>
-    <row r="133" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A133" s="27"/>
-      <c r="B133" s="15"/>
-      <c r="C133" s="6" t="s">
+      <c r="D134" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="D133" s="6" t="s">
+      <c r="E134" s="4">
+        <v>4</v>
+      </c>
+      <c r="F134" s="28"/>
+    </row>
+    <row r="135" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A135" s="32"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="E133" s="7">
-        <v>4</v>
-      </c>
-      <c r="F133" s="2"/>
-    </row>
-    <row r="134" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A134" s="27"/>
-      <c r="B134" s="15"/>
-      <c r="C134" s="6" t="s">
+      <c r="D135" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="D134" s="6" t="s">
+      <c r="E135" s="4">
+        <v>2</v>
+      </c>
+      <c r="F135" s="28"/>
+    </row>
+    <row r="136" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A136" s="32"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="E134" s="7">
-        <v>4</v>
-      </c>
-      <c r="F134" s="2"/>
-    </row>
-    <row r="135" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A135" s="27"/>
-      <c r="B135" s="15"/>
-      <c r="C135" s="6" t="s">
+      <c r="D136" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="D135" s="6" t="s">
+      <c r="E136" s="4">
+        <v>2</v>
+      </c>
+      <c r="F136" s="28"/>
+    </row>
+    <row r="137" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A137" s="32"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="E135" s="7">
+      <c r="D137" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E137" s="4">
         <v>2</v>
       </c>
-      <c r="F135" s="2"/>
-    </row>
-    <row r="136" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A136" s="27"/>
-      <c r="B136" s="15"/>
-      <c r="C136" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D136" s="6" t="s">
+      <c r="F137" s="28"/>
+    </row>
+    <row r="138" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A138" s="32"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E136" s="7">
+      <c r="D138" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E138" s="4">
         <v>2</v>
       </c>
-      <c r="F136" s="2"/>
-    </row>
-    <row r="137" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A137" s="27"/>
-      <c r="B137" s="15"/>
-      <c r="C137" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="D137" s="6" t="s">
+      <c r="F138" s="28"/>
+    </row>
+    <row r="139" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A139" s="32"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="E137" s="7">
-        <v>2</v>
-      </c>
-      <c r="F137" s="2"/>
-    </row>
-    <row r="138" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A138" s="27"/>
-      <c r="B138" s="15"/>
-      <c r="C138" s="6" t="s">
+      <c r="D139" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="D138" s="6" t="s">
+      <c r="E139" s="4">
+        <v>4</v>
+      </c>
+      <c r="F139" s="28"/>
+    </row>
+    <row r="140" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A140" s="32"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E138" s="7">
-        <v>2</v>
-      </c>
-      <c r="F138" s="2"/>
-    </row>
-    <row r="139" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A139" s="27"/>
-      <c r="B139" s="15"/>
-      <c r="C139" s="6" t="s">
+      <c r="D140" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D139" s="6" t="s">
+      <c r="E140" s="4">
+        <v>4</v>
+      </c>
+      <c r="F140" s="28"/>
+    </row>
+    <row r="141" spans="1:6" ht="171" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A141" s="33"/>
+      <c r="B141" s="31"/>
+      <c r="C141" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D141" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="E139" s="7">
-        <v>4</v>
-      </c>
-      <c r="F139" s="2"/>
-    </row>
-    <row r="140" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A140" s="27"/>
-      <c r="B140" s="15"/>
-      <c r="C140" s="6" t="s">
+      <c r="E141" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F141" s="29"/>
+    </row>
+    <row r="142" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A142" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="D140" s="6" t="s">
+      <c r="B142" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="E140" s="7">
-        <v>4</v>
-      </c>
-      <c r="F140" s="2"/>
-    </row>
-    <row r="141" spans="1:6" ht="171" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A141" s="42"/>
-      <c r="B141" s="18"/>
-      <c r="C141" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D141" s="12" t="s">
+      <c r="C142" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="E141" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F141" s="3"/>
-    </row>
-    <row r="142" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A142" s="26" t="s">
+      <c r="D142" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="B142" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="C142" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="D142" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="E142" s="11">
-        <v>4</v>
-      </c>
-      <c r="F142" s="1">
+      <c r="E142" s="8">
+        <v>4</v>
+      </c>
+      <c r="F142" s="16">
         <f>SUM(E142:E152)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="186" x14ac:dyDescent="0.35">
-      <c r="A143" s="27"/>
-      <c r="B143" s="15"/>
-      <c r="C143" s="6" t="s">
+      <c r="A143" s="32"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E143" s="4">
+        <v>4</v>
+      </c>
+      <c r="F143" s="28"/>
+    </row>
+    <row r="144" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A144" s="32"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D144" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="E144" s="4">
+        <v>4</v>
+      </c>
+      <c r="F144" s="28"/>
+    </row>
+    <row r="145" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A145" s="32"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E143" s="7">
-        <v>4</v>
-      </c>
-      <c r="F143" s="2"/>
-    </row>
-    <row r="144" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A144" s="27"/>
-      <c r="B144" s="15"/>
-      <c r="C144" s="6" t="s">
+      <c r="D145" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="D144" s="6" t="s">
+      <c r="E145" s="4">
+        <v>4</v>
+      </c>
+      <c r="F145" s="28"/>
+    </row>
+    <row r="146" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A146" s="32"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E144" s="7">
-        <v>4</v>
-      </c>
-      <c r="F144" s="2"/>
-    </row>
-    <row r="145" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A145" s="27"/>
-      <c r="B145" s="15"/>
-      <c r="C145" s="6" t="s">
+      <c r="D146" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D145" s="6" t="s">
+      <c r="E146" s="4">
+        <v>4</v>
+      </c>
+      <c r="F146" s="28"/>
+    </row>
+    <row r="147" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A147" s="32"/>
+      <c r="B147" s="30"/>
+      <c r="C147" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="E145" s="7">
-        <v>4</v>
-      </c>
-      <c r="F145" s="2"/>
-    </row>
-    <row r="146" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A146" s="27"/>
-      <c r="B146" s="15"/>
-      <c r="C146" s="6" t="s">
+      <c r="D147" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="E147" s="4">
+        <v>4</v>
+      </c>
+      <c r="F147" s="28"/>
+    </row>
+    <row r="148" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A148" s="32"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E146" s="7">
-        <v>4</v>
-      </c>
-      <c r="F146" s="2"/>
-    </row>
-    <row r="147" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A147" s="27"/>
-      <c r="B147" s="15"/>
-      <c r="C147" s="6" t="s">
+      <c r="D148" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D147" s="6" t="s">
+      <c r="E148" s="4">
+        <v>4</v>
+      </c>
+      <c r="F148" s="28"/>
+    </row>
+    <row r="149" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A149" s="32"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="E147" s="7">
-        <v>4</v>
-      </c>
-      <c r="F147" s="2"/>
-    </row>
-    <row r="148" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A148" s="27"/>
-      <c r="B148" s="15"/>
-      <c r="C148" s="6" t="s">
+      <c r="D149" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="D148" s="6" t="s">
+      <c r="E149" s="4">
+        <v>4</v>
+      </c>
+      <c r="F149" s="28"/>
+    </row>
+    <row r="150" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A150" s="32"/>
+      <c r="B150" s="30"/>
+      <c r="C150" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="E148" s="7">
-        <v>4</v>
-      </c>
-      <c r="F148" s="2"/>
-    </row>
-    <row r="149" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A149" s="27"/>
-      <c r="B149" s="15"/>
-      <c r="C149" s="6" t="s">
+      <c r="D150" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D149" s="6" t="s">
+      <c r="E150" s="4">
+        <v>4</v>
+      </c>
+      <c r="F150" s="28"/>
+    </row>
+    <row r="151" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A151" s="32"/>
+      <c r="B151" s="30"/>
+      <c r="C151" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="E149" s="7">
-        <v>4</v>
-      </c>
-      <c r="F149" s="2"/>
-    </row>
-    <row r="150" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A150" s="27"/>
-      <c r="B150" s="15"/>
-      <c r="C150" s="6" t="s">
+      <c r="D151" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D150" s="6" t="s">
+      <c r="E151" s="4">
+        <v>4</v>
+      </c>
+      <c r="F151" s="28"/>
+    </row>
+    <row r="152" spans="1:6" ht="186.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A152" s="33"/>
+      <c r="B152" s="31"/>
+      <c r="C152" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D152" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="E150" s="7">
-        <v>4</v>
-      </c>
-      <c r="F150" s="2"/>
-    </row>
-    <row r="151" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A151" s="27"/>
-      <c r="B151" s="15"/>
-      <c r="C151" s="6" t="s">
+      <c r="E152" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F152" s="29"/>
+    </row>
+    <row r="153" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A153" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="D151" s="6" t="s">
+      <c r="B153" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="E151" s="7">
-        <v>4</v>
-      </c>
-      <c r="F151" s="2"/>
-    </row>
-    <row r="152" spans="1:6" ht="186.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A152" s="42"/>
-      <c r="B152" s="18"/>
-      <c r="C152" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D152" s="12" t="s">
+      <c r="C153" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="E152" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F152" s="3"/>
-    </row>
-    <row r="153" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A153" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="B153" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="C153" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="D153" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E153" s="11">
-        <v>4</v>
-      </c>
-      <c r="F153" s="1">
+      <c r="D153" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E153" s="8">
+        <v>4</v>
+      </c>
+      <c r="F153" s="16">
         <f>SUM(E153:E162)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A154" s="27"/>
-      <c r="B154" s="15"/>
-      <c r="C154" s="6" t="s">
+    <row r="154" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A154" s="32"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E154" s="4">
+        <v>4</v>
+      </c>
+      <c r="F154" s="28"/>
+    </row>
+    <row r="155" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A155" s="32"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E155" s="4">
+        <v>4</v>
+      </c>
+      <c r="F155" s="28"/>
+    </row>
+    <row r="156" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A156" s="32"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="D154" s="6" t="s">
+      <c r="D156" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E156" s="4">
+        <v>4</v>
+      </c>
+      <c r="F156" s="28"/>
+    </row>
+    <row r="157" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A157" s="32"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E154" s="7">
-        <v>4</v>
-      </c>
-      <c r="F154" s="2"/>
-    </row>
-    <row r="155" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A155" s="27"/>
-      <c r="B155" s="15"/>
-      <c r="C155" s="6" t="s">
+      <c r="D157" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E157" s="4">
+        <v>4</v>
+      </c>
+      <c r="F157" s="28"/>
+    </row>
+    <row r="158" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A158" s="32"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D155" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E155" s="7">
-        <v>4</v>
-      </c>
-      <c r="F155" s="2"/>
-    </row>
-    <row r="156" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A156" s="27"/>
-      <c r="B156" s="15"/>
-      <c r="C156" s="6" t="s">
+      <c r="D158" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E158" s="4">
+        <v>4</v>
+      </c>
+      <c r="F158" s="28"/>
+    </row>
+    <row r="159" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A159" s="32"/>
+      <c r="B159" s="30"/>
+      <c r="C159" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="D156" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E156" s="7">
-        <v>4</v>
-      </c>
-      <c r="F156" s="2"/>
-    </row>
-    <row r="157" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A157" s="27"/>
-      <c r="B157" s="15"/>
-      <c r="C157" s="6" t="s">
+      <c r="D159" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E159" s="4">
+        <v>4</v>
+      </c>
+      <c r="F159" s="28"/>
+    </row>
+    <row r="160" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A160" s="32"/>
+      <c r="B160" s="30"/>
+      <c r="C160" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="D157" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E157" s="7">
-        <v>4</v>
-      </c>
-      <c r="F157" s="2"/>
-    </row>
-    <row r="158" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A158" s="27"/>
-      <c r="B158" s="15"/>
-      <c r="C158" s="6" t="s">
+      <c r="D160" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E160" s="4">
+        <v>4</v>
+      </c>
+      <c r="F160" s="28"/>
+    </row>
+    <row r="161" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A161" s="32"/>
+      <c r="B161" s="30"/>
+      <c r="C161" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D158" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E158" s="7">
-        <v>4</v>
-      </c>
-      <c r="F158" s="2"/>
-    </row>
-    <row r="159" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A159" s="27"/>
-      <c r="B159" s="15"/>
-      <c r="C159" s="6" t="s">
+      <c r="D161" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E161" s="4">
+        <v>4</v>
+      </c>
+      <c r="F161" s="28"/>
+    </row>
+    <row r="162" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A162" s="33"/>
+      <c r="B162" s="31"/>
+      <c r="C162" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="D159" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E159" s="7">
-        <v>4</v>
-      </c>
-      <c r="F159" s="2"/>
-    </row>
-    <row r="160" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A160" s="27"/>
-      <c r="B160" s="15"/>
-      <c r="C160" s="6" t="s">
+      <c r="D162" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E162" s="10">
+        <v>4</v>
+      </c>
+      <c r="F162" s="29"/>
+    </row>
+    <row r="163" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A163" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="D160" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E160" s="7">
-        <v>4</v>
-      </c>
-      <c r="F160" s="2"/>
-    </row>
-    <row r="161" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A161" s="27"/>
-      <c r="B161" s="15"/>
-      <c r="C161" s="6" t="s">
+      <c r="B163" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="D161" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E161" s="7">
-        <v>4</v>
-      </c>
-      <c r="F161" s="2"/>
-    </row>
-    <row r="162" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A162" s="42"/>
-      <c r="B162" s="18"/>
-      <c r="C162" s="12" t="s">
+      <c r="C163" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="D162" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="E162" s="13">
-        <v>4</v>
-      </c>
-      <c r="F162" s="3"/>
-    </row>
-    <row r="163" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A163" s="26" t="s">
+      <c r="D163" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="B163" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="C163" s="10" t="s">
-        <v>329</v>
-      </c>
-      <c r="D163" s="10" t="s">
-        <v>330</v>
-      </c>
-      <c r="E163" s="11">
+      <c r="E163" s="8">
         <v>2</v>
       </c>
-      <c r="F163" s="1">
+      <c r="F163" s="16">
         <f>SUM(E163:E176)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A164" s="27"/>
-      <c r="B164" s="15"/>
-      <c r="C164" s="6" t="s">
+      <c r="A164" s="32"/>
+      <c r="B164" s="30"/>
+      <c r="C164" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E164" s="4">
+        <v>2</v>
+      </c>
+      <c r="F164" s="28"/>
+    </row>
+    <row r="165" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A165" s="32"/>
+      <c r="B165" s="30"/>
+      <c r="C165" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D165" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D164" s="6" t="s">
+      <c r="E165" s="4">
+        <v>2</v>
+      </c>
+      <c r="F165" s="28"/>
+    </row>
+    <row r="166" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A166" s="32"/>
+      <c r="B166" s="30"/>
+      <c r="C166" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E164" s="7">
+      <c r="D166" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E166" s="4">
         <v>2</v>
       </c>
-      <c r="F164" s="2"/>
-    </row>
-    <row r="165" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A165" s="27"/>
-      <c r="B165" s="15"/>
-      <c r="C165" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="D165" s="6" t="s">
+      <c r="F166" s="28"/>
+    </row>
+    <row r="167" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A167" s="32"/>
+      <c r="B167" s="30"/>
+      <c r="C167" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E165" s="7">
-        <v>2</v>
-      </c>
-      <c r="F165" s="2"/>
-    </row>
-    <row r="166" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A166" s="27"/>
-      <c r="B166" s="15"/>
-      <c r="C166" s="6" t="s">
+      <c r="D167" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D166" s="6" t="s">
+      <c r="E167" s="4">
+        <v>4</v>
+      </c>
+      <c r="F167" s="28"/>
+    </row>
+    <row r="168" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A168" s="32"/>
+      <c r="B168" s="30"/>
+      <c r="C168" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E166" s="7">
-        <v>2</v>
-      </c>
-      <c r="F166" s="2"/>
-    </row>
-    <row r="167" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A167" s="27"/>
-      <c r="B167" s="15"/>
-      <c r="C167" s="6" t="s">
+      <c r="D168" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="D167" s="6" t="s">
+      <c r="E168" s="4">
+        <v>4</v>
+      </c>
+      <c r="F168" s="28"/>
+    </row>
+    <row r="169" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A169" s="32"/>
+      <c r="B169" s="30"/>
+      <c r="C169" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="E167" s="7">
-        <v>4</v>
-      </c>
-      <c r="F167" s="2"/>
-    </row>
-    <row r="168" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A168" s="27"/>
-      <c r="B168" s="15"/>
-      <c r="C168" s="6" t="s">
+      <c r="D169" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D168" s="6" t="s">
+      <c r="E169" s="4">
+        <v>4</v>
+      </c>
+      <c r="F169" s="28"/>
+    </row>
+    <row r="170" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A170" s="32"/>
+      <c r="B170" s="30"/>
+      <c r="C170" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E168" s="7">
-        <v>4</v>
-      </c>
-      <c r="F168" s="2"/>
-    </row>
-    <row r="169" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A169" s="27"/>
-      <c r="B169" s="15"/>
-      <c r="C169" s="6" t="s">
+      <c r="D170" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D169" s="6" t="s">
+      <c r="E170" s="4">
+        <v>4</v>
+      </c>
+      <c r="F170" s="28"/>
+    </row>
+    <row r="171" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A171" s="32"/>
+      <c r="B171" s="30"/>
+      <c r="C171" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="E169" s="7">
-        <v>4</v>
-      </c>
-      <c r="F169" s="2"/>
-    </row>
-    <row r="170" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A170" s="27"/>
-      <c r="B170" s="15"/>
-      <c r="C170" s="6" t="s">
+      <c r="D171" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D170" s="6" t="s">
+      <c r="E171" s="4">
+        <v>4</v>
+      </c>
+      <c r="F171" s="28"/>
+    </row>
+    <row r="172" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A172" s="32"/>
+      <c r="B172" s="30"/>
+      <c r="C172" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="E170" s="7">
-        <v>4</v>
-      </c>
-      <c r="F170" s="2"/>
-    </row>
-    <row r="171" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A171" s="27"/>
-      <c r="B171" s="15"/>
-      <c r="C171" s="6" t="s">
+      <c r="D172" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="D171" s="6" t="s">
+      <c r="E172" s="4">
+        <v>4</v>
+      </c>
+      <c r="F172" s="28"/>
+    </row>
+    <row r="173" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A173" s="32"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="E171" s="7">
-        <v>4</v>
-      </c>
-      <c r="F171" s="2"/>
-    </row>
-    <row r="172" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A172" s="27"/>
-      <c r="B172" s="15"/>
-      <c r="C172" s="6" t="s">
+      <c r="D173" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="D172" s="6" t="s">
+      <c r="E173" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="F173" s="28"/>
+    </row>
+    <row r="174" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A174" s="32"/>
+      <c r="B174" s="30"/>
+      <c r="C174" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="E172" s="7">
-        <v>4</v>
-      </c>
-      <c r="F172" s="2"/>
-    </row>
-    <row r="173" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A173" s="27"/>
-      <c r="B173" s="15"/>
-      <c r="C173" s="6" t="s">
+      <c r="D174" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="D173" s="6" t="s">
+      <c r="E174" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="F174" s="28"/>
+    </row>
+    <row r="175" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A175" s="32"/>
+      <c r="B175" s="30"/>
+      <c r="C175" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E173" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="F173" s="2"/>
-    </row>
-    <row r="174" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A174" s="27"/>
-      <c r="B174" s="15"/>
-      <c r="C174" s="6" t="s">
+      <c r="D175" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="D174" s="6" t="s">
+      <c r="E175" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="F175" s="28"/>
+    </row>
+    <row r="176" spans="1:6" ht="186.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A176" s="33"/>
+      <c r="B176" s="31"/>
+      <c r="C176" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D176" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="E174" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="F174" s="2"/>
-    </row>
-    <row r="175" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A175" s="27"/>
-      <c r="B175" s="15"/>
-      <c r="C175" s="6" t="s">
+      <c r="E176" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F176" s="29"/>
+    </row>
+    <row r="177" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+      <c r="A177" s="20" t="s">
         <v>353</v>
       </c>
-      <c r="D175" s="6" t="s">
+      <c r="B177" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="E175" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="F175" s="2"/>
-    </row>
-    <row r="176" spans="1:6" ht="186.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A176" s="42"/>
-      <c r="B176" s="18"/>
-      <c r="C176" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D176" s="12" t="s">
+      <c r="C177" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="E176" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F176" s="3"/>
-    </row>
-    <row r="177" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A177" s="26" t="s">
+      <c r="D177" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="B177" s="17" t="s">
-        <v>357</v>
-      </c>
-      <c r="C177" s="10" t="s">
-        <v>358</v>
-      </c>
-      <c r="D177" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="E177" s="11">
+      <c r="E177" s="8">
         <v>1</v>
       </c>
-      <c r="F177" s="1">
+      <c r="F177" s="16">
         <f>SUM(E177:E195)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A178" s="27"/>
-      <c r="B178" s="15"/>
-      <c r="C178" s="6" t="s">
+      <c r="A178" s="32"/>
+      <c r="B178" s="30"/>
+      <c r="C178" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E178" s="4">
+        <v>1</v>
+      </c>
+      <c r="F178" s="28"/>
+    </row>
+    <row r="179" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A179" s="32"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D179" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D178" s="6" t="s">
+      <c r="E179" s="4">
+        <v>1</v>
+      </c>
+      <c r="F179" s="28"/>
+    </row>
+    <row r="180" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A180" s="32"/>
+      <c r="B180" s="30"/>
+      <c r="C180" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="E178" s="7">
+      <c r="D180" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E180" s="4">
         <v>1</v>
       </c>
-      <c r="F178" s="2"/>
-    </row>
-    <row r="179" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A179" s="27"/>
-      <c r="B179" s="15"/>
-      <c r="C179" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="D179" s="6" t="s">
+      <c r="F180" s="28"/>
+    </row>
+    <row r="181" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A181" s="32"/>
+      <c r="B181" s="30"/>
+      <c r="C181" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E179" s="7">
+      <c r="D181" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E181" s="4">
         <v>1</v>
       </c>
-      <c r="F179" s="2"/>
-    </row>
-    <row r="180" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A180" s="27"/>
-      <c r="B180" s="15"/>
-      <c r="C180" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="D180" s="6" t="s">
+      <c r="F181" s="28"/>
+    </row>
+    <row r="182" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A182" s="32"/>
+      <c r="B182" s="30"/>
+      <c r="C182" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="E180" s="7">
+      <c r="D182" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="E182" s="4">
         <v>1</v>
       </c>
-      <c r="F180" s="2"/>
-    </row>
-    <row r="181" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A181" s="27"/>
-      <c r="B181" s="15"/>
-      <c r="C181" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D181" s="6" t="s">
+      <c r="F182" s="28"/>
+    </row>
+    <row r="183" spans="1:6" ht="31" x14ac:dyDescent="0.35">
+      <c r="A183" s="32"/>
+      <c r="B183" s="30"/>
+      <c r="C183" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="E181" s="7">
+      <c r="D183" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E183" s="4">
         <v>1</v>
       </c>
-      <c r="F181" s="2"/>
-    </row>
-    <row r="182" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A182" s="27"/>
-      <c r="B182" s="15"/>
-      <c r="C182" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D182" s="6" t="s">
+      <c r="F183" s="28"/>
+    </row>
+    <row r="184" spans="1:6" ht="201.5" x14ac:dyDescent="0.35">
+      <c r="A184" s="32"/>
+      <c r="B184" s="30"/>
+      <c r="C184" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="E182" s="7">
-        <v>1</v>
-      </c>
-      <c r="F182" s="2"/>
-    </row>
-    <row r="183" spans="1:6" ht="31" x14ac:dyDescent="0.35">
-      <c r="A183" s="27"/>
-      <c r="B183" s="15"/>
-      <c r="C183" s="6" t="s">
+      <c r="D184" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="D183" s="6" t="s">
+      <c r="E184" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="F184" s="28"/>
+    </row>
+    <row r="185" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A185" s="32"/>
+      <c r="B185" s="30"/>
+      <c r="C185" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="E183" s="7">
-        <v>1</v>
-      </c>
-      <c r="F183" s="2"/>
-    </row>
-    <row r="184" spans="1:6" ht="201.5" x14ac:dyDescent="0.35">
-      <c r="A184" s="27"/>
-      <c r="B184" s="15"/>
-      <c r="C184" s="6" t="s">
+      <c r="D185" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="D184" s="6" t="s">
+      <c r="E185" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="F185" s="28"/>
+    </row>
+    <row r="186" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A186" s="32"/>
+      <c r="B186" s="30"/>
+      <c r="C186" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E184" s="7">
+      <c r="D186" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E186" s="4">
         <v>2.75</v>
       </c>
-      <c r="F184" s="2"/>
-    </row>
-    <row r="185" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A185" s="27"/>
-      <c r="B185" s="15"/>
-      <c r="C185" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="D185" s="6" t="s">
+      <c r="F186" s="28"/>
+    </row>
+    <row r="187" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A187" s="32"/>
+      <c r="B187" s="30"/>
+      <c r="C187" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E185" s="7">
+      <c r="D187" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="E187" s="4">
+        <v>4</v>
+      </c>
+      <c r="F187" s="28"/>
+    </row>
+    <row r="188" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A188" s="32"/>
+      <c r="B188" s="30"/>
+      <c r="C188" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="E188" s="4">
+        <v>4</v>
+      </c>
+      <c r="F188" s="28"/>
+    </row>
+    <row r="189" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A189" s="32"/>
+      <c r="B189" s="30"/>
+      <c r="C189" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E189" s="4">
         <v>2.75</v>
       </c>
-      <c r="F185" s="2"/>
-    </row>
-    <row r="186" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A186" s="27"/>
-      <c r="B186" s="15"/>
-      <c r="C186" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="D186" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E186" s="7">
+      <c r="F189" s="28"/>
+    </row>
+    <row r="190" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A190" s="32"/>
+      <c r="B190" s="30"/>
+      <c r="C190" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E190" s="4">
         <v>2.75</v>
       </c>
-      <c r="F186" s="2"/>
-    </row>
-    <row r="187" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A187" s="27"/>
-      <c r="B187" s="15"/>
-      <c r="C187" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="D187" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="E187" s="7">
-        <v>4</v>
-      </c>
-      <c r="F187" s="2"/>
-    </row>
-    <row r="188" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A188" s="27"/>
-      <c r="B188" s="15"/>
-      <c r="C188" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="D188" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="E188" s="7">
-        <v>4</v>
-      </c>
-      <c r="F188" s="2"/>
-    </row>
-    <row r="189" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A189" s="27"/>
-      <c r="B189" s="15"/>
-      <c r="C189" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="D189" s="6" t="s">
+      <c r="F190" s="28"/>
+    </row>
+    <row r="191" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A191" s="32"/>
+      <c r="B191" s="30"/>
+      <c r="C191" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E189" s="7">
+      <c r="D191" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E191" s="4">
         <v>2.75</v>
       </c>
-      <c r="F189" s="2"/>
-    </row>
-    <row r="190" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A190" s="27"/>
-      <c r="B190" s="15"/>
-      <c r="C190" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="D190" s="6" t="s">
+      <c r="F191" s="28"/>
+    </row>
+    <row r="192" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A192" s="32"/>
+      <c r="B192" s="30"/>
+      <c r="C192" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="E190" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="F190" s="2"/>
-    </row>
-    <row r="191" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A191" s="27"/>
-      <c r="B191" s="15"/>
-      <c r="C191" s="6" t="s">
+      <c r="D192" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="D191" s="6" t="s">
+      <c r="E192" s="4">
+        <v>4</v>
+      </c>
+      <c r="F192" s="28"/>
+    </row>
+    <row r="193" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A193" s="32"/>
+      <c r="B193" s="30"/>
+      <c r="C193" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E191" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="F191" s="2"/>
-    </row>
-    <row r="192" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A192" s="27"/>
-      <c r="B192" s="15"/>
-      <c r="C192" s="6" t="s">
+      <c r="D193" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="D192" s="6" t="s">
+      <c r="E193" s="4">
+        <v>2.25</v>
+      </c>
+      <c r="F193" s="28"/>
+    </row>
+    <row r="194" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A194" s="32"/>
+      <c r="B194" s="30"/>
+      <c r="C194" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="E192" s="7">
-        <v>4</v>
-      </c>
-      <c r="F192" s="2"/>
-    </row>
-    <row r="193" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A193" s="27"/>
-      <c r="B193" s="15"/>
-      <c r="C193" s="6" t="s">
+      <c r="D194" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E194" s="4">
+        <v>2.25</v>
+      </c>
+      <c r="F194" s="28"/>
+    </row>
+    <row r="195" spans="1:6" ht="171" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A195" s="33"/>
+      <c r="B195" s="31"/>
+      <c r="C195" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D195" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="D193" s="6" t="s">
+      <c r="E195" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F195" s="29"/>
+    </row>
+    <row r="196" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A196" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="E193" s="7">
-        <v>2.25</v>
-      </c>
-      <c r="F193" s="2"/>
-    </row>
-    <row r="194" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A194" s="27"/>
-      <c r="B194" s="15"/>
-      <c r="C194" s="6" t="s">
+      <c r="B196" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="D194" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="E194" s="7">
-        <v>2.25</v>
-      </c>
-      <c r="F194" s="2"/>
-    </row>
-    <row r="195" spans="1:6" ht="171" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A195" s="42"/>
-      <c r="B195" s="18"/>
-      <c r="C195" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D195" s="12" t="s">
+      <c r="C196" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="E195" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F195" s="3"/>
-    </row>
-    <row r="196" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A196" s="26" t="s">
+      <c r="D196" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="B196" s="17" t="s">
-        <v>395</v>
-      </c>
-      <c r="C196" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="D196" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="E196" s="11">
+      <c r="E196" s="8">
         <v>1.25</v>
       </c>
-      <c r="F196" s="1">
+      <c r="F196" s="16">
         <f>SUM(E196:E214)</f>
         <v>42.5</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A197" s="27"/>
-      <c r="B197" s="15"/>
-      <c r="C197" s="6" t="s">
+      <c r="A197" s="32"/>
+      <c r="B197" s="30"/>
+      <c r="C197" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E197" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F197" s="28"/>
+    </row>
+    <row r="198" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A198" s="32"/>
+      <c r="B198" s="30"/>
+      <c r="C198" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="D198" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="D197" s="6" t="s">
+      <c r="E198" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F198" s="28"/>
+    </row>
+    <row r="199" spans="1:6" ht="62" x14ac:dyDescent="0.35">
+      <c r="A199" s="32"/>
+      <c r="B199" s="30"/>
+      <c r="C199" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="E197" s="7">
+      <c r="D199" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E199" s="4">
         <v>1.25</v>
       </c>
-      <c r="F197" s="2"/>
-    </row>
-    <row r="198" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A198" s="27"/>
-      <c r="B198" s="15"/>
-      <c r="C198" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="D198" s="6" t="s">
+      <c r="F199" s="28"/>
+    </row>
+    <row r="200" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A200" s="32"/>
+      <c r="B200" s="30"/>
+      <c r="C200" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="E198" s="7">
+      <c r="D200" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E200" s="4">
         <v>1.25</v>
       </c>
-      <c r="F198" s="2"/>
-    </row>
-    <row r="199" spans="1:6" ht="62" x14ac:dyDescent="0.35">
-      <c r="A199" s="27"/>
-      <c r="B199" s="15"/>
-      <c r="C199" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="D199" s="6" t="s">
+      <c r="F200" s="28"/>
+    </row>
+    <row r="201" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A201" s="32"/>
+      <c r="B201" s="30"/>
+      <c r="C201" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="E199" s="7">
+      <c r="D201" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E201" s="4">
         <v>1.25</v>
       </c>
-      <c r="F199" s="2"/>
-    </row>
-    <row r="200" spans="1:6" ht="62" x14ac:dyDescent="0.35">
-      <c r="A200" s="27"/>
-      <c r="B200" s="15"/>
-      <c r="C200" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="D200" s="6" t="s">
+      <c r="F201" s="28"/>
+    </row>
+    <row r="202" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A202" s="32"/>
+      <c r="B202" s="30"/>
+      <c r="C202" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="E200" s="7">
-        <v>1.25</v>
-      </c>
-      <c r="F200" s="2"/>
-    </row>
-    <row r="201" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A201" s="27"/>
-      <c r="B201" s="15"/>
-      <c r="C201" s="6" t="s">
+      <c r="D202" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D201" s="6" t="s">
+      <c r="E202" s="4">
+        <v>4</v>
+      </c>
+      <c r="F202" s="28"/>
+    </row>
+    <row r="203" spans="1:6" ht="186" x14ac:dyDescent="0.35">
+      <c r="A203" s="32"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E201" s="7">
-        <v>1.25</v>
-      </c>
-      <c r="F201" s="2"/>
-    </row>
-    <row r="202" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A202" s="27"/>
-      <c r="B202" s="15"/>
-      <c r="C202" s="6" t="s">
+      <c r="D203" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D202" s="6" t="s">
+      <c r="E203" s="4">
+        <v>4</v>
+      </c>
+      <c r="F203" s="28"/>
+    </row>
+    <row r="204" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A204" s="32"/>
+      <c r="B204" s="30"/>
+      <c r="C204" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="E202" s="7">
-        <v>4</v>
-      </c>
-      <c r="F202" s="2"/>
-    </row>
-    <row r="203" spans="1:6" ht="186" x14ac:dyDescent="0.35">
-      <c r="A203" s="27"/>
-      <c r="B203" s="15"/>
-      <c r="C203" s="6" t="s">
+      <c r="D204" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="D203" s="6" t="s">
+      <c r="E204" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="F204" s="28"/>
+    </row>
+    <row r="205" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A205" s="32"/>
+      <c r="B205" s="30"/>
+      <c r="C205" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="E203" s="7">
-        <v>4</v>
-      </c>
-      <c r="F203" s="2"/>
-    </row>
-    <row r="204" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A204" s="27"/>
-      <c r="B204" s="15"/>
-      <c r="C204" s="6" t="s">
+      <c r="D205" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="D204" s="6" t="s">
+      <c r="E205" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="F205" s="28"/>
+    </row>
+    <row r="206" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A206" s="32"/>
+      <c r="B206" s="30"/>
+      <c r="C206" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="E204" s="7">
+      <c r="D206" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E206" s="4">
         <v>2.75</v>
       </c>
-      <c r="F204" s="2"/>
-    </row>
-    <row r="205" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A205" s="27"/>
-      <c r="B205" s="15"/>
-      <c r="C205" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="D205" s="6" t="s">
+      <c r="F206" s="28"/>
+    </row>
+    <row r="207" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A207" s="32"/>
+      <c r="B207" s="30"/>
+      <c r="C207" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E205" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="F205" s="2"/>
-    </row>
-    <row r="206" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A206" s="27"/>
-      <c r="B206" s="15"/>
-      <c r="C206" s="6" t="s">
+      <c r="D207" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D206" s="6" t="s">
+      <c r="E207" s="4">
+        <v>4</v>
+      </c>
+      <c r="F207" s="28"/>
+    </row>
+    <row r="208" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A208" s="32"/>
+      <c r="B208" s="30"/>
+      <c r="C208" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="E206" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="F206" s="2"/>
-    </row>
-    <row r="207" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A207" s="27"/>
-      <c r="B207" s="15"/>
-      <c r="C207" s="6" t="s">
+      <c r="D208" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="D207" s="6" t="s">
+      <c r="E208" s="4">
+        <v>4</v>
+      </c>
+      <c r="F208" s="28"/>
+    </row>
+    <row r="209" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A209" s="32"/>
+      <c r="B209" s="30"/>
+      <c r="C209" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="E207" s="7">
-        <v>4</v>
-      </c>
-      <c r="F207" s="2"/>
-    </row>
-    <row r="208" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A208" s="27"/>
-      <c r="B208" s="15"/>
-      <c r="C208" s="6" t="s">
+      <c r="D209" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D208" s="6" t="s">
+      <c r="E209" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="F209" s="28"/>
+    </row>
+    <row r="210" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A210" s="32"/>
+      <c r="B210" s="30"/>
+      <c r="C210" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="E208" s="7">
-        <v>4</v>
-      </c>
-      <c r="F208" s="2"/>
-    </row>
-    <row r="209" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A209" s="27"/>
-      <c r="B209" s="15"/>
-      <c r="C209" s="6" t="s">
+      <c r="D210" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="D209" s="6" t="s">
+      <c r="E210" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="F210" s="28"/>
+    </row>
+    <row r="211" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A211" s="32"/>
+      <c r="B211" s="30"/>
+      <c r="C211" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="E209" s="7">
+      <c r="D211" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E211" s="4">
         <v>1.5</v>
       </c>
-      <c r="F209" s="2"/>
-    </row>
-    <row r="210" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A210" s="27"/>
-      <c r="B210" s="15"/>
-      <c r="C210" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="D210" s="6" t="s">
+      <c r="F211" s="28"/>
+    </row>
+    <row r="212" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A212" s="32"/>
+      <c r="B212" s="30"/>
+      <c r="C212" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="E210" s="7">
+      <c r="D212" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E212" s="4">
         <v>1.5</v>
       </c>
-      <c r="F210" s="2"/>
-    </row>
-    <row r="211" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A211" s="27"/>
-      <c r="B211" s="15"/>
-      <c r="C211" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="D211" s="6" t="s">
+      <c r="F212" s="28"/>
+    </row>
+    <row r="213" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A213" s="32"/>
+      <c r="B213" s="30"/>
+      <c r="C213" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="E211" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="F211" s="2"/>
-    </row>
-    <row r="212" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A212" s="27"/>
-      <c r="B212" s="15"/>
-      <c r="C212" s="6" t="s">
+      <c r="D213" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="D212" s="6" t="s">
+      <c r="E213" s="4">
+        <v>2.25</v>
+      </c>
+      <c r="F213" s="28"/>
+    </row>
+    <row r="214" spans="1:6" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A214" s="33"/>
+      <c r="B214" s="31"/>
+      <c r="C214" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D214" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="E212" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="F212" s="2"/>
-    </row>
-    <row r="213" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A213" s="27"/>
-      <c r="B213" s="15"/>
-      <c r="C213" s="6" t="s">
+      <c r="E214" s="10">
+        <v>2.5</v>
+      </c>
+      <c r="F214" s="29"/>
+    </row>
+    <row r="215" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A215" s="20" t="s">
         <v>430</v>
       </c>
-      <c r="D213" s="6" t="s">
+      <c r="B215" s="18" t="s">
         <v>431</v>
       </c>
-      <c r="E213" s="7">
-        <v>2.25</v>
-      </c>
-      <c r="F213" s="2"/>
-    </row>
-    <row r="214" spans="1:6" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A214" s="42"/>
-      <c r="B214" s="18"/>
-      <c r="C214" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D214" s="12" t="s">
+      <c r="C215" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="E214" s="13">
-        <v>2.5</v>
-      </c>
-      <c r="F214" s="3"/>
-    </row>
-    <row r="215" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A215" s="26" t="s">
-        <v>433</v>
-      </c>
-      <c r="B215" s="17" t="s">
-        <v>434</v>
-      </c>
-      <c r="C215" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="D215" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E215" s="11">
-        <v>4</v>
-      </c>
-      <c r="F215" s="1">
+      <c r="D215" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E215" s="8">
+        <v>4</v>
+      </c>
+      <c r="F215" s="16">
         <f>SUM(E215:E224)</f>
         <v>40</v>
       </c>
     </row>
     <row r="216" spans="1:6" ht="201.5" x14ac:dyDescent="0.35">
-      <c r="A216" s="27"/>
-      <c r="B216" s="15"/>
-      <c r="C216" s="6" t="s">
+      <c r="A216" s="32"/>
+      <c r="B216" s="30"/>
+      <c r="C216" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="E216" s="4">
+        <v>4</v>
+      </c>
+      <c r="F216" s="28"/>
+    </row>
+    <row r="217" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A217" s="32"/>
+      <c r="B217" s="30"/>
+      <c r="C217" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E217" s="4">
+        <v>4</v>
+      </c>
+      <c r="F217" s="28"/>
+    </row>
+    <row r="218" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A218" s="32"/>
+      <c r="B218" s="30"/>
+      <c r="C218" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="D216" s="6" t="s">
+      <c r="D218" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E218" s="4">
+        <v>4</v>
+      </c>
+      <c r="F218" s="28"/>
+    </row>
+    <row r="219" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A219" s="32"/>
+      <c r="B219" s="30"/>
+      <c r="C219" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="E216" s="7">
-        <v>4</v>
-      </c>
-      <c r="F216" s="2"/>
-    </row>
-    <row r="217" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A217" s="27"/>
-      <c r="B217" s="15"/>
-      <c r="C217" s="6" t="s">
+      <c r="D219" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E219" s="4">
+        <v>4</v>
+      </c>
+      <c r="F219" s="28"/>
+    </row>
+    <row r="220" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A220" s="32"/>
+      <c r="B220" s="30"/>
+      <c r="C220" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="D217" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E217" s="7">
-        <v>4</v>
-      </c>
-      <c r="F217" s="2"/>
-    </row>
-    <row r="218" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A218" s="27"/>
-      <c r="B218" s="15"/>
-      <c r="C218" s="6" t="s">
+      <c r="D220" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="D218" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E218" s="7">
-        <v>4</v>
-      </c>
-      <c r="F218" s="2"/>
-    </row>
-    <row r="219" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A219" s="27"/>
-      <c r="B219" s="15"/>
-      <c r="C219" s="6" t="s">
+      <c r="E220" s="4">
+        <v>4</v>
+      </c>
+      <c r="F220" s="28"/>
+    </row>
+    <row r="221" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A221" s="32"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D219" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E219" s="7">
-        <v>4</v>
-      </c>
-      <c r="F219" s="2"/>
-    </row>
-    <row r="220" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A220" s="27"/>
-      <c r="B220" s="15"/>
-      <c r="C220" s="6" t="s">
+      <c r="D221" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E221" s="4">
+        <v>4</v>
+      </c>
+      <c r="F221" s="28"/>
+    </row>
+    <row r="222" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A222" s="32"/>
+      <c r="B222" s="30"/>
+      <c r="C222" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="D220" s="6" t="s">
+      <c r="D222" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E220" s="7">
-        <v>4</v>
-      </c>
-      <c r="F220" s="2"/>
-    </row>
-    <row r="221" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A221" s="27"/>
-      <c r="B221" s="15"/>
-      <c r="C221" s="6" t="s">
+      <c r="E222" s="4">
+        <v>4</v>
+      </c>
+      <c r="F222" s="28"/>
+    </row>
+    <row r="223" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A223" s="32"/>
+      <c r="B223" s="30"/>
+      <c r="C223" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="D221" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E221" s="7">
-        <v>4</v>
-      </c>
-      <c r="F221" s="2"/>
-    </row>
-    <row r="222" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A222" s="27"/>
-      <c r="B222" s="15"/>
-      <c r="C222" s="6" t="s">
+      <c r="D223" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E223" s="4">
+        <v>4</v>
+      </c>
+      <c r="F223" s="28"/>
+    </row>
+    <row r="224" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A224" s="33"/>
+      <c r="B224" s="31"/>
+      <c r="C224" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="D222" s="6" t="s">
+      <c r="D224" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="E224" s="10">
+        <v>4</v>
+      </c>
+      <c r="F224" s="29"/>
+    </row>
+    <row r="225" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A225" s="20" t="s">
         <v>445</v>
       </c>
-      <c r="E222" s="7">
-        <v>4</v>
-      </c>
-      <c r="F222" s="2"/>
-    </row>
-    <row r="223" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A223" s="27"/>
-      <c r="B223" s="15"/>
-      <c r="C223" s="6" t="s">
+      <c r="B225" s="18" t="s">
         <v>446</v>
       </c>
-      <c r="D223" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E223" s="7">
-        <v>4</v>
-      </c>
-      <c r="F223" s="2"/>
-    </row>
-    <row r="224" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A224" s="42"/>
-      <c r="B224" s="18"/>
-      <c r="C224" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="D224" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="E224" s="13">
-        <v>4</v>
-      </c>
-      <c r="F224" s="3"/>
-    </row>
-    <row r="225" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A225" s="26" t="s">
-        <v>448</v>
-      </c>
-      <c r="B225" s="17" t="s">
-        <v>449</v>
-      </c>
-      <c r="C225" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D225" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E225" s="11">
-        <v>4</v>
-      </c>
-      <c r="F225" s="1">
+      <c r="C225" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E225" s="8">
+        <v>4</v>
+      </c>
+      <c r="F225" s="16">
         <f>SUM(E225:E241)</f>
         <v>41.5</v>
       </c>
     </row>
     <row r="226" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A226" s="27"/>
-      <c r="B226" s="15"/>
-      <c r="C226" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D226" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E226" s="7">
-        <v>4</v>
-      </c>
-      <c r="F226" s="2"/>
+      <c r="A226" s="32"/>
+      <c r="B226" s="30"/>
+      <c r="C226" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E226" s="4">
+        <v>4</v>
+      </c>
+      <c r="F226" s="28"/>
     </row>
     <row r="227" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A227" s="27"/>
-      <c r="B227" s="15"/>
-      <c r="C227" s="6" t="s">
+      <c r="A227" s="32"/>
+      <c r="B227" s="30"/>
+      <c r="C227" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E227" s="4">
+        <v>4</v>
+      </c>
+      <c r="F227" s="28"/>
+    </row>
+    <row r="228" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A228" s="32"/>
+      <c r="B228" s="30"/>
+      <c r="C228" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D228" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D227" s="6" t="s">
+      <c r="E228" s="4">
+        <v>4</v>
+      </c>
+      <c r="F228" s="28"/>
+    </row>
+    <row r="229" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A229" s="32"/>
+      <c r="B229" s="30"/>
+      <c r="C229" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E227" s="7">
-        <v>4</v>
-      </c>
-      <c r="F227" s="2"/>
-    </row>
-    <row r="228" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A228" s="27"/>
-      <c r="B228" s="15"/>
-      <c r="C228" s="6" t="s">
+      <c r="D229" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="D228" s="6" t="s">
+      <c r="E229" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="F229" s="28"/>
+    </row>
+    <row r="230" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A230" s="32"/>
+      <c r="B230" s="30"/>
+      <c r="C230" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="E228" s="7">
-        <v>4</v>
-      </c>
-      <c r="F228" s="2"/>
-    </row>
-    <row r="229" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A229" s="27"/>
-      <c r="B229" s="15"/>
-      <c r="C229" s="6" t="s">
+      <c r="D230" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="D229" s="6" t="s">
+      <c r="E230" s="4">
+        <v>2.75</v>
+      </c>
+      <c r="F230" s="28"/>
+    </row>
+    <row r="231" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A231" s="32"/>
+      <c r="B231" s="30"/>
+      <c r="C231" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="E229" s="7">
+      <c r="D231" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="E231" s="4">
         <v>2.75</v>
       </c>
-      <c r="F229" s="2"/>
-    </row>
-    <row r="230" spans="1:6" ht="108.5" x14ac:dyDescent="0.35">
-      <c r="A230" s="27"/>
-      <c r="B230" s="15"/>
-      <c r="C230" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="D230" s="6" t="s">
+      <c r="F231" s="28"/>
+    </row>
+    <row r="232" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A232" s="32"/>
+      <c r="B232" s="30"/>
+      <c r="C232" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="E230" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="F230" s="2"/>
-    </row>
-    <row r="231" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A231" s="27"/>
-      <c r="B231" s="15"/>
-      <c r="C231" s="6" t="s">
+      <c r="D232" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="D231" s="6" t="s">
+      <c r="E232" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F232" s="28"/>
+    </row>
+    <row r="233" spans="1:6" ht="62" x14ac:dyDescent="0.35">
+      <c r="A233" s="32"/>
+      <c r="B233" s="30"/>
+      <c r="C233" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="E231" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="F231" s="2"/>
-    </row>
-    <row r="232" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A232" s="27"/>
-      <c r="B232" s="15"/>
-      <c r="C232" s="6" t="s">
+      <c r="D233" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="D232" s="6" t="s">
+      <c r="E233" s="4">
+        <v>1.25</v>
+      </c>
+      <c r="F233" s="28"/>
+    </row>
+    <row r="234" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A234" s="32"/>
+      <c r="B234" s="30"/>
+      <c r="C234" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="E232" s="7">
+      <c r="D234" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="E234" s="4">
         <v>1.25</v>
       </c>
-      <c r="F232" s="2"/>
-    </row>
-    <row r="233" spans="1:6" ht="62" x14ac:dyDescent="0.35">
-      <c r="A233" s="27"/>
-      <c r="B233" s="15"/>
-      <c r="C233" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="D233" s="6" t="s">
+      <c r="F234" s="28"/>
+    </row>
+    <row r="235" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A235" s="32"/>
+      <c r="B235" s="30"/>
+      <c r="C235" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="E233" s="7">
+      <c r="D235" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="E235" s="4">
         <v>1.25</v>
       </c>
-      <c r="F233" s="2"/>
-    </row>
-    <row r="234" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A234" s="27"/>
-      <c r="B234" s="15"/>
-      <c r="C234" s="6" t="s">
-        <v>464</v>
-      </c>
-      <c r="D234" s="6" t="s">
+      <c r="F235" s="28"/>
+    </row>
+    <row r="236" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A236" s="32"/>
+      <c r="B236" s="30"/>
+      <c r="C236" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="E234" s="7">
+      <c r="D236" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E236" s="4">
         <v>1.25</v>
       </c>
-      <c r="F234" s="2"/>
-    </row>
-    <row r="235" spans="1:6" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A235" s="27"/>
-      <c r="B235" s="15"/>
-      <c r="C235" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="D235" s="6" t="s">
+      <c r="F236" s="28"/>
+    </row>
+    <row r="237" spans="1:6" ht="62" x14ac:dyDescent="0.35">
+      <c r="A237" s="32"/>
+      <c r="B237" s="30"/>
+      <c r="C237" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="E235" s="7">
+      <c r="D237" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E237" s="4">
         <v>1.25</v>
       </c>
-      <c r="F235" s="2"/>
-    </row>
-    <row r="236" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A236" s="27"/>
-      <c r="B236" s="15"/>
-      <c r="C236" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="D236" s="6" t="s">
+      <c r="F237" s="28"/>
+    </row>
+    <row r="238" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A238" s="32"/>
+      <c r="B238" s="30"/>
+      <c r="C238" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="E236" s="7">
-        <v>1.25</v>
-      </c>
-      <c r="F236" s="2"/>
-    </row>
-    <row r="237" spans="1:6" ht="62" x14ac:dyDescent="0.35">
-      <c r="A237" s="27"/>
-      <c r="B237" s="15"/>
-      <c r="C237" s="6" t="s">
+      <c r="D238" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="D237" s="6" t="s">
+      <c r="E238" s="4">
+        <v>4</v>
+      </c>
+      <c r="F238" s="28"/>
+    </row>
+    <row r="239" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A239" s="32"/>
+      <c r="B239" s="30"/>
+      <c r="C239" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="E237" s="7">
-        <v>1.25</v>
-      </c>
-      <c r="F237" s="2"/>
-    </row>
-    <row r="238" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A238" s="27"/>
-      <c r="B238" s="15"/>
-      <c r="C238" s="6" t="s">
+      <c r="D239" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="D238" s="6" t="s">
+      <c r="E239" s="4">
+        <v>2</v>
+      </c>
+      <c r="F239" s="28"/>
+    </row>
+    <row r="240" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A240" s="32"/>
+      <c r="B240" s="30"/>
+      <c r="C240" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E238" s="7">
-        <v>4</v>
-      </c>
-      <c r="F238" s="2"/>
-    </row>
-    <row r="239" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A239" s="27"/>
-      <c r="B239" s="15"/>
-      <c r="C239" s="6" t="s">
+      <c r="D240" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="D239" s="6" t="s">
+      <c r="E240" s="4">
+        <v>2.25</v>
+      </c>
+      <c r="F240" s="28"/>
+    </row>
+    <row r="241" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A241" s="33"/>
+      <c r="B241" s="31"/>
+      <c r="C241" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D241" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="E239" s="7">
-        <v>2</v>
-      </c>
-      <c r="F239" s="2"/>
-    </row>
-    <row r="240" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A240" s="27"/>
-      <c r="B240" s="15"/>
-      <c r="C240" s="6" t="s">
+      <c r="E241" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="F241" s="29"/>
+    </row>
+    <row r="242" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A242" s="20" t="s">
         <v>476</v>
       </c>
-      <c r="D240" s="6" t="s">
+      <c r="B242" s="18" t="s">
         <v>477</v>
       </c>
-      <c r="E240" s="7">
-        <v>2.25</v>
-      </c>
-      <c r="F240" s="2"/>
-    </row>
-    <row r="241" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A241" s="42"/>
-      <c r="B241" s="18"/>
-      <c r="C241" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D241" s="12" t="s">
+      <c r="C242" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="E241" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="F241" s="3"/>
-    </row>
-    <row r="242" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A242" s="26" t="s">
+      <c r="D242" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="B242" s="17" t="s">
-        <v>480</v>
-      </c>
-      <c r="C242" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="D242" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="E242" s="11">
-        <v>4</v>
-      </c>
-      <c r="F242" s="1">
+      <c r="E242" s="8">
+        <v>4</v>
+      </c>
+      <c r="F242" s="16">
         <f>SUM(E242:E252)</f>
         <v>41.5</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A243" s="27"/>
-      <c r="B243" s="15"/>
-      <c r="C243" s="6" t="s">
+      <c r="A243" s="32"/>
+      <c r="B243" s="30"/>
+      <c r="C243" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="E243" s="4">
+        <v>4</v>
+      </c>
+      <c r="F243" s="28"/>
+    </row>
+    <row r="244" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A244" s="32"/>
+      <c r="B244" s="30"/>
+      <c r="C244" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D244" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="D243" s="6" t="s">
+      <c r="E244" s="4">
+        <v>4</v>
+      </c>
+      <c r="F244" s="28"/>
+    </row>
+    <row r="245" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A245" s="32"/>
+      <c r="B245" s="30"/>
+      <c r="C245" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="E243" s="7">
-        <v>4</v>
-      </c>
-      <c r="F243" s="2"/>
-    </row>
-    <row r="244" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A244" s="27"/>
-      <c r="B244" s="15"/>
-      <c r="C244" s="6" t="s">
+      <c r="D245" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="D244" s="6" t="s">
+      <c r="E245" s="4">
+        <v>4</v>
+      </c>
+      <c r="F245" s="28"/>
+    </row>
+    <row r="246" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A246" s="32"/>
+      <c r="B246" s="30"/>
+      <c r="C246" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="E244" s="7">
-        <v>4</v>
-      </c>
-      <c r="F244" s="2"/>
-    </row>
-    <row r="245" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A245" s="27"/>
-      <c r="B245" s="15"/>
-      <c r="C245" s="6" t="s">
+      <c r="D246" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="D245" s="6" t="s">
+      <c r="E246" s="4">
+        <v>4</v>
+      </c>
+      <c r="F246" s="28"/>
+    </row>
+    <row r="247" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A247" s="32"/>
+      <c r="B247" s="30"/>
+      <c r="C247" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="E245" s="7">
-        <v>4</v>
-      </c>
-      <c r="F245" s="2"/>
-    </row>
-    <row r="246" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A246" s="27"/>
-      <c r="B246" s="15"/>
-      <c r="C246" s="6" t="s">
+      <c r="D247" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="D246" s="6" t="s">
+      <c r="E247" s="4">
+        <v>4</v>
+      </c>
+      <c r="F247" s="28"/>
+    </row>
+    <row r="248" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A248" s="32"/>
+      <c r="B248" s="30"/>
+      <c r="C248" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="E246" s="7">
-        <v>4</v>
-      </c>
-      <c r="F246" s="2"/>
-    </row>
-    <row r="247" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A247" s="27"/>
-      <c r="B247" s="15"/>
-      <c r="C247" s="6" t="s">
+      <c r="D248" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="D247" s="6" t="s">
+      <c r="E248" s="4">
+        <v>4</v>
+      </c>
+      <c r="F248" s="28"/>
+    </row>
+    <row r="249" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A249" s="32"/>
+      <c r="B249" s="30"/>
+      <c r="C249" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="E247" s="7">
-        <v>4</v>
-      </c>
-      <c r="F247" s="2"/>
-    </row>
-    <row r="248" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A248" s="27"/>
-      <c r="B248" s="15"/>
-      <c r="C248" s="6" t="s">
+      <c r="D249" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="D248" s="6" t="s">
+      <c r="E249" s="4">
+        <v>4</v>
+      </c>
+      <c r="F249" s="28"/>
+    </row>
+    <row r="250" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A250" s="32"/>
+      <c r="B250" s="30"/>
+      <c r="C250" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="E248" s="7">
-        <v>4</v>
-      </c>
-      <c r="F248" s="2"/>
-    </row>
-    <row r="249" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A249" s="27"/>
-      <c r="B249" s="15"/>
-      <c r="C249" s="6" t="s">
+      <c r="D250" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="D249" s="6" t="s">
+      <c r="E250" s="4">
+        <v>4</v>
+      </c>
+      <c r="F250" s="28"/>
+    </row>
+    <row r="251" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A251" s="32"/>
+      <c r="B251" s="30"/>
+      <c r="C251" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="E249" s="7">
-        <v>4</v>
-      </c>
-      <c r="F249" s="2"/>
-    </row>
-    <row r="250" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A250" s="27"/>
-      <c r="B250" s="15"/>
-      <c r="C250" s="6" t="s">
+      <c r="D251" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="D250" s="6" t="s">
+      <c r="E251" s="4">
+        <v>4</v>
+      </c>
+      <c r="F251" s="28"/>
+    </row>
+    <row r="252" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A252" s="33"/>
+      <c r="B252" s="31"/>
+      <c r="C252" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D252" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E252" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="F252" s="29"/>
+    </row>
+    <row r="253" spans="1:6" ht="124" x14ac:dyDescent="0.35">
+      <c r="A253" s="20" t="s">
         <v>498</v>
       </c>
-      <c r="E250" s="7">
-        <v>4</v>
-      </c>
-      <c r="F250" s="2"/>
-    </row>
-    <row r="251" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A251" s="27"/>
-      <c r="B251" s="15"/>
-      <c r="C251" s="6" t="s">
+      <c r="B253" s="18" t="s">
         <v>499</v>
       </c>
-      <c r="D251" s="6" t="s">
+      <c r="C253" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="E251" s="7">
-        <v>4</v>
-      </c>
-      <c r="F251" s="2"/>
-    </row>
-    <row r="252" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A252" s="42"/>
-      <c r="B252" s="18"/>
-      <c r="C252" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D252" s="12" t="s">
-        <v>478</v>
-      </c>
-      <c r="E252" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="F252" s="3"/>
-    </row>
-    <row r="253" spans="1:6" ht="124" x14ac:dyDescent="0.35">
-      <c r="A253" s="26" t="s">
+      <c r="D253" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="B253" s="17" t="s">
-        <v>502</v>
-      </c>
-      <c r="C253" s="10" t="s">
-        <v>503</v>
-      </c>
-      <c r="D253" s="10" t="s">
-        <v>504</v>
-      </c>
-      <c r="E253" s="11">
+      <c r="E253" s="8">
         <v>2</v>
       </c>
-      <c r="F253" s="1">
+      <c r="F253" s="16">
         <f>SUM(E253:E269)</f>
         <v>41.5</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A254" s="27"/>
-      <c r="B254" s="15"/>
-      <c r="C254" s="6" t="s">
+      <c r="A254" s="32"/>
+      <c r="B254" s="30"/>
+      <c r="C254" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="E254" s="4">
+        <v>2</v>
+      </c>
+      <c r="F254" s="28"/>
+    </row>
+    <row r="255" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A255" s="32"/>
+      <c r="B255" s="30"/>
+      <c r="C255" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D255" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="D254" s="6" t="s">
+      <c r="E255" s="4">
+        <v>2</v>
+      </c>
+      <c r="F255" s="28"/>
+    </row>
+    <row r="256" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A256" s="32"/>
+      <c r="B256" s="30"/>
+      <c r="C256" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="E254" s="7">
+      <c r="D256" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="E256" s="4">
         <v>2</v>
       </c>
-      <c r="F254" s="2"/>
-    </row>
-    <row r="255" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A255" s="27"/>
-      <c r="B255" s="15"/>
-      <c r="C255" s="6" t="s">
-        <v>507</v>
-      </c>
-      <c r="D255" s="6" t="s">
+      <c r="F256" s="28"/>
+    </row>
+    <row r="257" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A257" s="32"/>
+      <c r="B257" s="30"/>
+      <c r="C257" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="E255" s="7">
+      <c r="D257" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E257" s="4">
+        <v>4</v>
+      </c>
+      <c r="F257" s="28"/>
+    </row>
+    <row r="258" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A258" s="32"/>
+      <c r="B258" s="30"/>
+      <c r="C258" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="E258" s="4">
+        <v>4</v>
+      </c>
+      <c r="F258" s="28"/>
+    </row>
+    <row r="259" spans="1:6" ht="62" x14ac:dyDescent="0.35">
+      <c r="A259" s="32"/>
+      <c r="B259" s="30"/>
+      <c r="C259" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E259" s="4">
         <v>2</v>
       </c>
-      <c r="F255" s="2"/>
-    </row>
-    <row r="256" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A256" s="27"/>
-      <c r="B256" s="15"/>
-      <c r="C256" s="6" t="s">
-        <v>509</v>
-      </c>
-      <c r="D256" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="E256" s="7">
+      <c r="F259" s="28"/>
+    </row>
+    <row r="260" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A260" s="32"/>
+      <c r="B260" s="30"/>
+      <c r="C260" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E260" s="4">
         <v>2</v>
       </c>
-      <c r="F256" s="2"/>
-    </row>
-    <row r="257" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A257" s="27"/>
-      <c r="B257" s="15"/>
-      <c r="C257" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="D257" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="E257" s="7">
-        <v>4</v>
-      </c>
-      <c r="F257" s="2"/>
-    </row>
-    <row r="258" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A258" s="27"/>
-      <c r="B258" s="15"/>
-      <c r="C258" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="D258" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="E258" s="7">
-        <v>4</v>
-      </c>
-      <c r="F258" s="2"/>
-    </row>
-    <row r="259" spans="1:6" ht="62" x14ac:dyDescent="0.35">
-      <c r="A259" s="27"/>
-      <c r="B259" s="15"/>
-      <c r="C259" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="D259" s="6" t="s">
+      <c r="F260" s="28"/>
+    </row>
+    <row r="261" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A261" s="32"/>
+      <c r="B261" s="30"/>
+      <c r="C261" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="E259" s="7">
+      <c r="D261" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="E261" s="4">
         <v>2</v>
       </c>
-      <c r="F259" s="2"/>
-    </row>
-    <row r="260" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A260" s="27"/>
-      <c r="B260" s="15"/>
-      <c r="C260" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="D260" s="6" t="s">
+      <c r="F261" s="28"/>
+    </row>
+    <row r="262" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A262" s="32"/>
+      <c r="B262" s="30"/>
+      <c r="C262" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="E260" s="7">
+      <c r="D262" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E262" s="4">
         <v>2</v>
       </c>
-      <c r="F260" s="2"/>
-    </row>
-    <row r="261" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A261" s="27"/>
-      <c r="B261" s="15"/>
-      <c r="C261" s="6" t="s">
-        <v>519</v>
-      </c>
-      <c r="D261" s="6" t="s">
+      <c r="F262" s="28"/>
+    </row>
+    <row r="263" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A263" s="32"/>
+      <c r="B263" s="30"/>
+      <c r="C263" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="E261" s="7">
+      <c r="D263" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="E263" s="4">
         <v>2</v>
       </c>
-      <c r="F261" s="2"/>
-    </row>
-    <row r="262" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A262" s="27"/>
-      <c r="B262" s="15"/>
-      <c r="C262" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="D262" s="6" t="s">
+      <c r="F263" s="28"/>
+    </row>
+    <row r="264" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A264" s="32"/>
+      <c r="B264" s="30"/>
+      <c r="C264" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="E262" s="7">
+      <c r="D264" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="E264" s="4">
         <v>2</v>
       </c>
-      <c r="F262" s="2"/>
-    </row>
-    <row r="263" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A263" s="27"/>
-      <c r="B263" s="15"/>
-      <c r="C263" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="D263" s="6" t="s">
+      <c r="F264" s="28"/>
+    </row>
+    <row r="265" spans="1:6" ht="93" x14ac:dyDescent="0.35">
+      <c r="A265" s="32"/>
+      <c r="B265" s="30"/>
+      <c r="C265" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="E263" s="7">
+      <c r="D265" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="E265" s="4">
         <v>2</v>
       </c>
-      <c r="F263" s="2"/>
-    </row>
-    <row r="264" spans="1:6" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A264" s="27"/>
-      <c r="B264" s="15"/>
-      <c r="C264" s="6" t="s">
-        <v>525</v>
-      </c>
-      <c r="D264" s="6" t="s">
+      <c r="F265" s="28"/>
+    </row>
+    <row r="266" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A266" s="32"/>
+      <c r="B266" s="30"/>
+      <c r="C266" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="E264" s="7">
+      <c r="D266" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="E266" s="4">
         <v>2</v>
       </c>
-      <c r="F264" s="2"/>
-    </row>
-    <row r="265" spans="1:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="A265" s="27"/>
-      <c r="B265" s="15"/>
-      <c r="C265" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="D265" s="6" t="s">
+      <c r="F266" s="28"/>
+    </row>
+    <row r="267" spans="1:6" ht="201.5" x14ac:dyDescent="0.35">
+      <c r="A267" s="32"/>
+      <c r="B267" s="30"/>
+      <c r="C267" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="E265" s="7">
-        <v>2</v>
-      </c>
-      <c r="F265" s="2"/>
-    </row>
-    <row r="266" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A266" s="27"/>
-      <c r="B266" s="15"/>
-      <c r="C266" s="6" t="s">
+      <c r="D267" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="D266" s="6" t="s">
+      <c r="E267" s="4">
+        <v>4</v>
+      </c>
+      <c r="F267" s="28"/>
+    </row>
+    <row r="268" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A268" s="32"/>
+      <c r="B268" s="30"/>
+      <c r="C268" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="E266" s="7">
-        <v>2</v>
-      </c>
-      <c r="F266" s="2"/>
-    </row>
-    <row r="267" spans="1:6" ht="201.5" x14ac:dyDescent="0.35">
-      <c r="A267" s="27"/>
-      <c r="B267" s="15"/>
-      <c r="C267" s="6" t="s">
+      <c r="D268" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="D267" s="6" t="s">
+      <c r="E268" s="4">
+        <v>4</v>
+      </c>
+      <c r="F268" s="28"/>
+    </row>
+    <row r="269" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A269" s="33"/>
+      <c r="B269" s="31"/>
+      <c r="C269" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D269" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="E269" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="F269" s="29"/>
+    </row>
+    <row r="270" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A270" s="20" t="s">
         <v>532</v>
       </c>
-      <c r="E267" s="7">
-        <v>4</v>
-      </c>
-      <c r="F267" s="2"/>
-    </row>
-    <row r="268" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A268" s="27"/>
-      <c r="B268" s="15"/>
-      <c r="C268" s="6" t="s">
+      <c r="B270" s="18" t="s">
         <v>533</v>
       </c>
-      <c r="D268" s="6" t="s">
+      <c r="C270" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="E268" s="7">
-        <v>4</v>
-      </c>
-      <c r="F268" s="2"/>
-    </row>
-    <row r="269" spans="1:6" ht="93.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A269" s="42"/>
-      <c r="B269" s="18"/>
-      <c r="C269" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="D269" s="12" t="s">
-        <v>478</v>
-      </c>
-      <c r="E269" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="F269" s="3"/>
-    </row>
-    <row r="270" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A270" s="26" t="s">
+      <c r="D270" s="7" t="s">
         <v>535</v>
       </c>
-      <c r="B270" s="17" t="s">
-        <v>536</v>
-      </c>
-      <c r="C270" s="10" t="s">
-        <v>537</v>
-      </c>
-      <c r="D270" s="10" t="s">
-        <v>538</v>
-      </c>
-      <c r="E270" s="11">
-        <v>4</v>
-      </c>
-      <c r="F270" s="1">
+      <c r="E270" s="8">
+        <v>4</v>
+      </c>
+      <c r="F270" s="16">
         <f>SUM(E270:E279)</f>
         <v>40</v>
       </c>
     </row>
     <row r="271" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A271" s="27"/>
-      <c r="B271" s="15"/>
-      <c r="C271" s="6" t="s">
+      <c r="A271" s="32"/>
+      <c r="B271" s="30"/>
+      <c r="C271" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="E271" s="4">
+        <v>4</v>
+      </c>
+      <c r="F271" s="28"/>
+    </row>
+    <row r="272" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A272" s="32"/>
+      <c r="B272" s="30"/>
+      <c r="C272" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="E272" s="4">
+        <v>4</v>
+      </c>
+      <c r="F272" s="28"/>
+    </row>
+    <row r="273" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A273" s="32"/>
+      <c r="B273" s="30"/>
+      <c r="C273" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="D271" s="6" t="s">
+      <c r="D273" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="E271" s="7">
-        <v>4</v>
-      </c>
-      <c r="F271" s="2"/>
-    </row>
-    <row r="272" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A272" s="27"/>
-      <c r="B272" s="15"/>
-      <c r="C272" s="6" t="s">
+      <c r="E273" s="4">
+        <v>4</v>
+      </c>
+      <c r="F273" s="28"/>
+    </row>
+    <row r="274" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A274" s="32"/>
+      <c r="B274" s="30"/>
+      <c r="C274" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="D272" s="6" t="s">
+      <c r="D274" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="E272" s="7">
-        <v>4</v>
-      </c>
-      <c r="F272" s="2"/>
-    </row>
-    <row r="273" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A273" s="27"/>
-      <c r="B273" s="15"/>
-      <c r="C273" s="6" t="s">
+      <c r="E274" s="4">
+        <v>4</v>
+      </c>
+      <c r="F274" s="28"/>
+    </row>
+    <row r="275" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A275" s="32"/>
+      <c r="B275" s="30"/>
+      <c r="C275" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="D273" s="6" t="s">
+      <c r="D275" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="E273" s="7">
-        <v>4</v>
-      </c>
-      <c r="F273" s="2"/>
-    </row>
-    <row r="274" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A274" s="27"/>
-      <c r="B274" s="15"/>
-      <c r="C274" s="6" t="s">
+      <c r="E275" s="4">
+        <v>4</v>
+      </c>
+      <c r="F275" s="28"/>
+    </row>
+    <row r="276" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
+      <c r="A276" s="32"/>
+      <c r="B276" s="30"/>
+      <c r="C276" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="D274" s="6" t="s">
+      <c r="D276" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="E274" s="7">
-        <v>4</v>
-      </c>
-      <c r="F274" s="2"/>
-    </row>
-    <row r="275" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A275" s="27"/>
-      <c r="B275" s="15"/>
-      <c r="C275" s="6" t="s">
+      <c r="E276" s="4">
+        <v>4</v>
+      </c>
+      <c r="F276" s="28"/>
+    </row>
+    <row r="277" spans="1:6" ht="155" x14ac:dyDescent="0.35">
+      <c r="A277" s="32"/>
+      <c r="B277" s="30"/>
+      <c r="C277" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="D275" s="6" t="s">
+      <c r="D277" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="E275" s="7">
-        <v>4</v>
-      </c>
-      <c r="F275" s="2"/>
-    </row>
-    <row r="276" spans="1:6" ht="139.5" x14ac:dyDescent="0.35">
-      <c r="A276" s="27"/>
-      <c r="B276" s="15"/>
-      <c r="C276" s="6" t="s">
+      <c r="E277" s="4">
+        <v>4</v>
+      </c>
+      <c r="F277" s="28"/>
+    </row>
+    <row r="278" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A278" s="32"/>
+      <c r="B278" s="30"/>
+      <c r="C278" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="D276" s="6" t="s">
+      <c r="D278" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="E278" s="4">
+        <v>4</v>
+      </c>
+      <c r="F278" s="28"/>
+    </row>
+    <row r="279" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A279" s="33"/>
+      <c r="B279" s="31"/>
+      <c r="C279" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="E276" s="7">
-        <v>4</v>
-      </c>
-      <c r="F276" s="2"/>
-    </row>
-    <row r="277" spans="1:6" ht="155" x14ac:dyDescent="0.35">
-      <c r="A277" s="27"/>
-      <c r="B277" s="15"/>
-      <c r="C277" s="6" t="s">
+      <c r="D279" s="9" t="s">
         <v>551</v>
       </c>
-      <c r="D277" s="6" t="s">
+      <c r="E279" s="10">
+        <v>4</v>
+      </c>
+      <c r="F279" s="29"/>
+    </row>
+    <row r="280" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
+      <c r="A280" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="E277" s="7">
-        <v>4</v>
-      </c>
-      <c r="F277" s="2"/>
-    </row>
-    <row r="278" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A278" s="27"/>
-      <c r="B278" s="15"/>
-      <c r="C278" s="6" t="s">
+      <c r="B280" s="18" t="s">
         <v>553</v>
       </c>
-      <c r="D278" s="6" t="s">
+      <c r="C280" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="E278" s="7">
-        <v>4</v>
-      </c>
-      <c r="F278" s="2"/>
-    </row>
-    <row r="279" spans="1:6" ht="140" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A279" s="42"/>
-      <c r="B279" s="18"/>
-      <c r="C279" s="12" t="s">
-        <v>555</v>
-      </c>
-      <c r="D279" s="12" t="s">
-        <v>556</v>
-      </c>
-      <c r="E279" s="13">
-        <v>4</v>
-      </c>
-      <c r="F279" s="3"/>
-    </row>
-    <row r="280" spans="1:6" ht="170.5" x14ac:dyDescent="0.35">
-      <c r="A280" s="26" t="s">
-        <v>557</v>
-      </c>
-      <c r="B280" s="17" t="s">
-        <v>558</v>
-      </c>
-      <c r="C280" s="10" t="s">
-        <v>559</v>
-      </c>
-      <c r="D280" s="10" t="s">
-        <v>560</v>
-      </c>
-      <c r="E280" s="11">
-        <v>4</v>
-      </c>
-      <c r="F280" s="1">
+      <c r="D280" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="E280" s="8">
+        <v>4</v>
+      </c>
+      <c r="F280" s="16">
         <f>SUM(E280:E281)</f>
         <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:6" ht="155.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A281" s="28"/>
-      <c r="B281" s="16"/>
-      <c r="C281" s="8" t="s">
-        <v>561</v>
-      </c>
-      <c r="D281" s="8" t="s">
-        <v>562</v>
-      </c>
-      <c r="E281" s="9">
-        <v>4</v>
-      </c>
-      <c r="F281" s="19"/>
+      <c r="A281" s="21"/>
+      <c r="B281" s="19"/>
+      <c r="C281" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="D281" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="E281" s="6">
+        <v>4</v>
+      </c>
+      <c r="F281" s="17"/>
     </row>
     <row r="282" spans="1:6" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A282" s="29" t="s">
-        <v>565</v>
-      </c>
-      <c r="B282" s="22"/>
-      <c r="C282" s="22"/>
-      <c r="D282" s="22"/>
-      <c r="E282" s="22"/>
-      <c r="F282" s="23">
+      <c r="A282" s="22" t="s">
+        <v>558</v>
+      </c>
+      <c r="B282" s="26"/>
+      <c r="C282" s="26"/>
+      <c r="D282" s="26"/>
+      <c r="E282" s="26"/>
+      <c r="F282" s="24">
         <f>SUM(F4:F281)</f>
         <v>900</v>
       </c>
     </row>
     <row r="283" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A283" s="30"/>
-      <c r="B283" s="24"/>
-      <c r="C283" s="24"/>
-      <c r="D283" s="24"/>
-      <c r="E283" s="24"/>
+      <c r="A283" s="23"/>
+      <c r="B283" s="27"/>
+      <c r="C283" s="27"/>
+      <c r="D283" s="27"/>
+      <c r="E283" s="27"/>
       <c r="F283" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="F9:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="F15:F19"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="F20:F24"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="A20:A24"/>
+    <mergeCell ref="F25:F35"/>
+    <mergeCell ref="B25:B35"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="F36:F48"/>
+    <mergeCell ref="B36:B48"/>
+    <mergeCell ref="A36:A48"/>
+    <mergeCell ref="F49:F65"/>
+    <mergeCell ref="B49:B65"/>
+    <mergeCell ref="A49:A65"/>
+    <mergeCell ref="F66:F75"/>
+    <mergeCell ref="B66:B75"/>
+    <mergeCell ref="A66:A75"/>
+    <mergeCell ref="F76:F86"/>
+    <mergeCell ref="B76:B86"/>
+    <mergeCell ref="A76:A86"/>
+    <mergeCell ref="F87:F96"/>
+    <mergeCell ref="B87:B96"/>
+    <mergeCell ref="A87:A96"/>
+    <mergeCell ref="F97:F107"/>
+    <mergeCell ref="B97:B107"/>
+    <mergeCell ref="A97:A107"/>
+    <mergeCell ref="F108:F117"/>
+    <mergeCell ref="B108:B117"/>
+    <mergeCell ref="A108:A117"/>
+    <mergeCell ref="F118:F128"/>
+    <mergeCell ref="B118:B128"/>
+    <mergeCell ref="A118:A128"/>
+    <mergeCell ref="F129:F141"/>
+    <mergeCell ref="B129:B141"/>
+    <mergeCell ref="A129:A141"/>
+    <mergeCell ref="F142:F152"/>
+    <mergeCell ref="B142:B152"/>
+    <mergeCell ref="A142:A152"/>
+    <mergeCell ref="F153:F162"/>
+    <mergeCell ref="B153:B162"/>
+    <mergeCell ref="A153:A162"/>
+    <mergeCell ref="F163:F176"/>
+    <mergeCell ref="B163:B176"/>
+    <mergeCell ref="A163:A176"/>
+    <mergeCell ref="F177:F195"/>
+    <mergeCell ref="B177:B195"/>
+    <mergeCell ref="A177:A195"/>
+    <mergeCell ref="F196:F214"/>
+    <mergeCell ref="B196:B214"/>
+    <mergeCell ref="A196:A214"/>
+    <mergeCell ref="F215:F224"/>
+    <mergeCell ref="B215:B224"/>
+    <mergeCell ref="A215:A224"/>
+    <mergeCell ref="F225:F241"/>
+    <mergeCell ref="B225:B241"/>
+    <mergeCell ref="A225:A241"/>
+    <mergeCell ref="F242:F252"/>
+    <mergeCell ref="B242:B252"/>
+    <mergeCell ref="A242:A252"/>
+    <mergeCell ref="F253:F269"/>
+    <mergeCell ref="B253:B269"/>
+    <mergeCell ref="A253:A269"/>
+    <mergeCell ref="F270:F279"/>
+    <mergeCell ref="B270:B279"/>
+    <mergeCell ref="A270:A279"/>
     <mergeCell ref="F280:F281"/>
     <mergeCell ref="B280:B281"/>
     <mergeCell ref="A280:A281"/>
     <mergeCell ref="A282:A283"/>
     <mergeCell ref="F282:F283"/>
     <mergeCell ref="B282:E283"/>
-    <mergeCell ref="F253:F269"/>
-    <mergeCell ref="B253:B269"/>
-    <mergeCell ref="A253:A269"/>
-    <mergeCell ref="F270:F279"/>
-    <mergeCell ref="B270:B279"/>
-    <mergeCell ref="A270:A279"/>
-    <mergeCell ref="F225:F241"/>
-    <mergeCell ref="B225:B241"/>
-    <mergeCell ref="A225:A241"/>
-    <mergeCell ref="F242:F252"/>
-    <mergeCell ref="B242:B252"/>
-    <mergeCell ref="A242:A252"/>
-    <mergeCell ref="F196:F214"/>
-    <mergeCell ref="B196:B214"/>
-    <mergeCell ref="A196:A214"/>
-    <mergeCell ref="F215:F224"/>
-    <mergeCell ref="B215:B224"/>
-    <mergeCell ref="A215:A224"/>
-    <mergeCell ref="F163:F176"/>
-    <mergeCell ref="B163:B176"/>
-    <mergeCell ref="A163:A176"/>
-    <mergeCell ref="F177:F195"/>
-    <mergeCell ref="B177:B195"/>
-    <mergeCell ref="A177:A195"/>
-    <mergeCell ref="F142:F152"/>
-    <mergeCell ref="B142:B152"/>
-    <mergeCell ref="A142:A152"/>
-    <mergeCell ref="F153:F162"/>
-    <mergeCell ref="B153:B162"/>
-    <mergeCell ref="A153:A162"/>
-    <mergeCell ref="F118:F128"/>
-    <mergeCell ref="B118:B128"/>
-    <mergeCell ref="A118:A128"/>
-    <mergeCell ref="F129:F141"/>
-    <mergeCell ref="B129:B141"/>
-    <mergeCell ref="A129:A141"/>
-    <mergeCell ref="F97:F107"/>
-    <mergeCell ref="B97:B107"/>
-    <mergeCell ref="A97:A107"/>
-    <mergeCell ref="F108:F117"/>
-    <mergeCell ref="B108:B117"/>
-    <mergeCell ref="A108:A117"/>
-    <mergeCell ref="F76:F86"/>
-    <mergeCell ref="B76:B86"/>
-    <mergeCell ref="A76:A86"/>
-    <mergeCell ref="F87:F96"/>
-    <mergeCell ref="B87:B96"/>
-    <mergeCell ref="A87:A96"/>
-    <mergeCell ref="F49:F65"/>
-    <mergeCell ref="B49:B65"/>
-    <mergeCell ref="A49:A65"/>
-    <mergeCell ref="F66:F75"/>
-    <mergeCell ref="B66:B75"/>
-    <mergeCell ref="A66:A75"/>
-    <mergeCell ref="F25:F35"/>
-    <mergeCell ref="B25:B35"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="F36:F48"/>
-    <mergeCell ref="B36:B48"/>
-    <mergeCell ref="A36:A48"/>
-    <mergeCell ref="F15:F19"/>
-    <mergeCell ref="B15:B19"/>
-    <mergeCell ref="A15:A19"/>
-    <mergeCell ref="F20:F24"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="A20:A24"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="F4:F8"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="B9:B14"/>
-    <mergeCell ref="F9:F14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="66" orientation="landscape" r:id="rId1"/>
